--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:26</t>
+          <t>2026-03-02 08:29:43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:27</t>
+          <t>2026-03-02 08:29:44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:27</t>
+          <t>2026-03-02 08:29:44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:27</t>
+          <t>2026-03-02 08:29:44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:27</t>
+          <t>2026-03-02 08:29:44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:29</t>
+          <t>2026-03-02 08:29:47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:31</t>
+          <t>2026-03-02 08:29:49</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:31</t>
+          <t>2026-03-02 08:29:49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:31</t>
+          <t>2026-03-02 08:29:49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:31</t>
+          <t>2026-03-02 08:29:49</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:33</t>
+          <t>2026-03-02 08:29:51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:35</t>
+          <t>2026-03-02 08:29:53</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:35</t>
+          <t>2026-03-02 08:29:53</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:35</t>
+          <t>2026-03-02 08:29:53</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:35</t>
+          <t>2026-03-02 08:29:53</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:37</t>
+          <t>2026-03-02 08:29:56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:38</t>
+          <t>2026-03-02 08:29:58</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:38</t>
+          <t>2026-03-02 08:29:58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:38</t>
+          <t>2026-03-02 08:29:58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:38</t>
+          <t>2026-03-02 08:29:58</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:41</t>
+          <t>2026-03-02 08:30:00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:42</t>
+          <t>2026-03-02 08:30:02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:42</t>
+          <t>2026-03-02 08:30:02</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:42</t>
+          <t>2026-03-02 08:30:02</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:42</t>
+          <t>2026-03-02 08:30:02</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:44</t>
+          <t>2026-03-02 08:30:05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:46</t>
+          <t>2026-03-02 08:30:07</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:46</t>
+          <t>2026-03-02 08:30:07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:46</t>
+          <t>2026-03-02 08:30:07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:46</t>
+          <t>2026-03-02 08:30:07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:48</t>
+          <t>2026-03-02 08:30:09</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:50</t>
+          <t>2026-03-02 08:30:11</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:50</t>
+          <t>2026-03-02 08:30:11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:50</t>
+          <t>2026-03-02 08:30:11</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:50</t>
+          <t>2026-03-02 08:30:11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:52</t>
+          <t>2026-03-02 08:30:13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:53</t>
+          <t>2026-03-02 08:30:14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:53</t>
+          <t>2026-03-02 08:30:14</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:53</t>
+          <t>2026-03-02 08:30:14</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:53</t>
+          <t>2026-03-02 08:30:14</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:56</t>
+          <t>2026-03-02 08:30:17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:57</t>
+          <t>2026-03-02 08:30:19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:57</t>
+          <t>2026-03-02 08:30:19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:57</t>
+          <t>2026-03-02 08:30:19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-02 08:15:57</t>
+          <t>2026-03-02 08:30:19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:00</t>
+          <t>2026-03-02 08:30:21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:01</t>
+          <t>2026-03-02 08:30:22</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:01</t>
+          <t>2026-03-02 08:30:22</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:01</t>
+          <t>2026-03-02 08:30:22</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:01</t>
+          <t>2026-03-02 08:30:22</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:03</t>
+          <t>2026-03-02 08:30:25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:05</t>
+          <t>2026-03-02 08:30:27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:05</t>
+          <t>2026-03-02 08:30:27</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:05</t>
+          <t>2026-03-02 08:30:27</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:05</t>
+          <t>2026-03-02 08:30:27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:07</t>
+          <t>2026-03-02 08:30:29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:08</t>
+          <t>2026-03-02 08:30:31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:08</t>
+          <t>2026-03-02 08:30:31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:08</t>
+          <t>2026-03-02 08:30:31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:08</t>
+          <t>2026-03-02 08:30:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:11</t>
+          <t>2026-03-02 08:30:34</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:12</t>
+          <t>2026-03-02 08:30:35</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:12</t>
+          <t>2026-03-02 08:30:35</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:12</t>
+          <t>2026-03-02 08:30:35</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:12</t>
+          <t>2026-03-02 08:30:35</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:15</t>
+          <t>2026-03-02 08:30:38</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:16</t>
+          <t>2026-03-02 08:30:39</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:16</t>
+          <t>2026-03-02 08:30:39</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:16</t>
+          <t>2026-03-02 08:30:39</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:16</t>
+          <t>2026-03-02 08:30:39</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:18</t>
+          <t>2026-03-02 08:30:41</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:19</t>
+          <t>2026-03-02 08:30:43</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:19</t>
+          <t>2026-03-02 08:30:43</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:19</t>
+          <t>2026-03-02 08:30:43</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:19</t>
+          <t>2026-03-02 08:30:43</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:22</t>
+          <t>2026-03-02 08:30:45</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:23</t>
+          <t>2026-03-02 08:30:47</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:23</t>
+          <t>2026-03-02 08:30:47</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:23</t>
+          <t>2026-03-02 08:30:47</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:23</t>
+          <t>2026-03-02 08:30:47</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:26</t>
+          <t>2026-03-02 08:30:50</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:27</t>
+          <t>2026-03-02 08:30:51</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:27</t>
+          <t>2026-03-02 08:30:51</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:27</t>
+          <t>2026-03-02 08:30:51</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:27</t>
+          <t>2026-03-02 08:30:51</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:29</t>
+          <t>2026-03-02 08:30:53</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:31</t>
+          <t>2026-03-02 08:30:55</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:31</t>
+          <t>2026-03-02 08:30:55</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:31</t>
+          <t>2026-03-02 08:30:55</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:31</t>
+          <t>2026-03-02 08:30:55</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:33</t>
+          <t>2026-03-02 08:30:58</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:35</t>
+          <t>2026-03-02 08:30:59</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:35</t>
+          <t>2026-03-02 08:30:59</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:35</t>
+          <t>2026-03-02 08:30:59</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:35</t>
+          <t>2026-03-02 08:30:59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:37</t>
+          <t>2026-03-02 08:31:02</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:38</t>
+          <t>2026-03-02 08:31:03</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:38</t>
+          <t>2026-03-02 08:31:03</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:38</t>
+          <t>2026-03-02 08:31:03</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:38</t>
+          <t>2026-03-02 08:31:03</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:41</t>
+          <t>2026-03-02 08:31:06</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:42</t>
+          <t>2026-03-02 08:31:08</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:42</t>
+          <t>2026-03-02 08:31:08</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:42</t>
+          <t>2026-03-02 08:31:08</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:42</t>
+          <t>2026-03-02 08:31:08</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:45</t>
+          <t>2026-03-02 08:31:11</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:46</t>
+          <t>2026-03-02 08:31:12</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:46</t>
+          <t>2026-03-02 08:31:12</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:46</t>
+          <t>2026-03-02 08:31:12</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:46</t>
+          <t>2026-03-02 08:31:12</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25048,17 +25048,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:49</t>
+          <t>2026-03-02 08:31:15</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:50</t>
+          <t>2026-03-02 08:31:17</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:50</t>
+          <t>2026-03-02 08:31:17</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:50</t>
+          <t>2026-03-02 08:31:17</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:50</t>
+          <t>2026-03-02 08:31:17</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,17 +26213,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:52</t>
+          <t>2026-03-02 08:31:20</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:54</t>
+          <t>2026-03-02 08:31:21</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:54</t>
+          <t>2026-03-02 08:31:21</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:54</t>
+          <t>2026-03-02 08:31:21</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:54</t>
+          <t>2026-03-02 08:31:21</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27378,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:56</t>
+          <t>2026-03-02 08:31:24</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:57</t>
+          <t>2026-03-02 08:31:25</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:57</t>
+          <t>2026-03-02 08:31:25</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:57</t>
+          <t>2026-03-02 08:31:25</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-02 08:16:57</t>
+          <t>2026-03-02 08:31:25</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:00</t>
+          <t>2026-03-02 08:31:28</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:01</t>
+          <t>2026-03-02 08:31:30</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:01</t>
+          <t>2026-03-02 08:31:30</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:01</t>
+          <t>2026-03-02 08:31:30</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:01</t>
+          <t>2026-03-02 08:31:30</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29736,17 +29736,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:03</t>
+          <t>2026-03-02 08:31:32</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29969,7 +29969,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:05</t>
+          <t>2026-03-02 08:31:34</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30202,7 +30202,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:05</t>
+          <t>2026-03-02 08:31:34</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:05</t>
+          <t>2026-03-02 08:31:34</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:05</t>
+          <t>2026-03-02 08:31:34</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30901,17 +30901,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:07</t>
+          <t>2026-03-02 08:31:37</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:08</t>
+          <t>2026-03-02 08:31:39</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31343,7 +31343,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:08</t>
+          <t>2026-03-02 08:31:39</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31564,7 +31564,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:08</t>
+          <t>2026-03-02 08:31:39</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:08</t>
+          <t>2026-03-02 08:31:39</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32006,17 +32006,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:11</t>
+          <t>2026-03-02 08:31:41</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:12</t>
+          <t>2026-03-02 08:31:42</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:12</t>
+          <t>2026-03-02 08:31:42</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:12</t>
+          <t>2026-03-02 08:31:42</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:12</t>
+          <t>2026-03-02 08:31:42</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33171,17 +33171,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:14</t>
+          <t>2026-03-02 08:31:44</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:15</t>
+          <t>2026-03-02 08:31:46</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33637,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:15</t>
+          <t>2026-03-02 08:31:46</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:15</t>
+          <t>2026-03-02 08:31:46</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:15</t>
+          <t>2026-03-02 08:31:46</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34336,17 +34336,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:18</t>
+          <t>2026-03-02 08:31:48</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:19</t>
+          <t>2026-03-02 08:31:50</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:19</t>
+          <t>2026-03-02 08:31:50</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:19</t>
+          <t>2026-03-02 08:31:50</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:19</t>
+          <t>2026-03-02 08:31:50</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35501,17 +35501,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:22</t>
+          <t>2026-03-02 08:31:53</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35734,7 +35734,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:23</t>
+          <t>2026-03-02 08:31:54</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35967,7 +35967,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:23</t>
+          <t>2026-03-02 08:31:54</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36200,7 +36200,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:23</t>
+          <t>2026-03-02 08:31:54</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:23</t>
+          <t>2026-03-02 08:31:54</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36666,17 +36666,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:25</t>
+          <t>2026-03-02 08:31:57</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36907,7 +36907,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:26</t>
+          <t>2026-03-02 08:31:58</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37148,7 +37148,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:26</t>
+          <t>2026-03-02 08:31:58</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:26</t>
+          <t>2026-03-02 08:31:58</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:26</t>
+          <t>2026-03-02 08:31:58</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37871,17 +37871,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:28</t>
+          <t>2026-03-02 08:32:01</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:30</t>
+          <t>2026-03-02 08:32:03</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38329,7 +38329,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:30</t>
+          <t>2026-03-02 08:32:03</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38558,7 +38558,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:30</t>
+          <t>2026-03-02 08:32:03</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38787,7 +38787,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:30</t>
+          <t>2026-03-02 08:32:03</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39016,17 +39016,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:32</t>
+          <t>2026-03-02 08:32:05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39249,7 +39249,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:34</t>
+          <t>2026-03-02 08:32:07</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39482,7 +39482,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:34</t>
+          <t>2026-03-02 08:32:07</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:34</t>
+          <t>2026-03-02 08:32:07</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39948,7 +39948,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:34</t>
+          <t>2026-03-02 08:32:07</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40181,17 +40181,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:36</t>
+          <t>2026-03-02 08:32:10</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40402,7 +40402,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:38</t>
+          <t>2026-03-02 08:32:12</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:38</t>
+          <t>2026-03-02 08:32:12</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:38</t>
+          <t>2026-03-02 08:32:12</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:38</t>
+          <t>2026-03-02 08:32:12</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41286,17 +41286,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:40</t>
+          <t>2026-03-02 08:32:14</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41507,7 +41507,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:42</t>
+          <t>2026-03-02 08:32:15</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:42</t>
+          <t>2026-03-02 08:32:15</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:42</t>
+          <t>2026-03-02 08:32:15</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42170,7 +42170,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:42</t>
+          <t>2026-03-02 08:32:15</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42391,17 +42391,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:44</t>
+          <t>2026-03-02 08:32:18</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:45</t>
+          <t>2026-03-02 08:32:20</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42857,7 +42857,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:45</t>
+          <t>2026-03-02 08:32:20</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43090,7 +43090,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:45</t>
+          <t>2026-03-02 08:32:20</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43323,7 +43323,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:45</t>
+          <t>2026-03-02 08:32:20</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43556,17 +43556,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:48</t>
+          <t>2026-03-02 08:32:22</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43753,7 +43753,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:49</t>
+          <t>2026-03-02 08:32:24</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43950,7 +43950,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:49</t>
+          <t>2026-03-02 08:32:24</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44147,7 +44147,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:49</t>
+          <t>2026-03-02 08:32:24</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44344,7 +44344,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:49</t>
+          <t>2026-03-02 08:32:24</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44541,17 +44541,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:52</t>
+          <t>2026-03-02 08:32:27</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:53</t>
+          <t>2026-03-02 08:32:28</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45007,7 +45007,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:53</t>
+          <t>2026-03-02 08:32:28</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45240,7 +45240,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:53</t>
+          <t>2026-03-02 08:32:28</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45473,7 +45473,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:53</t>
+          <t>2026-03-02 08:32:28</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45706,17 +45706,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:55</t>
+          <t>2026-03-02 08:32:31</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:57</t>
+          <t>2026-03-02 08:32:32</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46052,7 +46052,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:57</t>
+          <t>2026-03-02 08:32:32</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:57</t>
+          <t>2026-03-02 08:32:32</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46398,7 +46398,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:57</t>
+          <t>2026-03-02 08:32:32</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46571,17 +46571,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-02 08:17:59</t>
+          <t>2026-03-02 08:32:35</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46792,7 +46792,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:00</t>
+          <t>2026-03-02 08:32:36</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:00</t>
+          <t>2026-03-02 08:32:36</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47234,7 +47234,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:00</t>
+          <t>2026-03-02 08:32:36</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47455,7 +47455,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:00</t>
+          <t>2026-03-02 08:32:36</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47676,17 +47676,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:03</t>
+          <t>2026-03-02 08:32:39</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47917,7 +47917,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:04</t>
+          <t>2026-03-02 08:32:41</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48158,7 +48158,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:04</t>
+          <t>2026-03-02 08:32:41</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48399,7 +48399,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:04</t>
+          <t>2026-03-02 08:32:41</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48640,7 +48640,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:04</t>
+          <t>2026-03-02 08:32:41</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48881,17 +48881,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:07</t>
+          <t>2026-03-02 08:32:44</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49122,7 +49122,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:08</t>
+          <t>2026-03-02 08:32:46</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49363,7 +49363,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:08</t>
+          <t>2026-03-02 08:32:46</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49604,7 +49604,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:08</t>
+          <t>2026-03-02 08:32:46</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49845,7 +49845,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:08</t>
+          <t>2026-03-02 08:32:46</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50086,17 +50086,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:11</t>
+          <t>2026-03-02 08:32:48</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50319,7 +50319,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:12</t>
+          <t>2026-03-02 08:32:50</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50552,7 +50552,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:12</t>
+          <t>2026-03-02 08:32:50</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50785,7 +50785,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:12</t>
+          <t>2026-03-02 08:32:50</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51018,7 +51018,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-02 08:18:12</t>
+          <t>2026-03-02 08:32:50</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51435,7 +51435,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51465,7 +51465,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51495,7 +51495,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51555,7 +51555,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51585,7 +51585,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51615,7 +51615,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51645,7 +51645,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51675,7 +51675,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51705,7 +51705,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51735,7 +51735,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51765,7 +51765,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51795,7 +51795,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51825,7 +51825,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51855,7 +51855,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51885,7 +51885,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51915,7 +51915,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51945,7 +51945,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51975,7 +51975,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52005,7 +52005,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52035,7 +52035,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52065,7 +52065,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52095,7 +52095,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52125,7 +52125,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52155,7 +52155,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52185,7 +52185,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52215,7 +52215,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52245,7 +52245,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52275,7 +52275,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52305,7 +52305,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52335,7 +52335,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52365,7 +52365,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52395,7 +52395,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52425,7 +52425,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52455,7 +52455,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52485,7 +52485,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52515,7 +52515,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52545,7 +52545,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52575,7 +52575,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52605,7 +52605,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T08:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:27</t>
+          <t>2026-03-02 09:33:13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:29</t>
+          <t>2026-03-02 09:33:14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:29</t>
+          <t>2026-03-02 09:33:14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:29</t>
+          <t>2026-03-02 09:33:14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:29</t>
+          <t>2026-03-02 09:33:14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:32</t>
+          <t>2026-03-02 09:33:17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:33</t>
+          <t>2026-03-02 09:33:18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:33</t>
+          <t>2026-03-02 09:33:18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:33</t>
+          <t>2026-03-02 09:33:18</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:33</t>
+          <t>2026-03-02 09:33:18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:36</t>
+          <t>2026-03-02 09:33:21</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:37</t>
+          <t>2026-03-02 09:33:22</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:37</t>
+          <t>2026-03-02 09:33:22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:37</t>
+          <t>2026-03-02 09:33:22</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:37</t>
+          <t>2026-03-02 09:33:22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:40</t>
+          <t>2026-03-02 09:33:25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:42</t>
+          <t>2026-03-02 09:33:26</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:42</t>
+          <t>2026-03-02 09:33:26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:42</t>
+          <t>2026-03-02 09:33:26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:42</t>
+          <t>2026-03-02 09:33:26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:44</t>
+          <t>2026-03-02 09:33:28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:46</t>
+          <t>2026-03-02 09:33:30</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:46</t>
+          <t>2026-03-02 09:33:30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:46</t>
+          <t>2026-03-02 09:33:30</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:46</t>
+          <t>2026-03-02 09:33:30</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:49</t>
+          <t>2026-03-02 09:33:32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:50</t>
+          <t>2026-03-02 09:33:34</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:50</t>
+          <t>2026-03-02 09:33:34</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:50</t>
+          <t>2026-03-02 09:33:34</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:50</t>
+          <t>2026-03-02 09:33:34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:53</t>
+          <t>2026-03-02 09:33:36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:55</t>
+          <t>2026-03-02 09:33:38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7783,15 +7783,15 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (10 m) km/h, DVM (10 m) graus, VVX (10 m) km/h, PM hPa, RS W/m 2</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (2 m) km/h, DVM (2 m) graus, VVX (2 m) km/h, PM hPa, RS W/m 2</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
@@ -7834,19 +7834,19 @@
           <t>8.8</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>20.9</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>22.0</t>
+        </is>
+      </c>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -7920,17 +7920,17 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:55</t>
+          <t>2026-03-02 09:33:38</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8016,15 +8016,15 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (10 m) km/h, DVM (10 m) graus, VVX (10 m) km/h, PM hPa, RS W/m 2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (2 m) km/h, DVM (2 m) graus, VVX (2 m) km/h, PM hPa, RS W/m 2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
@@ -8067,19 +8067,19 @@
           <t>8.7</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>14.4</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>247</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:55</t>
+          <t>2026-03-02 09:33:38</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8249,15 +8249,15 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (10 m) km/h, DVM (10 m) graus, VVX (10 m) km/h, PM hPa, RS W/m 2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (2 m) km/h, DVM (2 m) graus, VVX (2 m) km/h, PM hPa, RS W/m 2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
@@ -8300,19 +8300,19 @@
           <t>8.8</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17.6</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
@@ -8346,12 +8346,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -8386,17 +8386,17 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:55</t>
+          <t>2026-03-02 09:33:38</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8482,15 +8482,15 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (10 m) km/h, DVM (10 m) graus, VVX (10 m) km/h, PM hPa, RS W/m 2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>Període TU, TM °C, TX °C, TN °C, HRM %, PPT mm, VVM (2 m) km/h, DVM (2 m) graus, VVX (2 m) km/h, PM hPa, RS W/m 2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
@@ -8533,19 +8533,19 @@
           <t>8.8</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>274</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -8619,17 +8619,17 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>274</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-02 09:15:58</t>
+          <t>2026-03-02 09:33:40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:00</t>
+          <t>2026-03-02 09:33:42</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:00</t>
+          <t>2026-03-02 09:33:42</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:00</t>
+          <t>2026-03-02 09:33:42</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:00</t>
+          <t>2026-03-02 09:33:42</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:02</t>
+          <t>2026-03-02 09:33:44</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:04</t>
+          <t>2026-03-02 09:33:45</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:04</t>
+          <t>2026-03-02 09:33:45</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:04</t>
+          <t>2026-03-02 09:33:45</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:04</t>
+          <t>2026-03-02 09:33:45</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:07</t>
+          <t>2026-03-02 09:33:48</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:08</t>
+          <t>2026-03-02 09:33:49</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:08</t>
+          <t>2026-03-02 09:33:49</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:08</t>
+          <t>2026-03-02 09:33:49</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:08</t>
+          <t>2026-03-02 09:33:49</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:10</t>
+          <t>2026-03-02 09:33:52</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:12</t>
+          <t>2026-03-02 09:33:53</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:12</t>
+          <t>2026-03-02 09:33:53</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:12</t>
+          <t>2026-03-02 09:33:53</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:12</t>
+          <t>2026-03-02 09:33:53</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:15</t>
+          <t>2026-03-02 09:33:55</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:16</t>
+          <t>2026-03-02 09:33:57</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:16</t>
+          <t>2026-03-02 09:33:57</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:16</t>
+          <t>2026-03-02 09:33:57</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:16</t>
+          <t>2026-03-02 09:33:57</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:19</t>
+          <t>2026-03-02 09:33:59</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:20</t>
+          <t>2026-03-02 09:34:01</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:20</t>
+          <t>2026-03-02 09:34:01</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:20</t>
+          <t>2026-03-02 09:34:01</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:20</t>
+          <t>2026-03-02 09:34:01</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:23</t>
+          <t>2026-03-02 09:34:03</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:25</t>
+          <t>2026-03-02 09:34:04</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:25</t>
+          <t>2026-03-02 09:34:04</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:25</t>
+          <t>2026-03-02 09:34:04</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:25</t>
+          <t>2026-03-02 09:34:04</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:27</t>
+          <t>2026-03-02 09:34:07</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:29</t>
+          <t>2026-03-02 09:34:08</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:29</t>
+          <t>2026-03-02 09:34:08</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:29</t>
+          <t>2026-03-02 09:34:08</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:29</t>
+          <t>2026-03-02 09:34:08</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:31</t>
+          <t>2026-03-02 09:34:11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:33</t>
+          <t>2026-03-02 09:34:12</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:33</t>
+          <t>2026-03-02 09:34:12</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:33</t>
+          <t>2026-03-02 09:34:12</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:33</t>
+          <t>2026-03-02 09:34:12</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:36</t>
+          <t>2026-03-02 09:34:15</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:38</t>
+          <t>2026-03-02 09:34:16</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:38</t>
+          <t>2026-03-02 09:34:16</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:38</t>
+          <t>2026-03-02 09:34:16</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:38</t>
+          <t>2026-03-02 09:34:16</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:40</t>
+          <t>2026-03-02 09:34:18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:42</t>
+          <t>2026-03-02 09:34:20</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:42</t>
+          <t>2026-03-02 09:34:20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:42</t>
+          <t>2026-03-02 09:34:20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:42</t>
+          <t>2026-03-02 09:34:20</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:45</t>
+          <t>2026-03-02 09:34:22</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:46</t>
+          <t>2026-03-02 09:34:23</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:46</t>
+          <t>2026-03-02 09:34:23</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21099,7 +21099,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:46</t>
+          <t>2026-03-02 09:34:23</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21332,7 +21332,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:46</t>
+          <t>2026-03-02 09:34:23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21565,17 +21565,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:49</t>
+          <t>2026-03-02 09:34:26</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:51</t>
+          <t>2026-03-02 09:34:27</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:51</t>
+          <t>2026-03-02 09:34:27</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:51</t>
+          <t>2026-03-02 09:34:27</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:51</t>
+          <t>2026-03-02 09:34:27</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22730,17 +22730,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:53</t>
+          <t>2026-03-02 09:34:30</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:55</t>
+          <t>2026-03-02 09:34:31</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -22993,7 +22993,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
@@ -23118,7 +23118,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:55</t>
+          <t>2026-03-02 09:34:31</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:55</t>
+          <t>2026-03-02 09:34:31</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
@@ -23584,7 +23584,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:55</t>
+          <t>2026-03-02 09:34:31</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23711,7 +23711,11 @@
           <t>22:00 - 22:30</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr"/>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="V106" t="inlineStr">
         <is>
           <t>-3.6</t>
@@ -23831,7 +23835,11 @@
           <t>14.4</t>
         </is>
       </c>
-      <c r="AW106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AX106" t="inlineStr">
         <is>
           <t>331</t>
@@ -23842,7 +23850,11 @@
           <t>14.4</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="BA106" t="inlineStr"/>
     </row>
     <row r="107">
@@ -23883,17 +23895,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-02 09:16:58</t>
+          <t>2026-03-02 09:34:33</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24116,7 +24128,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:00</t>
+          <t>2026-03-02 09:34:35</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24361,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:00</t>
+          <t>2026-03-02 09:34:35</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24594,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:00</t>
+          <t>2026-03-02 09:34:35</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24827,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:00</t>
+          <t>2026-03-02 09:34:35</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25048,17 +25060,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:02</t>
+          <t>2026-03-02 09:34:37</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25281,7 +25293,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:04</t>
+          <t>2026-03-02 09:34:38</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25526,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:04</t>
+          <t>2026-03-02 09:34:38</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25759,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:04</t>
+          <t>2026-03-02 09:34:38</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25992,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:04</t>
+          <t>2026-03-02 09:34:38</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,17 +26225,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:07</t>
+          <t>2026-03-02 09:34:41</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26446,7 +26458,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:08</t>
+          <t>2026-03-02 09:34:42</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26691,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:08</t>
+          <t>2026-03-02 09:34:42</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26924,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:08</t>
+          <t>2026-03-02 09:34:42</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27157,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:08</t>
+          <t>2026-03-02 09:34:42</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,17 +27390,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:11</t>
+          <t>2026-03-02 09:34:45</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27619,7 +27631,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:13</t>
+          <t>2026-03-02 09:34:46</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27872,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:13</t>
+          <t>2026-03-02 09:34:46</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28113,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:13</t>
+          <t>2026-03-02 09:34:46</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28354,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:13</t>
+          <t>2026-03-02 09:34:46</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,17 +28595,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:15</t>
+          <t>2026-03-02 09:34:49</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28816,7 +28828,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:17</t>
+          <t>2026-03-02 09:34:50</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29061,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:17</t>
+          <t>2026-03-02 09:34:50</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:17</t>
+          <t>2026-03-02 09:34:50</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:17</t>
+          <t>2026-03-02 09:34:50</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29736,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:20</t>
+          <t>2026-03-02 09:34:53</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29969,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:22</t>
+          <t>2026-03-02 09:34:54</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30202,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:22</t>
+          <t>2026-03-02 09:34:54</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30435,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:22</t>
+          <t>2026-03-02 09:34:54</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30668,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:22</t>
+          <t>2026-03-02 09:34:54</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30901,17 +30913,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:24</t>
+          <t>2026-03-02 09:34:57</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31122,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:25</t>
+          <t>2026-03-02 09:34:58</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31343,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:25</t>
+          <t>2026-03-02 09:34:58</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31564,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:25</t>
+          <t>2026-03-02 09:34:58</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:25</t>
+          <t>2026-03-02 09:34:58</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32006,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:28</t>
+          <t>2026-03-02 09:35:00</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32239,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:29</t>
+          <t>2026-03-02 09:35:02</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:29</t>
+          <t>2026-03-02 09:35:02</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:29</t>
+          <t>2026-03-02 09:35:02</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:29</t>
+          <t>2026-03-02 09:35:02</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33171,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:31</t>
+          <t>2026-03-02 09:35:04</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33404,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:33</t>
+          <t>2026-03-02 09:35:06</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:33</t>
+          <t>2026-03-02 09:35:06</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:33</t>
+          <t>2026-03-02 09:35:06</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:33</t>
+          <t>2026-03-02 09:35:06</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34336,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:35</t>
+          <t>2026-03-02 09:35:08</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34569,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:36</t>
+          <t>2026-03-02 09:35:10</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34599,7 +34611,7 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
@@ -34684,7 +34696,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -34724,7 +34736,7 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
@@ -34802,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:36</t>
+          <t>2026-03-02 09:35:10</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34832,7 +34844,7 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
@@ -34917,7 +34929,7 @@
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -34957,7 +34969,7 @@
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
@@ -35035,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:36</t>
+          <t>2026-03-02 09:35:10</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35065,7 +35077,7 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
@@ -35150,7 +35162,7 @@
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -35190,7 +35202,7 @@
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
@@ -35268,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:36</t>
+          <t>2026-03-02 09:35:10</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35298,7 +35310,7 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
@@ -35383,7 +35395,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -35423,7 +35435,7 @@
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
@@ -35501,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:39</t>
+          <t>2026-03-02 09:35:12</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35734,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:40</t>
+          <t>2026-03-02 09:35:14</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35967,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:40</t>
+          <t>2026-03-02 09:35:14</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36200,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:40</t>
+          <t>2026-03-02 09:35:14</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36433,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:40</t>
+          <t>2026-03-02 09:35:14</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36666,17 +36678,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:43</t>
+          <t>2026-03-02 09:35:16</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36907,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:45</t>
+          <t>2026-03-02 09:35:18</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37148,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:45</t>
+          <t>2026-03-02 09:35:18</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37389,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:45</t>
+          <t>2026-03-02 09:35:18</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37630,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:45</t>
+          <t>2026-03-02 09:35:18</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37871,17 +37883,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:47</t>
+          <t>2026-03-02 09:35:20</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38112,7 +38124,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:49</t>
+          <t>2026-03-02 09:35:22</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38140,7 +38152,11 @@
       </c>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>91</t>
@@ -38225,7 +38241,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK168" t="inlineStr"/>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL168" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -38261,7 +38281,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS168" t="inlineStr"/>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT168" t="inlineStr">
         <is>
           <t>10.4</t>
@@ -38341,7 +38365,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:49</t>
+          <t>2026-03-02 09:35:22</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38369,7 +38393,11 @@
       </c>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>92</t>
@@ -38454,7 +38482,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK169" t="inlineStr"/>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL169" t="inlineStr">
         <is>
           <t>11.2</t>
@@ -38490,7 +38522,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS169" t="inlineStr"/>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT169" t="inlineStr">
         <is>
           <t>11.2</t>
@@ -38570,7 +38606,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:49</t>
+          <t>2026-03-02 09:35:22</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38598,7 +38634,11 @@
       </c>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>93</t>
@@ -38683,7 +38723,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK170" t="inlineStr"/>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL170" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -38719,7 +38763,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS170" t="inlineStr"/>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT170" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -38799,7 +38847,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:49</t>
+          <t>2026-03-02 09:35:22</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38827,7 +38875,11 @@
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="Q171" t="inlineStr">
         <is>
           <t>93</t>
@@ -38912,7 +38964,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK171" t="inlineStr"/>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AL171" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -38948,7 +39004,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS171" t="inlineStr"/>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AT171" t="inlineStr">
         <is>
           <t>10.1</t>
@@ -39028,17 +39088,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:51</t>
+          <t>2026-03-02 09:35:24</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39261,7 +39321,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:52</t>
+          <t>2026-03-02 09:35:25</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39494,7 +39554,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:52</t>
+          <t>2026-03-02 09:35:25</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39727,7 +39787,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:52</t>
+          <t>2026-03-02 09:35:25</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39960,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:52</t>
+          <t>2026-03-02 09:35:25</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40193,17 +40253,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:55</t>
+          <t>2026-03-02 09:35:28</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40414,7 +40474,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:57</t>
+          <t>2026-03-02 09:35:29</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40635,7 +40695,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:57</t>
+          <t>2026-03-02 09:35:29</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40856,7 +40916,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:57</t>
+          <t>2026-03-02 09:35:29</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41077,7 +41137,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:57</t>
+          <t>2026-03-02 09:35:29</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41298,17 +41358,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-02 09:17:59</t>
+          <t>2026-03-02 09:35:32</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41519,7 +41579,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:00</t>
+          <t>2026-03-02 09:35:33</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41740,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:00</t>
+          <t>2026-03-02 09:35:33</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41961,7 +42021,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:00</t>
+          <t>2026-03-02 09:35:33</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42182,7 +42242,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:00</t>
+          <t>2026-03-02 09:35:33</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42403,17 +42463,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:03</t>
+          <t>2026-03-02 09:35:36</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42636,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:04</t>
+          <t>2026-03-02 09:35:37</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42869,7 +42929,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:04</t>
+          <t>2026-03-02 09:35:37</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43102,7 +43162,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:04</t>
+          <t>2026-03-02 09:35:37</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43335,7 +43395,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:04</t>
+          <t>2026-03-02 09:35:37</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43568,17 +43628,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:07</t>
+          <t>2026-03-02 09:35:40</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43765,7 +43825,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:08</t>
+          <t>2026-03-02 09:35:41</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43962,7 +44022,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:08</t>
+          <t>2026-03-02 09:35:41</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44159,7 +44219,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:08</t>
+          <t>2026-03-02 09:35:41</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44356,7 +44416,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:08</t>
+          <t>2026-03-02 09:35:41</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44553,17 +44613,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:10</t>
+          <t>2026-03-02 09:35:44</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44786,7 +44846,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:11</t>
+          <t>2026-03-02 09:35:45</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45019,7 +45079,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:11</t>
+          <t>2026-03-02 09:35:45</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45252,7 +45312,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:11</t>
+          <t>2026-03-02 09:35:45</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45485,7 +45545,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:11</t>
+          <t>2026-03-02 09:35:45</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45718,17 +45778,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:14</t>
+          <t>2026-03-02 09:35:47</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45891,7 +45951,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:15</t>
+          <t>2026-03-02 09:35:48</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46064,7 +46124,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:15</t>
+          <t>2026-03-02 09:35:48</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46237,7 +46297,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:15</t>
+          <t>2026-03-02 09:35:48</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46410,7 +46470,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:15</t>
+          <t>2026-03-02 09:35:48</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46583,17 +46643,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:18</t>
+          <t>2026-03-02 09:35:51</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46804,7 +46864,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:19</t>
+          <t>2026-03-02 09:35:53</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47025,7 +47085,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:19</t>
+          <t>2026-03-02 09:35:53</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47246,7 +47306,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:19</t>
+          <t>2026-03-02 09:35:53</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47467,7 +47527,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:19</t>
+          <t>2026-03-02 09:35:53</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47688,17 +47748,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:21</t>
+          <t>2026-03-02 09:35:55</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47929,7 +47989,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:22</t>
+          <t>2026-03-02 09:35:57</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48170,7 +48230,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:22</t>
+          <t>2026-03-02 09:35:57</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48411,7 +48471,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:22</t>
+          <t>2026-03-02 09:35:57</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48652,7 +48712,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:22</t>
+          <t>2026-03-02 09:35:57</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48893,17 +48953,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:25</t>
+          <t>2026-03-02 09:35:59</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49134,7 +49194,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:27</t>
+          <t>2026-03-02 09:36:00</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49375,7 +49435,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:27</t>
+          <t>2026-03-02 09:36:00</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49616,7 +49676,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:27</t>
+          <t>2026-03-02 09:36:00</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49857,7 +49917,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:27</t>
+          <t>2026-03-02 09:36:00</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50098,17 +50158,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:30</t>
+          <t>2026-03-02 09:36:03</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50331,7 +50391,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:31</t>
+          <t>2026-03-02 09:36:04</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50564,7 +50624,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:31</t>
+          <t>2026-03-02 09:36:04</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50797,7 +50857,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:31</t>
+          <t>2026-03-02 09:36:04</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51030,7 +51090,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-02 09:18:31</t>
+          <t>2026-03-02 09:36:04</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51297,7 +51357,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51327,7 +51387,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51357,7 +51417,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51387,7 +51447,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51417,7 +51477,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51447,7 +51507,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51477,7 +51537,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51507,7 +51567,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51537,7 +51597,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51567,7 +51627,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51597,7 +51657,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51627,7 +51687,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51657,7 +51717,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51687,7 +51747,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51717,7 +51777,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51747,7 +51807,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51777,7 +51837,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51807,7 +51867,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51837,7 +51897,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51867,7 +51927,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51897,7 +51957,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51927,7 +51987,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51957,7 +52017,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -51987,7 +52047,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52017,7 +52077,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52047,7 +52107,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52077,7 +52137,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52107,7 +52167,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52137,7 +52197,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52167,7 +52227,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52197,7 +52257,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52227,7 +52287,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52257,7 +52317,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52287,7 +52347,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52317,7 +52377,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52347,7 +52407,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52377,7 +52437,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52407,7 +52467,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52437,7 +52497,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52467,7 +52527,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52497,7 +52557,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52527,7 +52587,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52557,7 +52617,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52587,7 +52647,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>
@@ -52617,7 +52677,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T08:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T09:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:26</t>
+          <t>2026-03-02 14:02:10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:27</t>
+          <t>2026-03-02 14:02:11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:27</t>
+          <t>2026-03-02 14:02:11</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:27</t>
+          <t>2026-03-02 14:02:11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:27</t>
+          <t>2026-03-02 14:02:11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:30</t>
+          <t>2026-03-02 14:02:14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:31</t>
+          <t>2026-03-02 14:02:16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:31</t>
+          <t>2026-03-02 14:02:16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:31</t>
+          <t>2026-03-02 14:02:16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:31</t>
+          <t>2026-03-02 14:02:16</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:34</t>
+          <t>2026-03-02 14:02:19</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:35</t>
+          <t>2026-03-02 14:02:20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:35</t>
+          <t>2026-03-02 14:02:20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:35</t>
+          <t>2026-03-02 14:02:20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:35</t>
+          <t>2026-03-02 14:02:20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:37</t>
+          <t>2026-03-02 14:02:23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:39</t>
+          <t>2026-03-02 14:02:25</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:39</t>
+          <t>2026-03-02 14:02:25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:39</t>
+          <t>2026-03-02 14:02:25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:39</t>
+          <t>2026-03-02 14:02:25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:41</t>
+          <t>2026-03-02 14:02:27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:42</t>
+          <t>2026-03-02 14:02:29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:42</t>
+          <t>2026-03-02 14:02:29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:42</t>
+          <t>2026-03-02 14:02:29</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:42</t>
+          <t>2026-03-02 14:02:29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:45</t>
+          <t>2026-03-02 14:02:32</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:46</t>
+          <t>2026-03-02 14:02:33</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:46</t>
+          <t>2026-03-02 14:02:33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:46</t>
+          <t>2026-03-02 14:02:33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:46</t>
+          <t>2026-03-02 14:02:33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:49</t>
+          <t>2026-03-02 14:02:36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:50</t>
+          <t>2026-03-02 14:02:38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:50</t>
+          <t>2026-03-02 14:02:38</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:50</t>
+          <t>2026-03-02 14:02:38</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:50</t>
+          <t>2026-03-02 14:02:38</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:52</t>
+          <t>2026-03-02 14:02:40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:54</t>
+          <t>2026-03-02 14:02:42</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:54</t>
+          <t>2026-03-02 14:02:42</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:54</t>
+          <t>2026-03-02 14:02:42</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:54</t>
+          <t>2026-03-02 14:02:42</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:56</t>
+          <t>2026-03-02 14:02:45</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:58</t>
+          <t>2026-03-02 14:02:46</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:58</t>
+          <t>2026-03-02 14:02:46</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:58</t>
+          <t>2026-03-02 14:02:46</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-02 13:45:58</t>
+          <t>2026-03-02 14:02:46</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:00</t>
+          <t>2026-03-02 14:02:49</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:01</t>
+          <t>2026-03-02 14:02:51</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:01</t>
+          <t>2026-03-02 14:02:51</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:01</t>
+          <t>2026-03-02 14:02:51</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:01</t>
+          <t>2026-03-02 14:02:51</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:04</t>
+          <t>2026-03-02 14:02:53</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:05</t>
+          <t>2026-03-02 14:02:55</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:05</t>
+          <t>2026-03-02 14:02:55</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:05</t>
+          <t>2026-03-02 14:02:55</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:05</t>
+          <t>2026-03-02 14:02:55</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:07</t>
+          <t>2026-03-02 14:02:57</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:09</t>
+          <t>2026-03-02 14:02:59</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:09</t>
+          <t>2026-03-02 14:02:59</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:09</t>
+          <t>2026-03-02 14:02:59</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:09</t>
+          <t>2026-03-02 14:02:59</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:11</t>
+          <t>2026-03-02 14:03:02</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:13</t>
+          <t>2026-03-02 14:03:04</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:13</t>
+          <t>2026-03-02 14:03:04</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:13</t>
+          <t>2026-03-02 14:03:04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:13</t>
+          <t>2026-03-02 14:03:04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:15</t>
+          <t>2026-03-02 14:03:06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:16</t>
+          <t>2026-03-02 14:03:08</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:16</t>
+          <t>2026-03-02 14:03:08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:16</t>
+          <t>2026-03-02 14:03:08</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:16</t>
+          <t>2026-03-02 14:03:08</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:18</t>
+          <t>2026-03-02 14:03:10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:20</t>
+          <t>2026-03-02 14:03:12</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:20</t>
+          <t>2026-03-02 14:03:12</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:20</t>
+          <t>2026-03-02 14:03:12</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:20</t>
+          <t>2026-03-02 14:03:12</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:22</t>
+          <t>2026-03-02 14:03:15</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:24</t>
+          <t>2026-03-02 14:03:16</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:24</t>
+          <t>2026-03-02 14:03:16</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:24</t>
+          <t>2026-03-02 14:03:16</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:24</t>
+          <t>2026-03-02 14:03:16</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:26</t>
+          <t>2026-03-02 14:03:19</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:27</t>
+          <t>2026-03-02 14:03:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:27</t>
+          <t>2026-03-02 14:03:20</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:27</t>
+          <t>2026-03-02 14:03:20</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:27</t>
+          <t>2026-03-02 14:03:20</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:30</t>
+          <t>2026-03-02 14:03:23</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:31</t>
+          <t>2026-03-02 14:03:24</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:31</t>
+          <t>2026-03-02 14:03:24</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:31</t>
+          <t>2026-03-02 14:03:24</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:31</t>
+          <t>2026-03-02 14:03:24</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:34</t>
+          <t>2026-03-02 14:03:27</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:35</t>
+          <t>2026-03-02 14:03:28</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:35</t>
+          <t>2026-03-02 14:03:28</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:35</t>
+          <t>2026-03-02 14:03:28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:35</t>
+          <t>2026-03-02 14:03:28</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:38</t>
+          <t>2026-03-02 14:03:31</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:39</t>
+          <t>2026-03-02 14:03:33</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:39</t>
+          <t>2026-03-02 14:03:33</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:39</t>
+          <t>2026-03-02 14:03:33</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:39</t>
+          <t>2026-03-02 14:03:33</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22742,17 +22742,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:42</t>
+          <t>2026-03-02 14:03:35</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:43</t>
+          <t>2026-03-02 14:03:37</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:43</t>
+          <t>2026-03-02 14:03:37</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:43</t>
+          <t>2026-03-02 14:03:37</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:43</t>
+          <t>2026-03-02 14:03:37</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23907,17 +23907,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:46</t>
+          <t>2026-03-02 14:03:39</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:47</t>
+          <t>2026-03-02 14:03:41</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:47</t>
+          <t>2026-03-02 14:03:41</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:47</t>
+          <t>2026-03-02 14:03:41</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:47</t>
+          <t>2026-03-02 14:03:41</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25072,17 +25072,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:49</t>
+          <t>2026-03-02 14:03:43</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:51</t>
+          <t>2026-03-02 14:03:45</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:51</t>
+          <t>2026-03-02 14:03:45</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:51</t>
+          <t>2026-03-02 14:03:45</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:51</t>
+          <t>2026-03-02 14:03:45</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26237,17 +26237,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:53</t>
+          <t>2026-03-02 14:03:47</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:54</t>
+          <t>2026-03-02 14:03:49</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:54</t>
+          <t>2026-03-02 14:03:49</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:54</t>
+          <t>2026-03-02 14:03:49</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:54</t>
+          <t>2026-03-02 14:03:49</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,17 +27402,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:57</t>
+          <t>2026-03-02 14:03:51</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:58</t>
+          <t>2026-03-02 14:03:53</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:58</t>
+          <t>2026-03-02 14:03:53</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:58</t>
+          <t>2026-03-02 14:03:53</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-02 13:46:58</t>
+          <t>2026-03-02 14:03:53</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28607,17 +28607,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:01</t>
+          <t>2026-03-02 14:03:56</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:02</t>
+          <t>2026-03-02 14:03:57</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:02</t>
+          <t>2026-03-02 14:03:57</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:02</t>
+          <t>2026-03-02 14:03:57</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:02</t>
+          <t>2026-03-02 14:03:57</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29772,17 +29772,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:05</t>
+          <t>2026-03-02 14:04:00</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:06</t>
+          <t>2026-03-02 14:04:01</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:06</t>
+          <t>2026-03-02 14:04:01</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:06</t>
+          <t>2026-03-02 14:04:01</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:06</t>
+          <t>2026-03-02 14:04:01</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30937,17 +30937,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:08</t>
+          <t>2026-03-02 14:04:04</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:10</t>
+          <t>2026-03-02 14:04:05</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:10</t>
+          <t>2026-03-02 14:04:05</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:10</t>
+          <t>2026-03-02 14:04:05</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:10</t>
+          <t>2026-03-02 14:04:05</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32042,17 +32042,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:12</t>
+          <t>2026-03-02 14:04:08</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:14</t>
+          <t>2026-03-02 14:04:09</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:14</t>
+          <t>2026-03-02 14:04:09</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:14</t>
+          <t>2026-03-02 14:04:09</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:14</t>
+          <t>2026-03-02 14:04:09</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33207,17 +33207,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:16</t>
+          <t>2026-03-02 14:04:12</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:17</t>
+          <t>2026-03-02 14:04:14</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33673,7 +33673,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:17</t>
+          <t>2026-03-02 14:04:14</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33906,7 +33906,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:17</t>
+          <t>2026-03-02 14:04:14</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:17</t>
+          <t>2026-03-02 14:04:14</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34372,17 +34372,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:20</t>
+          <t>2026-03-02 14:04:16</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:21</t>
+          <t>2026-03-02 14:04:18</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:21</t>
+          <t>2026-03-02 14:04:18</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35071,7 +35071,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:21</t>
+          <t>2026-03-02 14:04:18</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35304,7 +35304,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:21</t>
+          <t>2026-03-02 14:04:18</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35537,17 +35537,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:23</t>
+          <t>2026-03-02 14:04:20</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35770,7 +35770,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:25</t>
+          <t>2026-03-02 14:04:22</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:25</t>
+          <t>2026-03-02 14:04:22</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:25</t>
+          <t>2026-03-02 14:04:22</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36469,7 +36469,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:25</t>
+          <t>2026-03-02 14:04:22</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36702,17 +36702,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:27</t>
+          <t>2026-03-02 14:04:24</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:29</t>
+          <t>2026-03-02 14:04:26</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:29</t>
+          <t>2026-03-02 14:04:26</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:29</t>
+          <t>2026-03-02 14:04:26</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37666,7 +37666,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:29</t>
+          <t>2026-03-02 14:04:26</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37907,17 +37907,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:31</t>
+          <t>2026-03-02 14:04:29</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:33</t>
+          <t>2026-03-02 14:04:30</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:33</t>
+          <t>2026-03-02 14:04:30</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:33</t>
+          <t>2026-03-02 14:04:30</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38859,7 +38859,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:33</t>
+          <t>2026-03-02 14:04:30</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39100,17 +39100,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:35</t>
+          <t>2026-03-02 14:04:33</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:36</t>
+          <t>2026-03-02 14:04:34</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:36</t>
+          <t>2026-03-02 14:04:34</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:36</t>
+          <t>2026-03-02 14:04:34</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40032,7 +40032,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:36</t>
+          <t>2026-03-02 14:04:34</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40265,17 +40265,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:39</t>
+          <t>2026-03-02 14:04:37</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:40</t>
+          <t>2026-03-02 14:04:38</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:40</t>
+          <t>2026-03-02 14:04:38</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40928,7 +40928,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:40</t>
+          <t>2026-03-02 14:04:38</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41149,7 +41149,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:40</t>
+          <t>2026-03-02 14:04:38</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41370,17 +41370,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:43</t>
+          <t>2026-03-02 14:04:41</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:44</t>
+          <t>2026-03-02 14:04:42</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41812,7 +41812,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:44</t>
+          <t>2026-03-02 14:04:42</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:44</t>
+          <t>2026-03-02 14:04:42</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:44</t>
+          <t>2026-03-02 14:04:42</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42475,17 +42475,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:47</t>
+          <t>2026-03-02 14:04:45</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:48</t>
+          <t>2026-03-02 14:04:46</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42941,7 +42941,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:48</t>
+          <t>2026-03-02 14:04:46</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43174,7 +43174,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:48</t>
+          <t>2026-03-02 14:04:46</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43407,7 +43407,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:48</t>
+          <t>2026-03-02 14:04:46</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43640,17 +43640,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:50</t>
+          <t>2026-03-02 14:04:48</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43837,7 +43837,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:52</t>
+          <t>2026-03-02 14:04:49</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44034,7 +44034,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:52</t>
+          <t>2026-03-02 14:04:49</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:52</t>
+          <t>2026-03-02 14:04:49</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44428,7 +44428,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:52</t>
+          <t>2026-03-02 14:04:49</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44625,17 +44625,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:54</t>
+          <t>2026-03-02 14:04:52</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44858,7 +44858,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:55</t>
+          <t>2026-03-02 14:04:53</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:55</t>
+          <t>2026-03-02 14:04:53</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:55</t>
+          <t>2026-03-02 14:04:53</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45557,7 +45557,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:55</t>
+          <t>2026-03-02 14:04:53</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45790,17 +45790,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:58</t>
+          <t>2026-03-02 14:04:56</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45963,7 +45963,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:59</t>
+          <t>2026-03-02 14:04:57</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46136,7 +46136,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:59</t>
+          <t>2026-03-02 14:04:57</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:59</t>
+          <t>2026-03-02 14:04:57</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-02 13:47:59</t>
+          <t>2026-03-02 14:04:57</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46655,17 +46655,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:02</t>
+          <t>2026-03-02 14:05:00</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:03</t>
+          <t>2026-03-02 14:05:01</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47097,7 +47097,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:03</t>
+          <t>2026-03-02 14:05:01</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:03</t>
+          <t>2026-03-02 14:05:01</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47539,7 +47539,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:03</t>
+          <t>2026-03-02 14:05:01</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47760,17 +47760,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:05</t>
+          <t>2026-03-02 14:05:04</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -48001,7 +48001,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:07</t>
+          <t>2026-03-02 14:05:06</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48242,7 +48242,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:07</t>
+          <t>2026-03-02 14:05:06</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48483,7 +48483,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:07</t>
+          <t>2026-03-02 14:05:06</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48724,7 +48724,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:07</t>
+          <t>2026-03-02 14:05:06</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48965,17 +48965,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:09</t>
+          <t>2026-03-02 14:05:08</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -49206,7 +49206,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:11</t>
+          <t>2026-03-02 14:05:10</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49447,7 +49447,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:11</t>
+          <t>2026-03-02 14:05:10</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:11</t>
+          <t>2026-03-02 14:05:10</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49929,7 +49929,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:11</t>
+          <t>2026-03-02 14:05:10</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50170,17 +50170,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:13</t>
+          <t>2026-03-02 14:05:12</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50403,7 +50403,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:15</t>
+          <t>2026-03-02 14:05:14</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:15</t>
+          <t>2026-03-02 14:05:14</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50869,7 +50869,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:15</t>
+          <t>2026-03-02 14:05:14</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51102,7 +51102,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-02 13:48:15</t>
+          <t>2026-03-02 14:05:14</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51369,7 +51369,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51399,7 +51399,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51429,7 +51429,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51459,7 +51459,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51489,7 +51489,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51519,7 +51519,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51549,7 +51549,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51609,7 +51609,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51639,7 +51639,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51669,7 +51669,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51699,7 +51699,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51729,7 +51729,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51759,7 +51759,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51789,7 +51789,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51819,7 +51819,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51849,7 +51849,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51879,7 +51879,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51909,7 +51909,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51939,7 +51939,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51969,7 +51969,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -51999,7 +51999,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52029,7 +52029,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52059,7 +52059,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52089,7 +52089,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52119,7 +52119,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52149,7 +52149,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52179,7 +52179,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52209,7 +52209,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52239,7 +52239,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52269,7 +52269,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52299,7 +52299,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52329,7 +52329,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52359,7 +52359,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52389,7 +52389,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52419,7 +52419,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52449,7 +52449,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52479,7 +52479,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52509,7 +52509,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52539,7 +52539,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52569,7 +52569,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52599,7 +52599,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52629,7 +52629,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52659,7 +52659,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>
@@ -52689,7 +52689,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T13:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-02T13:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:27</t>
+          <t>2026-03-02 14:22:17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:29</t>
+          <t>2026-03-02 14:22:18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:29</t>
+          <t>2026-03-02 14:22:18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:29</t>
+          <t>2026-03-02 14:22:18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:29</t>
+          <t>2026-03-02 14:22:18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:31</t>
+          <t>2026-03-02 14:22:21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:33</t>
+          <t>2026-03-02 14:22:22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:33</t>
+          <t>2026-03-02 14:22:22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:33</t>
+          <t>2026-03-02 14:22:22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:33</t>
+          <t>2026-03-02 14:22:22</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:35</t>
+          <t>2026-03-02 14:22:24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:36</t>
+          <t>2026-03-02 14:22:26</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:36</t>
+          <t>2026-03-02 14:22:26</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:36</t>
+          <t>2026-03-02 14:22:26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:36</t>
+          <t>2026-03-02 14:22:26</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:39</t>
+          <t>2026-03-02 14:22:28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:40</t>
+          <t>2026-03-02 14:22:30</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:40</t>
+          <t>2026-03-02 14:22:30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:40</t>
+          <t>2026-03-02 14:22:30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:40</t>
+          <t>2026-03-02 14:22:30</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:43</t>
+          <t>2026-03-02 14:22:32</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:44</t>
+          <t>2026-03-02 14:22:34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:44</t>
+          <t>2026-03-02 14:22:34</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:44</t>
+          <t>2026-03-02 14:22:34</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:44</t>
+          <t>2026-03-02 14:22:34</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:47</t>
+          <t>2026-03-02 14:22:36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:48</t>
+          <t>2026-03-02 14:22:37</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:48</t>
+          <t>2026-03-02 14:22:37</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:48</t>
+          <t>2026-03-02 14:22:37</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:48</t>
+          <t>2026-03-02 14:22:37</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:51</t>
+          <t>2026-03-02 14:22:40</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:52</t>
+          <t>2026-03-02 14:22:41</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:52</t>
+          <t>2026-03-02 14:22:41</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:52</t>
+          <t>2026-03-02 14:22:41</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:52</t>
+          <t>2026-03-02 14:22:41</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:55</t>
+          <t>2026-03-02 14:22:44</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:56</t>
+          <t>2026-03-02 14:22:45</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:56</t>
+          <t>2026-03-02 14:22:45</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:56</t>
+          <t>2026-03-02 14:22:45</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:56</t>
+          <t>2026-03-02 14:22:45</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-02 14:15:59</t>
+          <t>2026-03-02 14:22:47</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:00</t>
+          <t>2026-03-02 14:22:49</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:00</t>
+          <t>2026-03-02 14:22:49</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:00</t>
+          <t>2026-03-02 14:22:49</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:00</t>
+          <t>2026-03-02 14:22:49</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:03</t>
+          <t>2026-03-02 14:22:51</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:04</t>
+          <t>2026-03-02 14:22:53</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:04</t>
+          <t>2026-03-02 14:22:53</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:04</t>
+          <t>2026-03-02 14:22:53</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:04</t>
+          <t>2026-03-02 14:22:53</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:06</t>
+          <t>2026-03-02 14:22:55</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:08</t>
+          <t>2026-03-02 14:22:56</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:08</t>
+          <t>2026-03-02 14:22:56</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:08</t>
+          <t>2026-03-02 14:22:56</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:08</t>
+          <t>2026-03-02 14:22:56</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:10</t>
+          <t>2026-03-02 14:22:59</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:12</t>
+          <t>2026-03-02 14:23:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:12</t>
+          <t>2026-03-02 14:23:00</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:12</t>
+          <t>2026-03-02 14:23:00</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:12</t>
+          <t>2026-03-02 14:23:00</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:14</t>
+          <t>2026-03-02 14:23:02</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:16</t>
+          <t>2026-03-02 14:23:04</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:16</t>
+          <t>2026-03-02 14:23:04</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:16</t>
+          <t>2026-03-02 14:23:04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:16</t>
+          <t>2026-03-02 14:23:04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:18</t>
+          <t>2026-03-02 14:23:06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:19</t>
+          <t>2026-03-02 14:23:07</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:19</t>
+          <t>2026-03-02 14:23:07</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:19</t>
+          <t>2026-03-02 14:23:07</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:19</t>
+          <t>2026-03-02 14:23:07</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:21</t>
+          <t>2026-03-02 14:23:10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:23</t>
+          <t>2026-03-02 14:23:11</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:23</t>
+          <t>2026-03-02 14:23:11</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:23</t>
+          <t>2026-03-02 14:23:11</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:23</t>
+          <t>2026-03-02 14:23:11</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:25</t>
+          <t>2026-03-02 14:23:14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:27</t>
+          <t>2026-03-02 14:23:15</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:27</t>
+          <t>2026-03-02 14:23:15</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:27</t>
+          <t>2026-03-02 14:23:15</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:27</t>
+          <t>2026-03-02 14:23:15</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:29</t>
+          <t>2026-03-02 14:23:17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:31</t>
+          <t>2026-03-02 14:23:19</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:31</t>
+          <t>2026-03-02 14:23:19</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:31</t>
+          <t>2026-03-02 14:23:19</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:31</t>
+          <t>2026-03-02 14:23:19</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:33</t>
+          <t>2026-03-02 14:23:21</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:35</t>
+          <t>2026-03-02 14:23:22</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:35</t>
+          <t>2026-03-02 14:23:22</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:35</t>
+          <t>2026-03-02 14:23:22</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:35</t>
+          <t>2026-03-02 14:23:22</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:37</t>
+          <t>2026-03-02 14:23:25</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:39</t>
+          <t>2026-03-02 14:23:26</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:39</t>
+          <t>2026-03-02 14:23:26</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:39</t>
+          <t>2026-03-02 14:23:26</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:39</t>
+          <t>2026-03-02 14:23:26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:41</t>
+          <t>2026-03-02 14:23:29</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:43</t>
+          <t>2026-03-02 14:23:30</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:43</t>
+          <t>2026-03-02 14:23:30</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:43</t>
+          <t>2026-03-02 14:23:30</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:43</t>
+          <t>2026-03-02 14:23:30</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:45</t>
+          <t>2026-03-02 14:23:33</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:46</t>
+          <t>2026-03-02 14:23:34</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:46</t>
+          <t>2026-03-02 14:23:34</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:46</t>
+          <t>2026-03-02 14:23:34</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:46</t>
+          <t>2026-03-02 14:23:34</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:49</t>
+          <t>2026-03-02 14:23:37</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:51</t>
+          <t>2026-03-02 14:23:38</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:51</t>
+          <t>2026-03-02 14:23:38</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:51</t>
+          <t>2026-03-02 14:23:38</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:51</t>
+          <t>2026-03-02 14:23:38</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:53</t>
+          <t>2026-03-02 14:23:41</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:54</t>
+          <t>2026-03-02 14:23:42</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:54</t>
+          <t>2026-03-02 14:23:42</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:54</t>
+          <t>2026-03-02 14:23:42</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:54</t>
+          <t>2026-03-02 14:23:42</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:57</t>
+          <t>2026-03-02 14:23:44</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:58</t>
+          <t>2026-03-02 14:23:46</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:58</t>
+          <t>2026-03-02 14:23:46</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:58</t>
+          <t>2026-03-02 14:23:46</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-02 14:16:58</t>
+          <t>2026-03-02 14:23:46</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:01</t>
+          <t>2026-03-02 14:23:48</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:03</t>
+          <t>2026-03-02 14:23:50</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:03</t>
+          <t>2026-03-02 14:23:50</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:03</t>
+          <t>2026-03-02 14:23:50</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:03</t>
+          <t>2026-03-02 14:23:50</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28607,7 +28607,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:05</t>
+          <t>2026-03-02 14:23:52</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:06</t>
+          <t>2026-03-02 14:23:53</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:06</t>
+          <t>2026-03-02 14:23:53</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:06</t>
+          <t>2026-03-02 14:23:53</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:06</t>
+          <t>2026-03-02 14:23:53</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:09</t>
+          <t>2026-03-02 14:23:56</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:10</t>
+          <t>2026-03-02 14:23:57</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:10</t>
+          <t>2026-03-02 14:23:57</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:10</t>
+          <t>2026-03-02 14:23:57</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:10</t>
+          <t>2026-03-02 14:23:57</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30937,7 +30937,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:13</t>
+          <t>2026-03-02 14:24:00</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:14</t>
+          <t>2026-03-02 14:24:01</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:14</t>
+          <t>2026-03-02 14:24:01</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:14</t>
+          <t>2026-03-02 14:24:01</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:14</t>
+          <t>2026-03-02 14:24:01</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32042,7 +32042,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:17</t>
+          <t>2026-03-02 14:24:03</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:18</t>
+          <t>2026-03-02 14:24:05</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:18</t>
+          <t>2026-03-02 14:24:05</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:18</t>
+          <t>2026-03-02 14:24:05</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:18</t>
+          <t>2026-03-02 14:24:05</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33207,7 +33207,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:21</t>
+          <t>2026-03-02 14:24:07</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:22</t>
+          <t>2026-03-02 14:24:09</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33673,7 +33673,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:22</t>
+          <t>2026-03-02 14:24:09</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33906,7 +33906,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:22</t>
+          <t>2026-03-02 14:24:09</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:22</t>
+          <t>2026-03-02 14:24:09</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34372,7 +34372,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:25</t>
+          <t>2026-03-02 14:24:11</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:26</t>
+          <t>2026-03-02 14:24:13</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:26</t>
+          <t>2026-03-02 14:24:13</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35071,7 +35071,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:26</t>
+          <t>2026-03-02 14:24:13</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35304,7 +35304,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:26</t>
+          <t>2026-03-02 14:24:13</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35537,7 +35537,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:29</t>
+          <t>2026-03-02 14:24:15</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35770,7 +35770,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:30</t>
+          <t>2026-03-02 14:24:16</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:30</t>
+          <t>2026-03-02 14:24:16</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:30</t>
+          <t>2026-03-02 14:24:16</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36469,7 +36469,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:30</t>
+          <t>2026-03-02 14:24:16</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36702,7 +36702,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:33</t>
+          <t>2026-03-02 14:24:19</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:34</t>
+          <t>2026-03-02 14:24:20</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:34</t>
+          <t>2026-03-02 14:24:20</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:34</t>
+          <t>2026-03-02 14:24:20</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37666,7 +37666,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:34</t>
+          <t>2026-03-02 14:24:20</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37907,7 +37907,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:37</t>
+          <t>2026-03-02 14:24:22</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -38136,7 +38136,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:38</t>
+          <t>2026-03-02 14:24:24</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:38</t>
+          <t>2026-03-02 14:24:24</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:38</t>
+          <t>2026-03-02 14:24:24</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38859,7 +38859,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:38</t>
+          <t>2026-03-02 14:24:24</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:41</t>
+          <t>2026-03-02 14:24:26</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:42</t>
+          <t>2026-03-02 14:24:28</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:42</t>
+          <t>2026-03-02 14:24:28</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39799,7 +39799,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:42</t>
+          <t>2026-03-02 14:24:28</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40032,7 +40032,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:42</t>
+          <t>2026-03-02 14:24:28</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40265,7 +40265,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:45</t>
+          <t>2026-03-02 14:24:30</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:46</t>
+          <t>2026-03-02 14:24:32</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40707,7 +40707,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:46</t>
+          <t>2026-03-02 14:24:32</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40928,7 +40928,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:46</t>
+          <t>2026-03-02 14:24:32</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41149,7 +41149,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:46</t>
+          <t>2026-03-02 14:24:32</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41370,7 +41370,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:49</t>
+          <t>2026-03-02 14:24:34</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41591,7 +41591,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:50</t>
+          <t>2026-03-02 14:24:35</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41812,7 +41812,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:50</t>
+          <t>2026-03-02 14:24:35</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:50</t>
+          <t>2026-03-02 14:24:35</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:50</t>
+          <t>2026-03-02 14:24:35</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42475,7 +42475,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:53</t>
+          <t>2026-03-02 14:24:38</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:54</t>
+          <t>2026-03-02 14:24:39</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42941,7 +42941,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:54</t>
+          <t>2026-03-02 14:24:39</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43174,7 +43174,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:54</t>
+          <t>2026-03-02 14:24:39</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43407,7 +43407,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:54</t>
+          <t>2026-03-02 14:24:39</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43640,7 +43640,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:56</t>
+          <t>2026-03-02 14:24:41</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43837,7 +43837,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:58</t>
+          <t>2026-03-02 14:24:43</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44034,7 +44034,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:58</t>
+          <t>2026-03-02 14:24:43</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:58</t>
+          <t>2026-03-02 14:24:43</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44428,7 +44428,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-02 14:17:58</t>
+          <t>2026-03-02 14:24:43</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44625,7 +44625,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:00</t>
+          <t>2026-03-02 14:24:45</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44858,7 +44858,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:02</t>
+          <t>2026-03-02 14:24:47</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45091,7 +45091,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:02</t>
+          <t>2026-03-02 14:24:47</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:02</t>
+          <t>2026-03-02 14:24:47</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45557,7 +45557,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:02</t>
+          <t>2026-03-02 14:24:47</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45790,7 +45790,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:04</t>
+          <t>2026-03-02 14:24:49</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45963,7 +45963,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:05</t>
+          <t>2026-03-02 14:24:50</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46136,7 +46136,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:05</t>
+          <t>2026-03-02 14:24:50</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46309,7 +46309,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:05</t>
+          <t>2026-03-02 14:24:50</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:05</t>
+          <t>2026-03-02 14:24:50</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46655,7 +46655,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:07</t>
+          <t>2026-03-02 14:24:53</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46876,7 +46876,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:09</t>
+          <t>2026-03-02 14:24:54</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47097,7 +47097,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:09</t>
+          <t>2026-03-02 14:24:54</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47318,7 +47318,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:09</t>
+          <t>2026-03-02 14:24:54</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47539,7 +47539,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:09</t>
+          <t>2026-03-02 14:24:54</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47760,7 +47760,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:11</t>
+          <t>2026-03-02 14:24:56</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -48001,7 +48001,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:13</t>
+          <t>2026-03-02 14:24:58</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48242,7 +48242,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:13</t>
+          <t>2026-03-02 14:24:58</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48483,7 +48483,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:13</t>
+          <t>2026-03-02 14:24:58</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48724,7 +48724,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:13</t>
+          <t>2026-03-02 14:24:58</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48965,7 +48965,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:16</t>
+          <t>2026-03-02 14:25:00</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49206,7 +49206,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:17</t>
+          <t>2026-03-02 14:25:02</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49447,7 +49447,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:17</t>
+          <t>2026-03-02 14:25:02</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49688,7 +49688,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:17</t>
+          <t>2026-03-02 14:25:02</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49929,7 +49929,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:17</t>
+          <t>2026-03-02 14:25:02</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50170,7 +50170,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:19</t>
+          <t>2026-03-02 14:25:04</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -50403,7 +50403,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:21</t>
+          <t>2026-03-02 14:25:05</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:21</t>
+          <t>2026-03-02 14:25:05</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50869,7 +50869,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:21</t>
+          <t>2026-03-02 14:25:05</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51102,7 +51102,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-02 14:18:21</t>
+          <t>2026-03-02 14:25:05</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:27</t>
+          <t>2026-03-03 08:58:09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:28</t>
+          <t>2026-03-03 08:58:10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:28</t>
+          <t>2026-03-03 08:58:10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:28</t>
+          <t>2026-03-03 08:58:10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:28</t>
+          <t>2026-03-03 08:58:10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:31</t>
+          <t>2026-03-03 08:58:13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:32</t>
+          <t>2026-03-03 08:58:15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:32</t>
+          <t>2026-03-03 08:58:15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:32</t>
+          <t>2026-03-03 08:58:15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:32</t>
+          <t>2026-03-03 08:58:15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:35</t>
+          <t>2026-03-03 08:58:18</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:36</t>
+          <t>2026-03-03 08:58:20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:36</t>
+          <t>2026-03-03 08:58:20</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:36</t>
+          <t>2026-03-03 08:58:20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:36</t>
+          <t>2026-03-03 08:58:20</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:38</t>
+          <t>2026-03-03 08:58:22</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:40</t>
+          <t>2026-03-03 08:58:24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:40</t>
+          <t>2026-03-03 08:58:24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:40</t>
+          <t>2026-03-03 08:58:24</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:40</t>
+          <t>2026-03-03 08:58:24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:42</t>
+          <t>2026-03-03 08:58:27</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:44</t>
+          <t>2026-03-03 08:58:28</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:44</t>
+          <t>2026-03-03 08:58:28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:44</t>
+          <t>2026-03-03 08:58:28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:44</t>
+          <t>2026-03-03 08:58:28</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:46</t>
+          <t>2026-03-03 08:58:31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:48</t>
+          <t>2026-03-03 08:58:33</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:48</t>
+          <t>2026-03-03 08:58:33</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:48</t>
+          <t>2026-03-03 08:58:33</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:48</t>
+          <t>2026-03-03 08:58:33</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:50</t>
+          <t>2026-03-03 08:58:36</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:52</t>
+          <t>2026-03-03 08:58:38</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:52</t>
+          <t>2026-03-03 08:58:38</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:52</t>
+          <t>2026-03-03 08:58:38</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:52</t>
+          <t>2026-03-03 08:58:38</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:54</t>
+          <t>2026-03-03 08:58:40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:55</t>
+          <t>2026-03-03 08:58:42</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:55</t>
+          <t>2026-03-03 08:58:42</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:55</t>
+          <t>2026-03-03 08:58:42</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:55</t>
+          <t>2026-03-03 08:58:42</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:58</t>
+          <t>2026-03-03 08:58:44</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:59</t>
+          <t>2026-03-03 08:58:46</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:59</t>
+          <t>2026-03-03 08:58:46</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:59</t>
+          <t>2026-03-03 08:58:46</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-03 08:45:59</t>
+          <t>2026-03-03 08:58:46</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:01</t>
+          <t>2026-03-03 08:58:48</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:03</t>
+          <t>2026-03-03 08:58:50</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:03</t>
+          <t>2026-03-03 08:58:50</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:03</t>
+          <t>2026-03-03 08:58:50</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:03</t>
+          <t>2026-03-03 08:58:50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:05</t>
+          <t>2026-03-03 08:58:53</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:06</t>
+          <t>2026-03-03 08:58:54</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:06</t>
+          <t>2026-03-03 08:58:54</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:06</t>
+          <t>2026-03-03 08:58:54</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:06</t>
+          <t>2026-03-03 08:58:54</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:09</t>
+          <t>2026-03-03 08:58:57</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:10</t>
+          <t>2026-03-03 08:58:59</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:10</t>
+          <t>2026-03-03 08:58:59</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:10</t>
+          <t>2026-03-03 08:58:59</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:10</t>
+          <t>2026-03-03 08:58:59</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:12</t>
+          <t>2026-03-03 08:59:02</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:14</t>
+          <t>2026-03-03 08:59:04</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:14</t>
+          <t>2026-03-03 08:59:04</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:14</t>
+          <t>2026-03-03 08:59:04</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:14</t>
+          <t>2026-03-03 08:59:04</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:16</t>
+          <t>2026-03-03 08:59:06</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:17</t>
+          <t>2026-03-03 08:59:08</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:17</t>
+          <t>2026-03-03 08:59:08</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:17</t>
+          <t>2026-03-03 08:59:08</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:17</t>
+          <t>2026-03-03 08:59:08</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:20</t>
+          <t>2026-03-03 08:59:11</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:21</t>
+          <t>2026-03-03 08:59:13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:21</t>
+          <t>2026-03-03 08:59:13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:21</t>
+          <t>2026-03-03 08:59:13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:21</t>
+          <t>2026-03-03 08:59:13</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:24</t>
+          <t>2026-03-03 08:59:15</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:25</t>
+          <t>2026-03-03 08:59:17</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:25</t>
+          <t>2026-03-03 08:59:17</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:25</t>
+          <t>2026-03-03 08:59:17</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:25</t>
+          <t>2026-03-03 08:59:17</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:28</t>
+          <t>2026-03-03 08:59:19</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:29</t>
+          <t>2026-03-03 08:59:21</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:29</t>
+          <t>2026-03-03 08:59:21</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:29</t>
+          <t>2026-03-03 08:59:21</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:29</t>
+          <t>2026-03-03 08:59:21</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:31</t>
+          <t>2026-03-03 08:59:23</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:33</t>
+          <t>2026-03-03 08:59:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:33</t>
+          <t>2026-03-03 08:59:25</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:33</t>
+          <t>2026-03-03 08:59:25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:33</t>
+          <t>2026-03-03 08:59:25</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:35</t>
+          <t>2026-03-03 08:59:28</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:37</t>
+          <t>2026-03-03 08:59:30</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:37</t>
+          <t>2026-03-03 08:59:30</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:37</t>
+          <t>2026-03-03 08:59:30</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:37</t>
+          <t>2026-03-03 08:59:30</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:39</t>
+          <t>2026-03-03 08:59:32</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:41</t>
+          <t>2026-03-03 08:59:34</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:41</t>
+          <t>2026-03-03 08:59:34</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:41</t>
+          <t>2026-03-03 08:59:34</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:41</t>
+          <t>2026-03-03 08:59:34</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:43</t>
+          <t>2026-03-03 08:59:37</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:44</t>
+          <t>2026-03-03 08:59:38</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:44</t>
+          <t>2026-03-03 08:59:38</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:44</t>
+          <t>2026-03-03 08:59:38</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:44</t>
+          <t>2026-03-03 08:59:38</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:47</t>
+          <t>2026-03-03 08:59:41</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:49</t>
+          <t>2026-03-03 08:59:43</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:49</t>
+          <t>2026-03-03 08:59:43</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:49</t>
+          <t>2026-03-03 08:59:43</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:49</t>
+          <t>2026-03-03 08:59:43</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:51</t>
+          <t>2026-03-03 08:59:45</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:52</t>
+          <t>2026-03-03 08:59:47</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:52</t>
+          <t>2026-03-03 08:59:47</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:52</t>
+          <t>2026-03-03 08:59:47</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:52</t>
+          <t>2026-03-03 08:59:47</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:55</t>
+          <t>2026-03-03 08:59:50</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:56</t>
+          <t>2026-03-03 08:59:52</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:56</t>
+          <t>2026-03-03 08:59:52</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:56</t>
+          <t>2026-03-03 08:59:52</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:56</t>
+          <t>2026-03-03 08:59:52</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-03 08:46:59</t>
+          <t>2026-03-03 08:59:54</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:00</t>
+          <t>2026-03-03 08:59:56</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:00</t>
+          <t>2026-03-03 08:59:56</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28089,7 +28089,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:00</t>
+          <t>2026-03-03 08:59:56</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28330,7 +28330,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:00</t>
+          <t>2026-03-03 08:59:56</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28559,7 +28559,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:03</t>
+          <t>2026-03-03 08:59:59</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28780,7 +28780,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:04</t>
+          <t>2026-03-03 09:00:00</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:04</t>
+          <t>2026-03-03 09:00:00</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29246,7 +29246,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:04</t>
+          <t>2026-03-03 09:00:00</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29479,7 +29479,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:04</t>
+          <t>2026-03-03 09:00:00</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29712,17 +29712,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:07</t>
+          <t>2026-03-03 09:00:03</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29945,7 +29945,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:08</t>
+          <t>2026-03-03 09:00:05</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:08</t>
+          <t>2026-03-03 09:00:05</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30411,7 +30411,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:08</t>
+          <t>2026-03-03 09:00:05</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30644,7 +30644,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:08</t>
+          <t>2026-03-03 09:00:05</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30877,17 +30877,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:11</t>
+          <t>2026-03-03 09:00:08</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31098,7 +31098,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:12</t>
+          <t>2026-03-03 09:00:09</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:12</t>
+          <t>2026-03-03 09:00:09</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:12</t>
+          <t>2026-03-03 09:00:09</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31761,7 +31761,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:12</t>
+          <t>2026-03-03 09:00:09</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31982,17 +31982,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:15</t>
+          <t>2026-03-03 09:00:12</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32215,7 +32215,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:16</t>
+          <t>2026-03-03 09:00:14</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32448,7 +32448,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:16</t>
+          <t>2026-03-03 09:00:14</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32681,7 +32681,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:16</t>
+          <t>2026-03-03 09:00:14</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:16</t>
+          <t>2026-03-03 09:00:14</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33147,17 +33147,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:19</t>
+          <t>2026-03-03 09:00:17</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33380,7 +33380,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:20</t>
+          <t>2026-03-03 09:00:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33613,7 +33613,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:20</t>
+          <t>2026-03-03 09:00:19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33846,7 +33846,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:20</t>
+          <t>2026-03-03 09:00:19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34079,7 +34079,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:20</t>
+          <t>2026-03-03 09:00:19</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34312,17 +34312,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:23</t>
+          <t>2026-03-03 09:00:21</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34545,7 +34545,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:24</t>
+          <t>2026-03-03 09:00:23</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:24</t>
+          <t>2026-03-03 09:00:23</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35011,7 +35011,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:24</t>
+          <t>2026-03-03 09:00:23</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35244,7 +35244,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:24</t>
+          <t>2026-03-03 09:00:23</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35477,17 +35477,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:27</t>
+          <t>2026-03-03 09:00:26</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35710,7 +35710,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:28</t>
+          <t>2026-03-03 09:00:28</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35943,7 +35943,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:28</t>
+          <t>2026-03-03 09:00:28</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36176,7 +36176,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:28</t>
+          <t>2026-03-03 09:00:28</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36409,7 +36409,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:28</t>
+          <t>2026-03-03 09:00:28</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36642,17 +36642,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:31</t>
+          <t>2026-03-03 09:00:30</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:32</t>
+          <t>2026-03-03 09:00:32</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37124,7 +37124,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:32</t>
+          <t>2026-03-03 09:00:32</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37365,7 +37365,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:32</t>
+          <t>2026-03-03 09:00:32</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:32</t>
+          <t>2026-03-03 09:00:32</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37847,17 +37847,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:35</t>
+          <t>2026-03-03 09:00:35</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -38088,7 +38088,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:36</t>
+          <t>2026-03-03 09:00:37</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38317,7 +38317,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:36</t>
+          <t>2026-03-03 09:00:37</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38546,7 +38546,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:36</t>
+          <t>2026-03-03 09:00:37</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38775,7 +38775,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:36</t>
+          <t>2026-03-03 09:00:37</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39004,17 +39004,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:39</t>
+          <t>2026-03-03 09:00:39</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39237,7 +39237,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:40</t>
+          <t>2026-03-03 09:00:40</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39470,7 +39470,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:40</t>
+          <t>2026-03-03 09:00:40</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39703,7 +39703,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:40</t>
+          <t>2026-03-03 09:00:40</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39936,7 +39936,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:40</t>
+          <t>2026-03-03 09:00:40</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40169,17 +40169,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:42</t>
+          <t>2026-03-03 09:00:43</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40390,7 +40390,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:44</t>
+          <t>2026-03-03 09:00:45</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40611,7 +40611,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:44</t>
+          <t>2026-03-03 09:00:45</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40832,7 +40832,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:44</t>
+          <t>2026-03-03 09:00:45</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:44</t>
+          <t>2026-03-03 09:00:45</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41274,17 +41274,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:46</t>
+          <t>2026-03-03 09:00:48</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41495,7 +41495,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:48</t>
+          <t>2026-03-03 09:00:50</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41716,7 +41716,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:48</t>
+          <t>2026-03-03 09:00:50</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41937,7 +41937,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:48</t>
+          <t>2026-03-03 09:00:50</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42158,7 +42158,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-03 08:47:48</t>
+          <t>2026-03-03 09:00:50</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42379,7 +42379,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:00</t>
+          <t>2026-03-03 09:01:03</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42612,7 +42612,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:00</t>
+          <t>2026-03-03 09:01:03</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42845,7 +42845,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:00</t>
+          <t>2026-03-03 09:01:03</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43078,7 +43078,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:00</t>
+          <t>2026-03-03 09:01:03</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43311,17 +43311,17 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:03</t>
+          <t>2026-03-03 09:01:06</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:04</t>
+          <t>2026-03-03 09:01:08</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43705,7 +43705,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:04</t>
+          <t>2026-03-03 09:01:08</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43902,7 +43902,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:04</t>
+          <t>2026-03-03 09:01:08</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44099,7 +44099,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:04</t>
+          <t>2026-03-03 09:01:08</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44296,17 +44296,17 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:07</t>
+          <t>2026-03-03 09:01:10</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K196" t="n">
@@ -44529,7 +44529,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:08</t>
+          <t>2026-03-03 09:01:12</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44762,7 +44762,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:08</t>
+          <t>2026-03-03 09:01:12</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:08</t>
+          <t>2026-03-03 09:01:12</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:08</t>
+          <t>2026-03-03 09:01:12</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45461,17 +45461,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:11</t>
+          <t>2026-03-03 09:01:14</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K201" t="n">
@@ -45634,7 +45634,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:12</t>
+          <t>2026-03-03 09:01:16</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45807,7 +45807,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:12</t>
+          <t>2026-03-03 09:01:16</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45980,7 +45980,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:12</t>
+          <t>2026-03-03 09:01:16</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46153,7 +46153,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:12</t>
+          <t>2026-03-03 09:01:16</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46326,17 +46326,17 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:14</t>
+          <t>2026-03-03 09:01:18</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K206" t="n">
@@ -46547,7 +46547,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:16</t>
+          <t>2026-03-03 09:01:20</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46768,7 +46768,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:16</t>
+          <t>2026-03-03 09:01:20</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46989,7 +46989,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:16</t>
+          <t>2026-03-03 09:01:20</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47210,7 +47210,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:16</t>
+          <t>2026-03-03 09:01:20</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47431,17 +47431,17 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:18</t>
+          <t>2026-03-03 09:01:23</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -47672,7 +47672,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:20</t>
+          <t>2026-03-03 09:01:25</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -47913,7 +47913,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:20</t>
+          <t>2026-03-03 09:01:25</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48154,7 +48154,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:20</t>
+          <t>2026-03-03 09:01:25</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48395,7 +48395,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:20</t>
+          <t>2026-03-03 09:01:25</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48636,17 +48636,17 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:22</t>
+          <t>2026-03-03 09:01:28</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K216" t="n">
@@ -48877,7 +48877,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:24</t>
+          <t>2026-03-03 09:01:29</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49118,7 +49118,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:24</t>
+          <t>2026-03-03 09:01:29</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49359,7 +49359,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:24</t>
+          <t>2026-03-03 09:01:29</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49600,7 +49600,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:24</t>
+          <t>2026-03-03 09:01:29</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49841,17 +49841,17 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:26</t>
+          <t>2026-03-03 09:01:32</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
       <c r="K221" t="n">
@@ -50074,7 +50074,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:28</t>
+          <t>2026-03-03 09:01:34</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -50307,7 +50307,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:28</t>
+          <t>2026-03-03 09:01:34</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50540,7 +50540,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:28</t>
+          <t>2026-03-03 09:01:34</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50773,7 +50773,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-03 08:48:28</t>
+          <t>2026-03-03 09:01:34</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51820,7 +51820,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51850,7 +51850,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51880,7 +51880,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51910,7 +51910,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51940,7 +51940,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -51970,7 +51970,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52000,7 +52000,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52030,7 +52030,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52060,7 +52060,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52090,7 +52090,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52120,7 +52120,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52180,7 +52180,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52210,7 +52210,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52240,7 +52240,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52270,7 +52270,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52300,7 +52300,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52330,7 +52330,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>
@@ -52360,7 +52360,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-03T08:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-03T08:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:50</t>
+          <t>2026-03-03 09:15:33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:51</t>
+          <t>2026-03-03 09:15:34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:51</t>
+          <t>2026-03-03 09:15:34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:51</t>
+          <t>2026-03-03 09:15:34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:51</t>
+          <t>2026-03-03 09:15:34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:54</t>
+          <t>2026-03-03 09:15:37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:55</t>
+          <t>2026-03-03 09:15:38</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:55</t>
+          <t>2026-03-03 09:15:38</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:55</t>
+          <t>2026-03-03 09:15:38</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:55</t>
+          <t>2026-03-03 09:15:38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03 09:09:58</t>
+          <t>2026-03-03 09:15:41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:00</t>
+          <t>2026-03-03 09:15:42</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:00</t>
+          <t>2026-03-03 09:15:42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:00</t>
+          <t>2026-03-03 09:15:42</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:00</t>
+          <t>2026-03-03 09:15:42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:02</t>
+          <t>2026-03-03 09:15:45</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:04</t>
+          <t>2026-03-03 09:15:47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:04</t>
+          <t>2026-03-03 09:15:47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:04</t>
+          <t>2026-03-03 09:15:47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:04</t>
+          <t>2026-03-03 09:15:47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:06</t>
+          <t>2026-03-03 09:15:49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:08</t>
+          <t>2026-03-03 09:15:50</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:08</t>
+          <t>2026-03-03 09:15:50</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:08</t>
+          <t>2026-03-03 09:15:50</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:08</t>
+          <t>2026-03-03 09:15:50</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:11</t>
+          <t>2026-03-03 09:15:53</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:12</t>
+          <t>2026-03-03 09:15:54</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:12</t>
+          <t>2026-03-03 09:15:54</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:12</t>
+          <t>2026-03-03 09:15:54</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:12</t>
+          <t>2026-03-03 09:15:54</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:15</t>
+          <t>2026-03-03 09:15:57</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:16</t>
+          <t>2026-03-03 09:15:58</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:16</t>
+          <t>2026-03-03 09:15:58</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:16</t>
+          <t>2026-03-03 09:15:58</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:16</t>
+          <t>2026-03-03 09:15:58</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:19</t>
+          <t>2026-03-03 09:16:01</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:20</t>
+          <t>2026-03-03 09:16:02</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:20</t>
+          <t>2026-03-03 09:16:02</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:20</t>
+          <t>2026-03-03 09:16:02</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:20</t>
+          <t>2026-03-03 09:16:02</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:22</t>
+          <t>2026-03-03 09:16:05</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:24</t>
+          <t>2026-03-03 09:16:06</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:24</t>
+          <t>2026-03-03 09:16:06</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:24</t>
+          <t>2026-03-03 09:16:06</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:24</t>
+          <t>2026-03-03 09:16:06</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:26</t>
+          <t>2026-03-03 09:16:09</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:28</t>
+          <t>2026-03-03 09:16:10</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:28</t>
+          <t>2026-03-03 09:16:10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:28</t>
+          <t>2026-03-03 09:16:10</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:28</t>
+          <t>2026-03-03 09:16:10</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:31</t>
+          <t>2026-03-03 09:16:13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:32</t>
+          <t>2026-03-03 09:16:14</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:32</t>
+          <t>2026-03-03 09:16:14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:32</t>
+          <t>2026-03-03 09:16:14</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:32</t>
+          <t>2026-03-03 09:16:14</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:35</t>
+          <t>2026-03-03 09:16:17</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:36</t>
+          <t>2026-03-03 09:16:18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:36</t>
+          <t>2026-03-03 09:16:18</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:36</t>
+          <t>2026-03-03 09:16:18</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:36</t>
+          <t>2026-03-03 09:16:18</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:39</t>
+          <t>2026-03-03 09:16:20</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14135,7 +14135,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:40</t>
+          <t>2026-03-03 09:16:22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:40</t>
+          <t>2026-03-03 09:16:22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:40</t>
+          <t>2026-03-03 09:16:22</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14654,7 +14654,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:40</t>
+          <t>2026-03-03 09:16:22</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:43</t>
+          <t>2026-03-03 09:16:24</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:45</t>
+          <t>2026-03-03 09:16:26</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:45</t>
+          <t>2026-03-03 09:16:26</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15526,7 +15526,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:45</t>
+          <t>2026-03-03 09:16:26</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:45</t>
+          <t>2026-03-03 09:16:26</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:48</t>
+          <t>2026-03-03 09:16:28</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16225,7 +16225,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:49</t>
+          <t>2026-03-03 09:16:30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16458,7 +16458,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:49</t>
+          <t>2026-03-03 09:16:30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:49</t>
+          <t>2026-03-03 09:16:30</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16924,7 +16924,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:49</t>
+          <t>2026-03-03 09:16:30</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:52</t>
+          <t>2026-03-03 09:16:32</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17390,7 +17390,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:54</t>
+          <t>2026-03-03 09:16:33</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:54</t>
+          <t>2026-03-03 09:16:33</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17856,7 +17856,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:54</t>
+          <t>2026-03-03 09:16:33</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:54</t>
+          <t>2026-03-03 09:16:33</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:56</t>
+          <t>2026-03-03 09:16:35</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:58</t>
+          <t>2026-03-03 09:16:37</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:58</t>
+          <t>2026-03-03 09:16:37</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:58</t>
+          <t>2026-03-03 09:16:37</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19206,7 +19206,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-03 09:10:58</t>
+          <t>2026-03-03 09:16:37</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19427,7 +19427,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:01</t>
+          <t>2026-03-03 09:16:39</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:03</t>
+          <t>2026-03-03 09:16:41</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19893,7 +19893,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:03</t>
+          <t>2026-03-03 09:16:41</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:03</t>
+          <t>2026-03-03 09:16:41</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:03</t>
+          <t>2026-03-03 09:16:41</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:05</t>
+          <t>2026-03-03 09:16:43</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20825,7 +20825,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:07</t>
+          <t>2026-03-03 09:16:45</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:07</t>
+          <t>2026-03-03 09:16:45</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:07</t>
+          <t>2026-03-03 09:16:45</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:07</t>
+          <t>2026-03-03 09:16:45</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:10</t>
+          <t>2026-03-03 09:16:47</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21990,7 +21990,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:11</t>
+          <t>2026-03-03 09:16:49</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:11</t>
+          <t>2026-03-03 09:16:49</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22456,7 +22456,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:11</t>
+          <t>2026-03-03 09:16:49</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22689,7 +22689,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:11</t>
+          <t>2026-03-03 09:16:49</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22922,7 +22922,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:14</t>
+          <t>2026-03-03 09:16:51</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -23155,7 +23155,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:16</t>
+          <t>2026-03-03 09:16:53</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:16</t>
+          <t>2026-03-03 09:16:53</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23621,7 +23621,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:16</t>
+          <t>2026-03-03 09:16:53</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:16</t>
+          <t>2026-03-03 09:16:53</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -24087,7 +24087,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:18</t>
+          <t>2026-03-03 09:16:55</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:20</t>
+          <t>2026-03-03 09:16:57</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24553,7 +24553,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:20</t>
+          <t>2026-03-03 09:16:57</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24786,7 +24786,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:20</t>
+          <t>2026-03-03 09:16:57</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -25019,7 +25019,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:20</t>
+          <t>2026-03-03 09:16:57</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:23</t>
+          <t>2026-03-03 09:16:59</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25485,7 +25485,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:24</t>
+          <t>2026-03-03 09:17:01</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25718,7 +25718,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:24</t>
+          <t>2026-03-03 09:17:01</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25951,7 +25951,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:24</t>
+          <t>2026-03-03 09:17:01</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26184,7 +26184,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:24</t>
+          <t>2026-03-03 09:17:01</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:27</t>
+          <t>2026-03-03 09:17:03</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:29</t>
+          <t>2026-03-03 09:17:04</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26875,7 +26875,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:29</t>
+          <t>2026-03-03 09:17:04</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:29</t>
+          <t>2026-03-03 09:17:04</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27345,7 +27345,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:29</t>
+          <t>2026-03-03 09:17:04</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27574,7 +27574,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:32</t>
+          <t>2026-03-03 09:17:07</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27795,7 +27795,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:33</t>
+          <t>2026-03-03 09:17:08</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:33</t>
+          <t>2026-03-03 09:17:08</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28261,7 +28261,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:33</t>
+          <t>2026-03-03 09:17:08</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28494,7 +28494,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:33</t>
+          <t>2026-03-03 09:17:08</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:36</t>
+          <t>2026-03-03 09:17:10</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28960,7 +28960,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:37</t>
+          <t>2026-03-03 09:17:12</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29193,7 +29193,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:37</t>
+          <t>2026-03-03 09:17:12</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29426,7 +29426,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:37</t>
+          <t>2026-03-03 09:17:12</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:37</t>
+          <t>2026-03-03 09:17:12</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:40</t>
+          <t>2026-03-03 09:17:14</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -30113,7 +30113,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:41</t>
+          <t>2026-03-03 09:17:15</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:41</t>
+          <t>2026-03-03 09:17:15</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30555,7 +30555,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:41</t>
+          <t>2026-03-03 09:17:15</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30776,7 +30776,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:41</t>
+          <t>2026-03-03 09:17:15</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30997,7 +30997,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:44</t>
+          <t>2026-03-03 09:17:18</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -31230,7 +31230,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:46</t>
+          <t>2026-03-03 09:17:19</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31463,7 +31463,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:46</t>
+          <t>2026-03-03 09:17:19</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31696,7 +31696,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:46</t>
+          <t>2026-03-03 09:17:19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31929,7 +31929,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:46</t>
+          <t>2026-03-03 09:17:19</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32162,7 +32162,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:48</t>
+          <t>2026-03-03 09:17:21</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:50</t>
+          <t>2026-03-03 09:17:23</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32628,7 +32628,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:50</t>
+          <t>2026-03-03 09:17:23</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:50</t>
+          <t>2026-03-03 09:17:23</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -33094,7 +33094,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:50</t>
+          <t>2026-03-03 09:17:23</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33327,7 +33327,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:52</t>
+          <t>2026-03-03 09:17:25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33560,7 +33560,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:54</t>
+          <t>2026-03-03 09:17:27</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33793,7 +33793,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:54</t>
+          <t>2026-03-03 09:17:27</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -34026,7 +34026,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:54</t>
+          <t>2026-03-03 09:17:27</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34259,7 +34259,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:54</t>
+          <t>2026-03-03 09:17:27</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:56</t>
+          <t>2026-03-03 09:17:29</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34725,7 +34725,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:58</t>
+          <t>2026-03-03 09:17:31</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:58</t>
+          <t>2026-03-03 09:17:31</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35191,7 +35191,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:58</t>
+          <t>2026-03-03 09:17:31</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35424,7 +35424,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-03 09:11:58</t>
+          <t>2026-03-03 09:17:31</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35657,7 +35657,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:01</t>
+          <t>2026-03-03 09:17:33</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35898,7 +35898,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:02</t>
+          <t>2026-03-03 09:17:34</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36139,7 +36139,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:02</t>
+          <t>2026-03-03 09:17:34</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36380,7 +36380,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:02</t>
+          <t>2026-03-03 09:17:34</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36621,7 +36621,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:02</t>
+          <t>2026-03-03 09:17:34</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36862,7 +36862,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:05</t>
+          <t>2026-03-03 09:17:37</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:07</t>
+          <t>2026-03-03 09:17:38</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:07</t>
+          <t>2026-03-03 09:17:38</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37561,7 +37561,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:07</t>
+          <t>2026-03-03 09:17:38</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37790,7 +37790,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:07</t>
+          <t>2026-03-03 09:17:38</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:09</t>
+          <t>2026-03-03 09:17:41</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -38252,7 +38252,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:11</t>
+          <t>2026-03-03 09:17:42</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38485,7 +38485,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:11</t>
+          <t>2026-03-03 09:17:42</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:11</t>
+          <t>2026-03-03 09:17:42</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38951,7 +38951,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:11</t>
+          <t>2026-03-03 09:17:42</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39184,7 +39184,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:13</t>
+          <t>2026-03-03 09:17:45</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:15</t>
+          <t>2026-03-03 09:17:46</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39626,7 +39626,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:15</t>
+          <t>2026-03-03 09:17:46</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39847,7 +39847,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:15</t>
+          <t>2026-03-03 09:17:46</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40068,7 +40068,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:15</t>
+          <t>2026-03-03 09:17:46</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40289,7 +40289,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:18</t>
+          <t>2026-03-03 09:17:49</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40510,7 +40510,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:19</t>
+          <t>2026-03-03 09:17:50</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40731,7 +40731,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:19</t>
+          <t>2026-03-03 09:17:50</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40952,7 +40952,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:19</t>
+          <t>2026-03-03 09:17:50</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41173,7 +41173,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:19</t>
+          <t>2026-03-03 09:17:50</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41394,7 +41394,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:33</t>
+          <t>2026-03-03 09:18:03</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41627,7 +41627,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:33</t>
+          <t>2026-03-03 09:18:03</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41860,7 +41860,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:33</t>
+          <t>2026-03-03 09:18:03</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42093,7 +42093,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:33</t>
+          <t>2026-03-03 09:18:03</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42326,7 +42326,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:35</t>
+          <t>2026-03-03 09:18:06</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42523,7 +42523,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:37</t>
+          <t>2026-03-03 09:18:07</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:37</t>
+          <t>2026-03-03 09:18:07</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:37</t>
+          <t>2026-03-03 09:18:07</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43114,7 +43114,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:37</t>
+          <t>2026-03-03 09:18:07</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43311,7 +43311,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:39</t>
+          <t>2026-03-03 09:18:10</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43544,7 +43544,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:41</t>
+          <t>2026-03-03 09:18:11</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43777,7 +43777,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:41</t>
+          <t>2026-03-03 09:18:11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:41</t>
+          <t>2026-03-03 09:18:11</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44243,7 +44243,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:41</t>
+          <t>2026-03-03 09:18:11</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44476,7 +44476,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:43</t>
+          <t>2026-03-03 09:18:14</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44649,7 +44649,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:44</t>
+          <t>2026-03-03 09:18:15</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:44</t>
+          <t>2026-03-03 09:18:15</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:44</t>
+          <t>2026-03-03 09:18:15</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:44</t>
+          <t>2026-03-03 09:18:15</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45341,7 +45341,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:47</t>
+          <t>2026-03-03 09:18:17</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:48</t>
+          <t>2026-03-03 09:18:19</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45783,7 +45783,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:48</t>
+          <t>2026-03-03 09:18:19</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46004,7 +46004,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:48</t>
+          <t>2026-03-03 09:18:19</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46225,7 +46225,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:48</t>
+          <t>2026-03-03 09:18:19</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:51</t>
+          <t>2026-03-03 09:18:22</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46687,7 +46687,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:53</t>
+          <t>2026-03-03 09:18:23</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46928,7 +46928,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:53</t>
+          <t>2026-03-03 09:18:23</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47169,7 +47169,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:53</t>
+          <t>2026-03-03 09:18:23</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47410,7 +47410,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:53</t>
+          <t>2026-03-03 09:18:23</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47651,7 +47651,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:55</t>
+          <t>2026-03-03 09:18:26</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47892,7 +47892,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:57</t>
+          <t>2026-03-03 09:18:27</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:57</t>
+          <t>2026-03-03 09:18:27</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48374,7 +48374,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:57</t>
+          <t>2026-03-03 09:18:27</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48615,7 +48615,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-03 09:12:57</t>
+          <t>2026-03-03 09:18:27</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48856,7 +48856,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-03 09:13:00</t>
+          <t>2026-03-03 09:18:30</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -49089,7 +49089,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-03 09:13:01</t>
+          <t>2026-03-03 09:18:31</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49322,7 +49322,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-03 09:13:01</t>
+          <t>2026-03-03 09:18:31</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49555,7 +49555,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-03 09:13:01</t>
+          <t>2026-03-03 09:18:31</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49788,7 +49788,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-03 09:13:01</t>
+          <t>2026-03-03 09:18:31</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:30</t>
+          <t>2026-03-03 09:55:57</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:31</t>
+          <t>2026-03-03 09:55:59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:31</t>
+          <t>2026-03-03 09:55:59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:31</t>
+          <t>2026-03-03 09:55:59</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:31</t>
+          <t>2026-03-03 09:55:59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:34</t>
+          <t>2026-03-03 09:56:02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:36</t>
+          <t>2026-03-03 09:56:04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:36</t>
+          <t>2026-03-03 09:56:04</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:36</t>
+          <t>2026-03-03 09:56:04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:36</t>
+          <t>2026-03-03 09:56:04</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:38</t>
+          <t>2026-03-03 09:56:06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:40</t>
+          <t>2026-03-03 09:56:08</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:40</t>
+          <t>2026-03-03 09:56:08</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:40</t>
+          <t>2026-03-03 09:56:08</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:40</t>
+          <t>2026-03-03 09:56:08</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:43</t>
+          <t>2026-03-03 09:56:11</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:45</t>
+          <t>2026-03-03 09:56:13</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:45</t>
+          <t>2026-03-03 09:56:13</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:45</t>
+          <t>2026-03-03 09:56:13</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:45</t>
+          <t>2026-03-03 09:56:13</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:47</t>
+          <t>2026-03-03 09:56:16</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:49</t>
+          <t>2026-03-03 09:56:17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:49</t>
+          <t>2026-03-03 09:56:17</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:49</t>
+          <t>2026-03-03 09:56:17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:49</t>
+          <t>2026-03-03 09:56:17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:52</t>
+          <t>2026-03-03 09:56:20</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:53</t>
+          <t>2026-03-03 09:56:22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:53</t>
+          <t>2026-03-03 09:56:22</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:53</t>
+          <t>2026-03-03 09:56:22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:53</t>
+          <t>2026-03-03 09:56:22</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:56</t>
+          <t>2026-03-03 09:56:24</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:58</t>
+          <t>2026-03-03 09:56:26</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:58</t>
+          <t>2026-03-03 09:56:26</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:58</t>
+          <t>2026-03-03 09:56:26</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-03 09:45:58</t>
+          <t>2026-03-03 09:56:26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,7 +8697,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:01</t>
+          <t>2026-03-03 09:56:29</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:02</t>
+          <t>2026-03-03 09:56:30</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:02</t>
+          <t>2026-03-03 09:56:30</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:02</t>
+          <t>2026-03-03 09:56:30</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:02</t>
+          <t>2026-03-03 09:56:30</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:05</t>
+          <t>2026-03-03 09:56:33</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:07</t>
+          <t>2026-03-03 09:56:35</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:07</t>
+          <t>2026-03-03 09:56:35</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:07</t>
+          <t>2026-03-03 09:56:35</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:07</t>
+          <t>2026-03-03 09:56:35</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:09</t>
+          <t>2026-03-03 09:56:37</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:11</t>
+          <t>2026-03-03 09:56:39</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:11</t>
+          <t>2026-03-03 09:56:39</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:11</t>
+          <t>2026-03-03 09:56:39</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:11</t>
+          <t>2026-03-03 09:56:39</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:13</t>
+          <t>2026-03-03 09:56:42</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:15</t>
+          <t>2026-03-03 09:56:43</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:15</t>
+          <t>2026-03-03 09:56:43</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:15</t>
+          <t>2026-03-03 09:56:43</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:15</t>
+          <t>2026-03-03 09:56:43</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:18</t>
+          <t>2026-03-03 09:56:46</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:19</t>
+          <t>2026-03-03 09:56:48</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:19</t>
+          <t>2026-03-03 09:56:48</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:19</t>
+          <t>2026-03-03 09:56:48</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:19</t>
+          <t>2026-03-03 09:56:48</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:22</t>
+          <t>2026-03-03 09:56:50</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:24</t>
+          <t>2026-03-03 09:56:52</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:24</t>
+          <t>2026-03-03 09:56:52</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:24</t>
+          <t>2026-03-03 09:56:52</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:24</t>
+          <t>2026-03-03 09:56:52</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:26</t>
+          <t>2026-03-03 09:56:55</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:28</t>
+          <t>2026-03-03 09:56:57</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:28</t>
+          <t>2026-03-03 09:56:57</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:28</t>
+          <t>2026-03-03 09:56:57</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:28</t>
+          <t>2026-03-03 09:56:57</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:31</t>
+          <t>2026-03-03 09:56:59</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:33</t>
+          <t>2026-03-03 09:57:01</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:33</t>
+          <t>2026-03-03 09:57:01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:33</t>
+          <t>2026-03-03 09:57:01</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:33</t>
+          <t>2026-03-03 09:57:01</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:35</t>
+          <t>2026-03-03 09:57:04</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:37</t>
+          <t>2026-03-03 09:57:06</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:37</t>
+          <t>2026-03-03 09:57:06</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:37</t>
+          <t>2026-03-03 09:57:06</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:37</t>
+          <t>2026-03-03 09:57:06</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:39</t>
+          <t>2026-03-03 09:57:09</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:41</t>
+          <t>2026-03-03 09:57:11</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:41</t>
+          <t>2026-03-03 09:57:11</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:41</t>
+          <t>2026-03-03 09:57:11</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:41</t>
+          <t>2026-03-03 09:57:11</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,7 +19307,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:44</t>
+          <t>2026-03-03 09:57:13</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:46</t>
+          <t>2026-03-03 09:57:15</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:46</t>
+          <t>2026-03-03 09:57:15</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:46</t>
+          <t>2026-03-03 09:57:15</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:46</t>
+          <t>2026-03-03 09:57:15</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:48</t>
+          <t>2026-03-03 09:57:18</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:50</t>
+          <t>2026-03-03 09:57:20</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:50</t>
+          <t>2026-03-03 09:57:20</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:50</t>
+          <t>2026-03-03 09:57:20</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:50</t>
+          <t>2026-03-03 09:57:20</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21577,7 +21577,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:53</t>
+          <t>2026-03-03 09:57:22</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:54</t>
+          <t>2026-03-03 09:57:24</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:54</t>
+          <t>2026-03-03 09:57:24</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:54</t>
+          <t>2026-03-03 09:57:24</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:54</t>
+          <t>2026-03-03 09:57:24</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:57</t>
+          <t>2026-03-03 09:57:27</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:59</t>
+          <t>2026-03-03 09:57:29</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:59</t>
+          <t>2026-03-03 09:57:29</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:59</t>
+          <t>2026-03-03 09:57:29</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-03 09:46:59</t>
+          <t>2026-03-03 09:57:29</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23907,7 +23907,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:01</t>
+          <t>2026-03-03 09:57:31</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:03</t>
+          <t>2026-03-03 09:57:33</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:03</t>
+          <t>2026-03-03 09:57:33</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:03</t>
+          <t>2026-03-03 09:57:33</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:03</t>
+          <t>2026-03-03 09:57:33</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25072,7 +25072,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:06</t>
+          <t>2026-03-03 09:57:35</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:07</t>
+          <t>2026-03-03 09:57:37</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:07</t>
+          <t>2026-03-03 09:57:37</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:07</t>
+          <t>2026-03-03 09:57:37</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:07</t>
+          <t>2026-03-03 09:57:37</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26237,7 +26237,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:10</t>
+          <t>2026-03-03 09:57:40</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:12</t>
+          <t>2026-03-03 09:57:42</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:12</t>
+          <t>2026-03-03 09:57:42</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:12</t>
+          <t>2026-03-03 09:57:42</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:12</t>
+          <t>2026-03-03 09:57:42</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,7 +27402,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:15</t>
+          <t>2026-03-03 09:57:44</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27631,7 +27631,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:17</t>
+          <t>2026-03-03 09:57:46</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:17</t>
+          <t>2026-03-03 09:57:46</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28113,7 +28113,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:17</t>
+          <t>2026-03-03 09:57:46</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:17</t>
+          <t>2026-03-03 09:57:46</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28595,7 +28595,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:19</t>
+          <t>2026-03-03 09:57:49</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:21</t>
+          <t>2026-03-03 09:57:51</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:21</t>
+          <t>2026-03-03 09:57:51</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:21</t>
+          <t>2026-03-03 09:57:51</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:21</t>
+          <t>2026-03-03 09:57:51</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,7 +29748,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:24</t>
+          <t>2026-03-03 09:57:54</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:25</t>
+          <t>2026-03-03 09:57:55</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:25</t>
+          <t>2026-03-03 09:57:55</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:25</t>
+          <t>2026-03-03 09:57:55</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:25</t>
+          <t>2026-03-03 09:57:55</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:27</t>
+          <t>2026-03-03 09:57:58</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:29</t>
+          <t>2026-03-03 09:57:59</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:29</t>
+          <t>2026-03-03 09:57:59</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:29</t>
+          <t>2026-03-03 09:57:59</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:29</t>
+          <t>2026-03-03 09:57:59</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:32</t>
+          <t>2026-03-03 09:58:02</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:34</t>
+          <t>2026-03-03 09:58:04</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:34</t>
+          <t>2026-03-03 09:58:04</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:34</t>
+          <t>2026-03-03 09:58:04</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:34</t>
+          <t>2026-03-03 09:58:04</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:36</t>
+          <t>2026-03-03 09:58:07</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:38</t>
+          <t>2026-03-03 09:58:08</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:38</t>
+          <t>2026-03-03 09:58:08</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:38</t>
+          <t>2026-03-03 09:58:08</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:38</t>
+          <t>2026-03-03 09:58:08</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:41</t>
+          <t>2026-03-03 09:58:10</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:42</t>
+          <t>2026-03-03 09:58:12</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:42</t>
+          <t>2026-03-03 09:58:12</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:42</t>
+          <t>2026-03-03 09:58:12</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:42</t>
+          <t>2026-03-03 09:58:12</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:45</t>
+          <t>2026-03-03 09:58:15</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:47</t>
+          <t>2026-03-03 09:58:17</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:47</t>
+          <t>2026-03-03 09:58:17</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:47</t>
+          <t>2026-03-03 09:58:17</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:47</t>
+          <t>2026-03-03 09:58:17</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,7 +36678,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:50</t>
+          <t>2026-03-03 09:58:19</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:51</t>
+          <t>2026-03-03 09:58:21</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:51</t>
+          <t>2026-03-03 09:58:21</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:51</t>
+          <t>2026-03-03 09:58:21</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:51</t>
+          <t>2026-03-03 09:58:21</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:54</t>
+          <t>2026-03-03 09:58:24</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -38124,7 +38124,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:56</t>
+          <t>2026-03-03 09:58:25</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38365,7 +38365,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:56</t>
+          <t>2026-03-03 09:58:25</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38606,7 +38606,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:56</t>
+          <t>2026-03-03 09:58:25</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38847,7 +38847,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:56</t>
+          <t>2026-03-03 09:58:25</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39088,7 +39088,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-03 09:47:58</t>
+          <t>2026-03-03 09:58:28</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39321,7 +39321,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:00</t>
+          <t>2026-03-03 09:58:30</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:00</t>
+          <t>2026-03-03 09:58:30</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39787,7 +39787,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:00</t>
+          <t>2026-03-03 09:58:30</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:00</t>
+          <t>2026-03-03 09:58:30</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40253,7 +40253,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:03</t>
+          <t>2026-03-03 09:58:33</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40474,7 +40474,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:04</t>
+          <t>2026-03-03 09:58:35</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:04</t>
+          <t>2026-03-03 09:58:35</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40916,7 +40916,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:04</t>
+          <t>2026-03-03 09:58:35</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41137,7 +41137,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:04</t>
+          <t>2026-03-03 09:58:35</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:07</t>
+          <t>2026-03-03 09:58:37</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41579,7 +41579,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:09</t>
+          <t>2026-03-03 09:58:39</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41800,7 +41800,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:09</t>
+          <t>2026-03-03 09:58:39</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42021,7 +42021,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:09</t>
+          <t>2026-03-03 09:58:39</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42242,7 +42242,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:09</t>
+          <t>2026-03-03 09:58:39</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42463,7 +42463,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:22</t>
+          <t>2026-03-03 09:58:52</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42696,7 +42696,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:22</t>
+          <t>2026-03-03 09:58:52</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42929,7 +42929,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:22</t>
+          <t>2026-03-03 09:58:52</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43162,7 +43162,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:22</t>
+          <t>2026-03-03 09:58:52</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43395,7 +43395,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:25</t>
+          <t>2026-03-03 09:58:55</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43592,7 +43592,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:27</t>
+          <t>2026-03-03 09:58:56</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43789,7 +43789,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:27</t>
+          <t>2026-03-03 09:58:56</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43986,7 +43986,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:27</t>
+          <t>2026-03-03 09:58:56</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:27</t>
+          <t>2026-03-03 09:58:56</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:29</t>
+          <t>2026-03-03 09:58:59</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44613,7 +44613,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:31</t>
+          <t>2026-03-03 09:59:01</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44846,7 +44846,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:31</t>
+          <t>2026-03-03 09:59:01</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45079,7 +45079,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:31</t>
+          <t>2026-03-03 09:59:01</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45312,7 +45312,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:31</t>
+          <t>2026-03-03 09:59:01</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45545,7 +45545,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:34</t>
+          <t>2026-03-03 09:59:04</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45718,7 +45718,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:35</t>
+          <t>2026-03-03 09:59:05</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45891,7 +45891,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:35</t>
+          <t>2026-03-03 09:59:05</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46064,7 +46064,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:35</t>
+          <t>2026-03-03 09:59:05</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:35</t>
+          <t>2026-03-03 09:59:05</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46410,7 +46410,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:38</t>
+          <t>2026-03-03 09:59:08</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46631,7 +46631,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:40</t>
+          <t>2026-03-03 09:59:10</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:40</t>
+          <t>2026-03-03 09:59:10</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:40</t>
+          <t>2026-03-03 09:59:10</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:40</t>
+          <t>2026-03-03 09:59:10</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:42</t>
+          <t>2026-03-03 09:59:13</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47756,7 +47756,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:44</t>
+          <t>2026-03-03 09:59:14</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -47997,7 +47997,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:44</t>
+          <t>2026-03-03 09:59:14</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48238,7 +48238,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:44</t>
+          <t>2026-03-03 09:59:14</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48479,7 +48479,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:44</t>
+          <t>2026-03-03 09:59:14</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48720,7 +48720,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:47</t>
+          <t>2026-03-03 09:59:17</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48961,7 +48961,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:48</t>
+          <t>2026-03-03 09:59:19</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49202,7 +49202,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:48</t>
+          <t>2026-03-03 09:59:19</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49443,7 +49443,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:48</t>
+          <t>2026-03-03 09:59:19</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49684,7 +49684,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:48</t>
+          <t>2026-03-03 09:59:19</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49925,7 +49925,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:51</t>
+          <t>2026-03-03 09:59:21</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50158,7 +50158,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:53</t>
+          <t>2026-03-03 09:59:23</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -50391,7 +50391,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:53</t>
+          <t>2026-03-03 09:59:23</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50624,7 +50624,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:53</t>
+          <t>2026-03-03 09:59:23</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50857,7 +50857,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-03 09:48:53</t>
+          <t>2026-03-03 09:59:23</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:50</t>
+          <t>2026-03-05 17:51:39</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:52</t>
+          <t>2026-03-05 17:51:40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:52</t>
+          <t>2026-03-05 17:51:40</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:52</t>
+          <t>2026-03-05 17:51:40</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:52</t>
+          <t>2026-03-05 17:51:40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:54</t>
+          <t>2026-03-05 17:51:43</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:56</t>
+          <t>2026-03-05 17:51:44</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:56</t>
+          <t>2026-03-05 17:51:44</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:56</t>
+          <t>2026-03-05 17:51:44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:56</t>
+          <t>2026-03-05 17:51:44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-05 17:40:58</t>
+          <t>2026-03-05 17:51:47</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:00</t>
+          <t>2026-03-05 17:51:48</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:00</t>
+          <t>2026-03-05 17:51:48</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:00</t>
+          <t>2026-03-05 17:51:48</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:00</t>
+          <t>2026-03-05 17:51:48</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:02</t>
+          <t>2026-03-05 17:51:51</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:04</t>
+          <t>2026-03-05 17:51:52</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:04</t>
+          <t>2026-03-05 17:51:52</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:04</t>
+          <t>2026-03-05 17:51:52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:04</t>
+          <t>2026-03-05 17:51:52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:07</t>
+          <t>2026-03-05 17:51:55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:08</t>
+          <t>2026-03-05 17:51:57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:08</t>
+          <t>2026-03-05 17:51:57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:08</t>
+          <t>2026-03-05 17:51:57</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:08</t>
+          <t>2026-03-05 17:51:57</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:11</t>
+          <t>2026-03-05 17:51:59</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:12</t>
+          <t>2026-03-05 17:52:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:12</t>
+          <t>2026-03-05 17:52:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:12</t>
+          <t>2026-03-05 17:52:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:12</t>
+          <t>2026-03-05 17:52:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:15</t>
+          <t>2026-03-05 17:52:03</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:16</t>
+          <t>2026-03-05 17:52:04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:16</t>
+          <t>2026-03-05 17:52:04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:16</t>
+          <t>2026-03-05 17:52:04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:16</t>
+          <t>2026-03-05 17:52:04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:18</t>
+          <t>2026-03-05 17:52:06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:20</t>
+          <t>2026-03-05 17:52:08</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:20</t>
+          <t>2026-03-05 17:52:08</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:20</t>
+          <t>2026-03-05 17:52:08</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:20</t>
+          <t>2026-03-05 17:52:08</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:22</t>
+          <t>2026-03-05 17:52:11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:24</t>
+          <t>2026-03-05 17:52:12</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:24</t>
+          <t>2026-03-05 17:52:12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:24</t>
+          <t>2026-03-05 17:52:12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:24</t>
+          <t>2026-03-05 17:52:12</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:27</t>
+          <t>2026-03-05 17:52:15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:28</t>
+          <t>2026-03-05 17:52:16</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11241,7 +11241,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:28</t>
+          <t>2026-03-05 17:52:16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11414,7 +11414,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:28</t>
+          <t>2026-03-05 17:52:16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:28</t>
+          <t>2026-03-05 17:52:16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:30</t>
+          <t>2026-03-05 17:52:18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:32</t>
+          <t>2026-03-05 17:52:20</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:32</t>
+          <t>2026-03-05 17:52:20</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:32</t>
+          <t>2026-03-05 17:52:20</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:32</t>
+          <t>2026-03-05 17:52:20</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:34</t>
+          <t>2026-03-05 17:52:22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:36</t>
+          <t>2026-03-05 17:52:24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:36</t>
+          <t>2026-03-05 17:52:24</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:36</t>
+          <t>2026-03-05 17:52:24</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:36</t>
+          <t>2026-03-05 17:52:24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:38</t>
+          <t>2026-03-05 17:52:26</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -14039,7 +14039,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:40</t>
+          <t>2026-03-05 17:52:28</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14260,7 +14260,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:40</t>
+          <t>2026-03-05 17:52:28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:40</t>
+          <t>2026-03-05 17:52:28</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:40</t>
+          <t>2026-03-05 17:52:28</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14923,7 +14923,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:42</t>
+          <t>2026-03-05 17:52:30</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:44</t>
+          <t>2026-03-05 17:52:31</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:44</t>
+          <t>2026-03-05 17:52:31</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:44</t>
+          <t>2026-03-05 17:52:31</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:44</t>
+          <t>2026-03-05 17:52:31</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:46</t>
+          <t>2026-03-05 17:52:34</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:48</t>
+          <t>2026-03-05 17:52:35</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:48</t>
+          <t>2026-03-05 17:52:35</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:48</t>
+          <t>2026-03-05 17:52:35</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:48</t>
+          <t>2026-03-05 17:52:35</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:50</t>
+          <t>2026-03-05 17:52:38</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:52</t>
+          <t>2026-03-05 17:52:39</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:52</t>
+          <t>2026-03-05 17:52:39</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:52</t>
+          <t>2026-03-05 17:52:39</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:52</t>
+          <t>2026-03-05 17:52:39</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:54</t>
+          <t>2026-03-05 17:52:42</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:56</t>
+          <t>2026-03-05 17:52:43</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:56</t>
+          <t>2026-03-05 17:52:43</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18817,7 +18817,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:56</t>
+          <t>2026-03-05 17:52:43</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:56</t>
+          <t>2026-03-05 17:52:43</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19283,7 +19283,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-05 17:41:58</t>
+          <t>2026-03-05 17:52:46</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:00</t>
+          <t>2026-03-05 17:52:47</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:00</t>
+          <t>2026-03-05 17:52:47</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:00</t>
+          <t>2026-03-05 17:52:47</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20167,7 +20167,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:00</t>
+          <t>2026-03-05 17:52:47</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20388,7 +20388,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:02</t>
+          <t>2026-03-05 17:52:50</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:04</t>
+          <t>2026-03-05 17:52:51</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:04</t>
+          <t>2026-03-05 17:52:51</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:04</t>
+          <t>2026-03-05 17:52:51</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:04</t>
+          <t>2026-03-05 17:52:51</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:07</t>
+          <t>2026-03-05 17:52:54</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:08</t>
+          <t>2026-03-05 17:52:55</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:08</t>
+          <t>2026-03-05 17:52:55</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:08</t>
+          <t>2026-03-05 17:52:55</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:08</t>
+          <t>2026-03-05 17:52:55</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:11</t>
+          <t>2026-03-05 17:52:58</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:12</t>
+          <t>2026-03-05 17:52:59</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:12</t>
+          <t>2026-03-05 17:52:59</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:12</t>
+          <t>2026-03-05 17:52:59</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:12</t>
+          <t>2026-03-05 17:52:59</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23883,7 +23883,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:15</t>
+          <t>2026-03-05 17:53:02</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:16</t>
+          <t>2026-03-05 17:53:03</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:16</t>
+          <t>2026-03-05 17:53:03</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:16</t>
+          <t>2026-03-05 17:53:03</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:16</t>
+          <t>2026-03-05 17:53:03</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:19</t>
+          <t>2026-03-05 17:53:06</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:20</t>
+          <t>2026-03-05 17:53:07</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:20</t>
+          <t>2026-03-05 17:53:07</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:20</t>
+          <t>2026-03-05 17:53:07</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:20</t>
+          <t>2026-03-05 17:53:07</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:23</t>
+          <t>2026-03-05 17:53:10</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:24</t>
+          <t>2026-03-05 17:53:11</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:24</t>
+          <t>2026-03-05 17:53:11</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:24</t>
+          <t>2026-03-05 17:53:11</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:24</t>
+          <t>2026-03-05 17:53:11</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:27</t>
+          <t>2026-03-05 17:53:14</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:28</t>
+          <t>2026-03-05 17:53:15</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27860,7 +27860,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:28</t>
+          <t>2026-03-05 17:53:15</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28101,7 +28101,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:28</t>
+          <t>2026-03-05 17:53:15</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28342,7 +28342,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:28</t>
+          <t>2026-03-05 17:53:15</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28583,7 +28583,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:31</t>
+          <t>2026-03-05 17:53:18</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:33</t>
+          <t>2026-03-05 17:53:19</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:33</t>
+          <t>2026-03-05 17:53:19</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:33</t>
+          <t>2026-03-05 17:53:19</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:33</t>
+          <t>2026-03-05 17:53:19</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29748,7 +29748,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:35</t>
+          <t>2026-03-05 17:53:22</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:37</t>
+          <t>2026-03-05 17:53:23</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30214,7 +30214,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:37</t>
+          <t>2026-03-05 17:53:23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30447,7 +30447,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:37</t>
+          <t>2026-03-05 17:53:23</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30680,7 +30680,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:37</t>
+          <t>2026-03-05 17:53:23</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30913,7 +30913,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:39</t>
+          <t>2026-03-05 17:53:25</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -31134,7 +31134,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:41</t>
+          <t>2026-03-05 17:53:27</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31355,7 +31355,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:41</t>
+          <t>2026-03-05 17:53:27</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:41</t>
+          <t>2026-03-05 17:53:27</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:41</t>
+          <t>2026-03-05 17:53:27</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:43</t>
+          <t>2026-03-05 17:53:29</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:45</t>
+          <t>2026-03-05 17:53:31</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:45</t>
+          <t>2026-03-05 17:53:31</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:45</t>
+          <t>2026-03-05 17:53:31</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:45</t>
+          <t>2026-03-05 17:53:31</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33183,7 +33183,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:47</t>
+          <t>2026-03-05 17:53:33</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:48</t>
+          <t>2026-03-05 17:53:35</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:48</t>
+          <t>2026-03-05 17:53:35</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:48</t>
+          <t>2026-03-05 17:53:35</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:48</t>
+          <t>2026-03-05 17:53:35</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34348,7 +34348,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:51</t>
+          <t>2026-03-05 17:53:37</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:52</t>
+          <t>2026-03-05 17:53:39</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:52</t>
+          <t>2026-03-05 17:53:39</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:52</t>
+          <t>2026-03-05 17:53:39</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:52</t>
+          <t>2026-03-05 17:53:39</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:55</t>
+          <t>2026-03-05 17:53:41</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:56</t>
+          <t>2026-03-05 17:53:43</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:56</t>
+          <t>2026-03-05 17:53:43</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36212,7 +36212,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:56</t>
+          <t>2026-03-05 17:53:43</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36445,7 +36445,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:56</t>
+          <t>2026-03-05 17:53:43</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36678,7 +36678,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-05 17:42:59</t>
+          <t>2026-03-05 17:53:45</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -36919,7 +36919,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:00</t>
+          <t>2026-03-05 17:53:47</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:00</t>
+          <t>2026-03-05 17:53:47</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37401,7 +37401,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:00</t>
+          <t>2026-03-05 17:53:47</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37642,7 +37642,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:00</t>
+          <t>2026-03-05 17:53:47</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37883,7 +37883,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:03</t>
+          <t>2026-03-05 17:53:49</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -38112,7 +38112,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:04</t>
+          <t>2026-03-05 17:53:51</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38353,7 +38353,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:04</t>
+          <t>2026-03-05 17:53:51</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38594,7 +38594,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:04</t>
+          <t>2026-03-05 17:53:51</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38835,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:04</t>
+          <t>2026-03-05 17:53:51</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:07</t>
+          <t>2026-03-05 17:53:53</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:09</t>
+          <t>2026-03-05 17:53:55</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:09</t>
+          <t>2026-03-05 17:53:55</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:09</t>
+          <t>2026-03-05 17:53:55</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +40008,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:09</t>
+          <t>2026-03-05 17:53:55</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40241,7 +40241,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:11</t>
+          <t>2026-03-05 17:53:58</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40462,7 +40462,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:13</t>
+          <t>2026-03-05 17:53:59</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:13</t>
+          <t>2026-03-05 17:53:59</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:13</t>
+          <t>2026-03-05 17:53:59</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41125,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:13</t>
+          <t>2026-03-05 17:53:59</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41346,7 +41346,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:15</t>
+          <t>2026-03-05 17:54:01</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41567,7 +41567,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:17</t>
+          <t>2026-03-05 17:54:03</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:17</t>
+          <t>2026-03-05 17:54:03</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:17</t>
+          <t>2026-03-05 17:54:03</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:17</t>
+          <t>2026-03-05 17:54:03</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,7 +42451,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:19</t>
+          <t>2026-03-05 17:54:06</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42684,7 +42684,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:21</t>
+          <t>2026-03-05 17:54:07</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:21</t>
+          <t>2026-03-05 17:54:07</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43150,7 +43150,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:21</t>
+          <t>2026-03-05 17:54:07</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43383,7 +43383,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:21</t>
+          <t>2026-03-05 17:54:07</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43616,7 +43616,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:23</t>
+          <t>2026-03-05 17:54:09</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43813,7 +43813,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:25</t>
+          <t>2026-03-05 17:54:11</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -44010,7 +44010,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:25</t>
+          <t>2026-03-05 17:54:11</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44207,7 +44207,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:25</t>
+          <t>2026-03-05 17:54:11</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44404,7 +44404,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:25</t>
+          <t>2026-03-05 17:54:11</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44601,7 +44601,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:27</t>
+          <t>2026-03-05 17:54:13</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44834,7 +44834,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:29</t>
+          <t>2026-03-05 17:54:15</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45067,7 +45067,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:29</t>
+          <t>2026-03-05 17:54:15</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:29</t>
+          <t>2026-03-05 17:54:15</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45533,7 +45533,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:29</t>
+          <t>2026-03-05 17:54:15</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45766,7 +45766,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:31</t>
+          <t>2026-03-05 17:54:17</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45939,7 +45939,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:32</t>
+          <t>2026-03-05 17:54:19</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46112,7 +46112,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:32</t>
+          <t>2026-03-05 17:54:19</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:32</t>
+          <t>2026-03-05 17:54:19</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46458,7 +46458,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:32</t>
+          <t>2026-03-05 17:54:19</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46631,7 +46631,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:35</t>
+          <t>2026-03-05 17:54:21</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:36</t>
+          <t>2026-03-05 17:54:22</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:36</t>
+          <t>2026-03-05 17:54:22</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47294,7 +47294,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:36</t>
+          <t>2026-03-05 17:54:22</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47515,7 +47515,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:36</t>
+          <t>2026-03-05 17:54:22</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47736,7 +47736,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:39</t>
+          <t>2026-03-05 17:54:25</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -47977,7 +47977,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:40</t>
+          <t>2026-03-05 17:54:26</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48218,7 +48218,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:40</t>
+          <t>2026-03-05 17:54:26</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48459,7 +48459,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:40</t>
+          <t>2026-03-05 17:54:26</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48700,7 +48700,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:40</t>
+          <t>2026-03-05 17:54:26</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48941,7 +48941,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:43</t>
+          <t>2026-03-05 17:54:29</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:44</t>
+          <t>2026-03-05 17:54:31</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49423,7 +49423,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:44</t>
+          <t>2026-03-05 17:54:31</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49664,7 +49664,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:44</t>
+          <t>2026-03-05 17:54:31</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49905,7 +49905,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:44</t>
+          <t>2026-03-05 17:54:31</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50146,7 +50146,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:47</t>
+          <t>2026-03-05 17:54:33</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -50379,7 +50379,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:48</t>
+          <t>2026-03-05 17:54:35</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50612,7 +50612,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:48</t>
+          <t>2026-03-05 17:54:35</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50845,7 +50845,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:48</t>
+          <t>2026-03-05 17:54:35</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51078,7 +51078,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-05 17:43:48</t>
+          <t>2026-03-05 17:54:35</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:26</t>
+          <t>2026-03-07 19:15:25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,27 +795,27 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>72</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:27</t>
+          <t>2026-03-07 19:15:27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:27</t>
+          <t>2026-03-07 19:15:27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:27</t>
+          <t>2026-03-07 19:15:27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:27</t>
+          <t>2026-03-07 19:15:27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:30</t>
+          <t>2026-03-07 19:15:29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:32</t>
+          <t>2026-03-07 19:15:31</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:32</t>
+          <t>2026-03-07 19:15:31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:32</t>
+          <t>2026-03-07 19:15:31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:32</t>
+          <t>2026-03-07 19:15:31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:34</t>
+          <t>2026-03-07 19:15:34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>346</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2759,12 +2759,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2784,96 +2784,96 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>12.9</t>
-        </is>
-      </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -2883,22 +2883,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:36</t>
+          <t>2026-03-07 19:15:35</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:36</t>
+          <t>2026-03-07 19:15:35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:36</t>
+          <t>2026-03-07 19:15:35</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:36</t>
+          <t>2026-03-07 19:15:35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:39</t>
+          <t>2026-03-07 19:15:38</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3918,7 +3918,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>56</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>-0.6</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>-0.4</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -3973,97 +3973,97 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
           <t>-0.6</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AT17" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>-0.5</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:41</t>
+          <t>2026-03-07 19:15:40</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:41</t>
+          <t>2026-03-07 19:15:40</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:41</t>
+          <t>2026-03-07 19:15:40</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:41</t>
+          <t>2026-03-07 19:15:40</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:43</t>
+          <t>2026-03-07 19:15:42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>345</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5089,12 +5089,12 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1022.0</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5114,48 +5114,48 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>10.9</t>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5173,29 +5173,29 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
           <t>11.3</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
           <t>10.9</t>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5213,22 +5213,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1022.0</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1022.0</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:45</t>
+          <t>2026-03-07 19:15:44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:45</t>
+          <t>2026-03-07 19:15:44</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:45</t>
+          <t>2026-03-07 19:15:44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:45</t>
+          <t>2026-03-07 19:15:44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6223,17 +6223,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:47</t>
+          <t>2026-03-07 19:15:47</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6254,12 +6254,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -6294,26 +6294,26 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6338,22 +6338,22 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6378,22 +6378,22 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:49</t>
+          <t>2026-03-07 19:15:48</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:49</t>
+          <t>2026-03-07 19:15:48</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:49</t>
+          <t>2026-03-07 19:15:48</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:49</t>
+          <t>2026-03-07 19:15:48</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7388,17 +7388,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:52</t>
+          <t>2026-03-07 19:15:51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7419,12 +7419,12 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1021.6</t>
+          <t>1021.9</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7434,23 +7434,23 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>9.1</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>9.4</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -7469,92 +7469,92 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
         <is>
           <t>19.1</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AT32" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AP32" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AU32" t="inlineStr">
         <is>
           <t>19.1</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1021.6</t>
+          <t>1021.9</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr"/>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1021.6</t>
+          <t>1021.9</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:53</t>
+          <t>2026-03-07 19:15:53</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:53</t>
+          <t>2026-03-07 19:15:53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:53</t>
+          <t>2026-03-07 19:15:53</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8272,7 +8272,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:53</t>
+          <t>2026-03-07 19:15:53</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8493,17 +8493,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:55</t>
+          <t>2026-03-07 19:15:55</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:57</t>
+          <t>2026-03-07 19:15:57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:57</t>
+          <t>2026-03-07 19:15:57</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:57</t>
+          <t>2026-03-07 19:15:57</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:57</t>
+          <t>2026-03-07 19:15:57</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9598,17 +9598,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-07 18:45:59</t>
+          <t>2026-03-07 19:16:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:01</t>
+          <t>2026-03-07 19:16:02</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:01</t>
+          <t>2026-03-07 19:16:02</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:01</t>
+          <t>2026-03-07 19:16:02</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:01</t>
+          <t>2026-03-07 19:16:02</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10703,17 +10703,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:04</t>
+          <t>2026-03-07 19:16:04</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:05</t>
+          <t>2026-03-07 19:16:06</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:05</t>
+          <t>2026-03-07 19:16:06</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:05</t>
+          <t>2026-03-07 19:16:06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:05</t>
+          <t>2026-03-07 19:16:06</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11568,17 +11568,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:08</t>
+          <t>2026-03-07 19:16:08</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11606,23 +11606,23 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
           <t>11.4</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>11.9</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -11633,22 +11633,22 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -11665,22 +11665,22 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:09</t>
+          <t>2026-03-07 19:16:10</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:09</t>
+          <t>2026-03-07 19:16:10</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:09</t>
+          <t>2026-03-07 19:16:10</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:09</t>
+          <t>2026-03-07 19:16:10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12433,17 +12433,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:12</t>
+          <t>2026-03-07 19:16:12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:14</t>
+          <t>2026-03-07 19:16:14</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:14</t>
+          <t>2026-03-07 19:16:14</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:14</t>
+          <t>2026-03-07 19:16:14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:14</t>
+          <t>2026-03-07 19:16:14</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13638,17 +13638,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:16</t>
+          <t>2026-03-07 19:16:16</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>315</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13675,12 +13675,12 @@
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13690,17 +13690,17 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -13712,29 +13712,29 @@
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -13754,27 +13754,27 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
@@ -13794,12 +13794,12 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>315</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -13810,7 +13810,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:17</t>
+          <t>2026-03-07 19:16:18</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:17</t>
+          <t>2026-03-07 19:16:18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:17</t>
+          <t>2026-03-07 19:16:18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:17</t>
+          <t>2026-03-07 19:16:18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14743,17 +14743,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:20</t>
+          <t>2026-03-07 19:16:21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14770,7 +14770,7 @@
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14781,23 +14781,23 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -14808,27 +14808,27 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -14840,27 +14840,27 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:22</t>
+          <t>2026-03-07 19:16:22</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:22</t>
+          <t>2026-03-07 19:16:22</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:22</t>
+          <t>2026-03-07 19:16:22</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:22</t>
+          <t>2026-03-07 19:16:22</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15593,7 +15593,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15608,17 +15608,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:24</t>
+          <t>2026-03-07 19:16:25</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15631,30 +15631,30 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15664,121 +15664,121 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15788,12 +15788,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -15841,7 +15841,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:26</t>
+          <t>2026-03-07 19:16:26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16074,7 +16074,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:26</t>
+          <t>2026-03-07 19:16:26</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16307,7 +16307,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:26</t>
+          <t>2026-03-07 19:16:26</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16540,7 +16540,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:26</t>
+          <t>2026-03-07 19:16:26</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16773,17 +16773,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:29</t>
+          <t>2026-03-07 19:16:29</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -16814,12 +16814,12 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -16829,121 +16829,121 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>33.5</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
           <t>-0.2</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>22.7</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -16953,12 +16953,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:30</t>
+          <t>2026-03-07 19:16:30</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:30</t>
+          <t>2026-03-07 19:16:30</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:30</t>
+          <t>2026-03-07 19:16:30</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:30</t>
+          <t>2026-03-07 19:16:30</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -17902,17 +17902,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:33</t>
+          <t>2026-03-07 19:16:33</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18135,7 +18135,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:34</t>
+          <t>2026-03-07 19:16:34</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:34</t>
+          <t>2026-03-07 19:16:34</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:34</t>
+          <t>2026-03-07 19:16:34</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:34</t>
+          <t>2026-03-07 19:16:34</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19067,17 +19067,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:37</t>
+          <t>2026-03-07 19:16:37</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19090,7 +19090,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19098,7 +19098,7 @@
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19109,17 +19109,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
@@ -19129,36 +19129,36 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -19168,7 +19168,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19178,27 +19178,27 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19218,33 +19218,33 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr"/>
@@ -19288,7 +19288,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:39</t>
+          <t>2026-03-07 19:16:39</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:39</t>
+          <t>2026-03-07 19:16:39</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:39</t>
+          <t>2026-03-07 19:16:39</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:39</t>
+          <t>2026-03-07 19:16:39</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20172,17 +20172,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:41</t>
+          <t>2026-03-07 19:16:42</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:43</t>
+          <t>2026-03-07 19:16:43</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:43</t>
+          <t>2026-03-07 19:16:43</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:43</t>
+          <t>2026-03-07 19:16:43</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:43</t>
+          <t>2026-03-07 19:16:43</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21322,7 +21322,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21337,17 +21337,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:46</t>
+          <t>2026-03-07 19:16:46</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>229</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -21368,12 +21368,12 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1020.4</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21393,56 +21393,56 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -21452,37 +21452,37 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21492,22 +21492,22 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1020.4</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -21517,12 +21517,12 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1020.4</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21570,7 +21570,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:47</t>
+          <t>2026-03-07 19:16:48</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -21803,7 +21803,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:47</t>
+          <t>2026-03-07 19:16:48</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:47</t>
+          <t>2026-03-07 19:16:48</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:47</t>
+          <t>2026-03-07 19:16:48</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22502,17 +22502,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:50</t>
+          <t>2026-03-07 19:16:50</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22532,7 +22532,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
@@ -22543,12 +22543,12 @@
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22575,19 +22575,19 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -22612,22 +22612,22 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
@@ -22652,17 +22652,17 @@
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>133</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
@@ -22672,7 +22672,7 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22687,7 +22687,7 @@
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:51</t>
+          <t>2026-03-07 19:16:51</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:51</t>
+          <t>2026-03-07 19:16:51</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:51</t>
+          <t>2026-03-07 19:16:51</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23434,7 +23434,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:51</t>
+          <t>2026-03-07 19:16:51</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23667,17 +23667,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:54</t>
+          <t>2026-03-07 19:16:54</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23692,7 +23692,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>327</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -23702,7 +23702,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
@@ -23713,66 +23713,66 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -23787,32 +23787,32 @@
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -23827,37 +23827,37 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>327</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>327</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr"/>
@@ -23900,7 +23900,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:56</t>
+          <t>2026-03-07 19:16:56</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:56</t>
+          <t>2026-03-07 19:16:56</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24366,7 +24366,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:56</t>
+          <t>2026-03-07 19:16:56</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:56</t>
+          <t>2026-03-07 19:16:56</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -24817,7 +24817,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -24832,17 +24832,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-07 18:46:58</t>
+          <t>2026-03-07 19:16:59</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -24855,7 +24855,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>103</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -24868,17 +24868,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.1</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -24888,121 +24888,121 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
       <c r="AH112" t="inlineStr">
         <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>8.9</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.1</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25012,12 +25012,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.1</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25065,7 +25065,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:00</t>
+          <t>2026-03-07 19:17:00</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25298,7 +25298,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:00</t>
+          <t>2026-03-07 19:17:00</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:00</t>
+          <t>2026-03-07 19:17:00</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:00</t>
+          <t>2026-03-07 19:17:00</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -25982,7 +25982,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -25997,17 +25997,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:03</t>
+          <t>2026-03-07 19:17:03</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26022,7 +26022,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
@@ -26043,7 +26043,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -26053,121 +26053,121 @@
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
           <t>-1.9</t>
-        </is>
-      </c>
-      <c r="X117" t="inlineStr">
-        <is>
-          <t>-1.8</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="AP117" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -26177,12 +26177,12 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:04</t>
+          <t>2026-03-07 19:17:05</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:04</t>
+          <t>2026-03-07 19:17:05</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26696,7 +26696,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:04</t>
+          <t>2026-03-07 19:17:05</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:04</t>
+          <t>2026-03-07 19:17:05</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27162,17 +27162,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:07</t>
+          <t>2026-03-07 19:17:07</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27403,7 +27403,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:09</t>
+          <t>2026-03-07 19:17:09</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27644,7 +27644,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:09</t>
+          <t>2026-03-07 19:17:09</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -27885,7 +27885,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:09</t>
+          <t>2026-03-07 19:17:09</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28126,7 +28126,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:09</t>
+          <t>2026-03-07 19:17:09</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28367,17 +28367,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:11</t>
+          <t>2026-03-07 19:17:12</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28600,7 +28600,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:13</t>
+          <t>2026-03-07 19:17:13</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -28833,7 +28833,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:13</t>
+          <t>2026-03-07 19:17:13</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:13</t>
+          <t>2026-03-07 19:17:13</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29299,7 +29299,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:13</t>
+          <t>2026-03-07 19:17:13</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29517,7 +29517,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29532,17 +29532,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:16</t>
+          <t>2026-03-07 19:17:16</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29563,12 +29563,12 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29578,27 +29578,27 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -29617,27 +29617,27 @@
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -29657,27 +29657,27 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -29702,12 +29702,12 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
@@ -29717,12 +29717,12 @@
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1021.5</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr"/>
@@ -29765,7 +29765,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:18</t>
+          <t>2026-03-07 19:17:18</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -29998,7 +29998,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:18</t>
+          <t>2026-03-07 19:17:18</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30231,7 +30231,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:18</t>
+          <t>2026-03-07 19:17:18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:18</t>
+          <t>2026-03-07 19:17:18</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30697,17 +30697,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:20</t>
+          <t>2026-03-07 19:17:20</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:22</t>
+          <t>2026-03-07 19:17:22</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31139,7 +31139,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:22</t>
+          <t>2026-03-07 19:17:22</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31360,7 +31360,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:22</t>
+          <t>2026-03-07 19:17:22</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31581,7 +31581,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:22</t>
+          <t>2026-03-07 19:17:22</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31787,7 +31787,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -31802,17 +31802,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:25</t>
+          <t>2026-03-07 19:17:25</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -31833,12 +31833,12 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -31858,96 +31858,96 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
           <t>9.9</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
           <t>9.9</t>
         </is>
       </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
@@ -31957,22 +31957,22 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
@@ -31982,12 +31982,12 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
@@ -32035,7 +32035,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:26</t>
+          <t>2026-03-07 19:17:26</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:26</t>
+          <t>2026-03-07 19:17:26</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32501,7 +32501,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:26</t>
+          <t>2026-03-07 19:17:26</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32734,7 +32734,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:26</t>
+          <t>2026-03-07 19:17:26</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -32952,7 +32952,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -32967,17 +32967,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:28</t>
+          <t>2026-03-07 19:17:29</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -32990,7 +32990,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>180</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -32998,12 +32998,12 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="S147" t="inlineStr">
@@ -33013,7 +33013,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33023,56 +33023,56 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -33082,37 +33082,37 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -33122,22 +33122,22 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
@@ -33147,12 +33147,12 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>1021.8</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:29</t>
+          <t>2026-03-07 19:17:31</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33433,7 +33433,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:29</t>
+          <t>2026-03-07 19:17:31</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33666,7 +33666,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:29</t>
+          <t>2026-03-07 19:17:31</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -33899,7 +33899,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:29</t>
+          <t>2026-03-07 19:17:31</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34117,7 +34117,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34132,17 +34132,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:32</t>
+          <t>2026-03-07 19:17:34</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34156,7 +34156,7 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -34173,66 +34173,66 @@
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
@@ -34242,7 +34242,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -34252,27 +34252,27 @@
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
@@ -34292,37 +34292,37 @@
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr"/>
@@ -34365,7 +34365,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:33</t>
+          <t>2026-03-07 19:17:35</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34598,7 +34598,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:33</t>
+          <t>2026-03-07 19:17:35</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34831,7 +34831,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:33</t>
+          <t>2026-03-07 19:17:35</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35064,7 +35064,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:33</t>
+          <t>2026-03-07 19:17:35</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35282,7 +35282,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35297,17 +35297,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:36</t>
+          <t>2026-03-07 19:17:37</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35320,7 +35320,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35328,12 +35328,12 @@
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.6</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -35343,7 +35343,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -35353,121 +35353,121 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN157" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="AI157" t="inlineStr">
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AT157" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AL157" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT157" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.6</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
@@ -35477,12 +35477,12 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.6</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
@@ -35530,7 +35530,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:38</t>
+          <t>2026-03-07 19:17:39</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:38</t>
+          <t>2026-03-07 19:17:39</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -35996,7 +35996,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:38</t>
+          <t>2026-03-07 19:17:39</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36229,7 +36229,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:38</t>
+          <t>2026-03-07 19:17:39</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36447,7 +36447,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36462,17 +36462,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:40</t>
+          <t>2026-03-07 19:17:42</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36485,7 +36485,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -36497,12 +36497,12 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>852.2</t>
+          <t>852.4</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36512,66 +36512,66 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -36586,32 +36586,32 @@
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -36626,42 +36626,42 @@
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>852.2</t>
+          <t>852.4</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>852.2</t>
+          <t>852.4</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -36703,7 +36703,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:41</t>
+          <t>2026-03-07 19:17:44</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -36944,7 +36944,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:41</t>
+          <t>2026-03-07 19:17:44</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37185,7 +37185,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:41</t>
+          <t>2026-03-07 19:17:44</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37426,7 +37426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:41</t>
+          <t>2026-03-07 19:17:44</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37652,7 +37652,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37667,17 +37667,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:44</t>
+          <t>2026-03-07 19:17:47</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37690,14 +37690,14 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -37707,166 +37707,166 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="AG167" t="inlineStr">
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL167" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>17:30 - 18:00</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -37908,7 +37908,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:46</t>
+          <t>2026-03-07 19:17:48</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38149,7 +38149,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:46</t>
+          <t>2026-03-07 19:17:48</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38390,7 +38390,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:46</t>
+          <t>2026-03-07 19:17:48</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38631,7 +38631,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:46</t>
+          <t>2026-03-07 19:17:48</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -38872,17 +38872,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:49</t>
+          <t>2026-03-07 19:17:51</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -38895,7 +38895,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -38903,12 +38903,12 @@
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -38918,66 +38918,66 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V172" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AG172" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -38987,37 +38987,37 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AL172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
@@ -39027,42 +39027,42 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr"/>
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:51</t>
+          <t>2026-03-07 19:17:52</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39338,7 +39338,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:51</t>
+          <t>2026-03-07 19:17:52</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39571,7 +39571,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:51</t>
+          <t>2026-03-07 19:17:52</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39804,7 +39804,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:51</t>
+          <t>2026-03-07 19:17:52</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40022,7 +40022,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40037,17 +40037,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:53</t>
+          <t>2026-03-07 19:17:55</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40060,7 +40060,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>82</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40068,12 +40068,12 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1023.0</t>
+          <t>1023.4</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -40083,102 +40083,102 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>7.4</t>
-        </is>
-      </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
           <t>7.2</t>
         </is>
       </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40188,33 +40188,33 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>1023.0</t>
+          <t>1023.4</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>1023.0</t>
+          <t>1023.4</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr"/>
@@ -40258,7 +40258,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:55</t>
+          <t>2026-03-07 19:17:57</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40479,7 +40479,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:55</t>
+          <t>2026-03-07 19:17:57</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40700,7 +40700,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:55</t>
+          <t>2026-03-07 19:17:57</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -40921,7 +40921,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:55</t>
+          <t>2026-03-07 19:17:57</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41142,17 +41142,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:57</t>
+          <t>2026-03-07 19:18:00</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41363,7 +41363,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:59</t>
+          <t>2026-03-07 19:18:01</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41584,7 +41584,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:59</t>
+          <t>2026-03-07 19:18:01</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41805,7 +41805,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:59</t>
+          <t>2026-03-07 19:18:01</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-07 18:47:59</t>
+          <t>2026-03-07 19:18:01</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42232,7 +42232,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42247,17 +42247,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:01</t>
+          <t>2026-03-07 19:18:04</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42270,7 +42270,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>94</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -42282,7 +42282,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R187" t="inlineStr"/>
@@ -42293,7 +42293,7 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
@@ -42303,121 +42303,121 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
           <t>-4.2</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-5.3</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AM187" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN187" t="inlineStr">
+        <is>
+          <t>-5.3</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
           <t>-4.2</t>
         </is>
       </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AJ187" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="AQ187" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="AL187" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="AM187" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN187" t="inlineStr">
-        <is>
-          <t>-3.8</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="AP187" t="inlineStr">
-        <is>
-          <t>-4.2</t>
-        </is>
-      </c>
-      <c r="AQ187" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS187" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
@@ -42427,12 +42427,12 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
@@ -42480,7 +42480,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:03</t>
+          <t>2026-03-07 19:18:06</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42713,7 +42713,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:03</t>
+          <t>2026-03-07 19:18:06</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -42946,7 +42946,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:03</t>
+          <t>2026-03-07 19:18:06</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43179,7 +43179,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:03</t>
+          <t>2026-03-07 19:18:06</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43397,7 +43397,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43412,17 +43412,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:05</t>
+          <t>2026-03-07 19:18:09</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43438,17 +43438,17 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1020.3</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43458,23 +43458,23 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
           <t>10.0</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>11.0</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr"/>
@@ -43485,67 +43485,67 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>1020.3</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>1020.0</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -43555,12 +43555,12 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1020.3</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr"/>
@@ -43609,7 +43609,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:07</t>
+          <t>2026-03-07 19:18:10</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:07</t>
+          <t>2026-03-07 19:18:10</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44003,7 +44003,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:07</t>
+          <t>2026-03-07 19:18:10</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44200,7 +44200,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:07</t>
+          <t>2026-03-07 19:18:10</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44382,7 +44382,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44397,17 +44397,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:09</t>
+          <t>2026-03-07 19:18:13</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44443,7 +44443,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -44453,116 +44453,116 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr">
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="AH197" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AI197" t="inlineStr">
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AL197" t="inlineStr">
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AT197" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AT197" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -44577,7 +44577,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -44630,7 +44630,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:11</t>
+          <t>2026-03-07 19:18:14</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44863,7 +44863,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:11</t>
+          <t>2026-03-07 19:18:14</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45096,7 +45096,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:11</t>
+          <t>2026-03-07 19:18:14</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45329,7 +45329,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:11</t>
+          <t>2026-03-07 19:18:14</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45547,7 +45547,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45562,17 +45562,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:14</t>
+          <t>2026-03-07 19:18:17</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45589,7 +45589,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -45600,23 +45600,23 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
           <t>10.9</t>
-        </is>
-      </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>11.8</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr"/>
@@ -45627,27 +45627,27 @@
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -45659,27 +45659,27 @@
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -45735,7 +45735,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:15</t>
+          <t>2026-03-07 19:18:18</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45908,7 +45908,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:15</t>
+          <t>2026-03-07 19:18:18</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46081,7 +46081,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:15</t>
+          <t>2026-03-07 19:18:18</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46254,7 +46254,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:15</t>
+          <t>2026-03-07 19:18:18</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46412,7 +46412,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46427,17 +46427,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:17</t>
+          <t>2026-03-07 19:18:20</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46450,7 +46450,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46458,7 +46458,7 @@
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R207" t="inlineStr"/>
@@ -46469,66 +46469,66 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -46538,37 +46538,37 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>17:30 - 18:00</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -46578,33 +46578,33 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>115</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr"/>
@@ -46648,7 +46648,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:19</t>
+          <t>2026-03-07 19:18:21</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46869,7 +46869,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:19</t>
+          <t>2026-03-07 19:18:21</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47090,7 +47090,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:19</t>
+          <t>2026-03-07 19:18:21</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47311,7 +47311,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:19</t>
+          <t>2026-03-07 19:18:21</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47517,7 +47517,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47532,17 +47532,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:22</t>
+          <t>2026-03-07 19:18:24</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47555,7 +47555,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -47572,17 +47572,17 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>851.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47592,141 +47592,141 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
           <t>-1.4</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
           <t>-1.4</t>
         </is>
       </c>
-      <c r="AI212" t="inlineStr">
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
         <is>
           <t>219</t>
         </is>
       </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>-1.4</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>851.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>851.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -47773,7 +47773,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:23</t>
+          <t>2026-03-07 19:18:25</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48014,7 +48014,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:23</t>
+          <t>2026-03-07 19:18:25</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:23</t>
+          <t>2026-03-07 19:18:25</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48496,7 +48496,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:23</t>
+          <t>2026-03-07 19:18:25</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48722,7 +48722,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48737,17 +48737,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:26</t>
+          <t>2026-03-07 19:18:28</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48762,7 +48762,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>204</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -48772,12 +48772,12 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>84</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -48787,7 +48787,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -48797,141 +48797,141 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
           <t>8.3</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>8.7</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>18:00 - 18:30</t>
+          <t>18:30 - 19:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AG217" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AH217" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>18:30 - 19:00</t>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AP217" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="AQ217" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AT217" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AU217" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AV217" t="inlineStr">
+        <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>18:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="AN217" t="inlineStr">
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>1019.5</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AP217" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AT217" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="AV217" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
-      <c r="AW217" t="inlineStr">
-        <is>
-          <t>1018.8</t>
-        </is>
-      </c>
-      <c r="AX217" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="AY217" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1019.5</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
@@ -48978,7 +48978,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:27</t>
+          <t>2026-03-07 19:18:30</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49219,7 +49219,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:27</t>
+          <t>2026-03-07 19:18:30</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49460,7 +49460,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:27</t>
+          <t>2026-03-07 19:18:30</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49701,7 +49701,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:27</t>
+          <t>2026-03-07 19:18:30</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -49942,17 +49942,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:30</t>
+          <t>2026-03-07 19:18:33</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50175,7 +50175,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:31</t>
+          <t>2026-03-07 19:18:35</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50408,7 +50408,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:31</t>
+          <t>2026-03-07 19:18:35</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50641,7 +50641,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:31</t>
+          <t>2026-03-07 19:18:35</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-07 18:48:31</t>
+          <t>2026-03-07 19:18:35</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51141,7 +51141,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51171,7 +51171,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51201,7 +51201,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51231,7 +51231,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51261,7 +51261,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51291,7 +51291,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51321,7 +51321,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51381,7 +51381,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51411,7 +51411,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51471,7 +51471,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51501,7 +51501,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51531,7 +51531,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51561,7 +51561,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51591,7 +51591,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51621,7 +51621,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51651,7 +51651,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51681,7 +51681,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51711,7 +51711,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51741,7 +51741,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51771,7 +51771,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51801,7 +51801,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51831,7 +51831,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51861,7 +51861,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51891,7 +51891,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51921,7 +51921,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51951,7 +51951,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -51981,7 +51981,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52011,7 +52011,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52041,7 +52041,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52071,7 +52071,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52101,7 +52101,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52131,7 +52131,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52161,7 +52161,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52191,7 +52191,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52221,7 +52221,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52251,7 +52251,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52281,7 +52281,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52311,7 +52311,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52341,7 +52341,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52371,7 +52371,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52401,7 +52401,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52431,7 +52431,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>
@@ -52461,7 +52461,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-07T18:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-07T18:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:25</t>
+          <t>2026-03-09 06:15:25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,27 +795,27 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:27</t>
+          <t>2026-03-09 06:15:26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:27</t>
+          <t>2026-03-09 06:15:26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:27</t>
+          <t>2026-03-09 06:15:26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:27</t>
+          <t>2026-03-09 06:15:26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:29</t>
+          <t>2026-03-09 06:15:29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1708,7 +1708,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1739,56 +1739,56 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:30</t>
+          <t>2026-03-09 06:15:30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:30</t>
+          <t>2026-03-09 06:15:30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:30</t>
+          <t>2026-03-09 06:15:30</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:30</t>
+          <t>2026-03-09 06:15:30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:33</t>
+          <t>2026-03-09 06:15:33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>333</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2879,12 +2879,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1020.9</t>
+          <t>1020.8</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2904,56 +2904,56 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2963,37 +2963,37 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3003,22 +3003,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1020.9</t>
+          <t>1020.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1020.9</t>
+          <t>1020.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:34</t>
+          <t>2026-03-09 06:15:34</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:34</t>
+          <t>2026-03-09 06:15:34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:34</t>
+          <t>2026-03-09 06:15:34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:34</t>
+          <t>2026-03-09 06:15:34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:36</t>
+          <t>2026-03-09 06:15:36</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4038,12 +4038,12 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>157</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4069,51 +4069,51 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -4128,32 +4128,32 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -4168,22 +4168,22 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>117</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:38</t>
+          <t>2026-03-09 06:15:38</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:38</t>
+          <t>2026-03-09 06:15:38</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:38</t>
+          <t>2026-03-09 06:15:38</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:38</t>
+          <t>2026-03-09 06:15:38</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:40</t>
+          <t>2026-03-09 06:15:40</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5234,53 +5234,53 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
       <c r="AI22" t="inlineStr">
         <is>
           <t>100</t>
@@ -5293,34 +5293,34 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
       <c r="AQ22" t="inlineStr">
         <is>
           <t>100</t>
@@ -5333,17 +5333,17 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:42</t>
+          <t>2026-03-09 06:15:42</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:42</t>
+          <t>2026-03-09 06:15:42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:42</t>
+          <t>2026-03-09 06:15:42</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:42</t>
+          <t>2026-03-09 06:15:42</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:44</t>
+          <t>2026-03-09 06:15:44</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6399,56 +6399,56 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6458,37 +6458,37 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:45</t>
+          <t>2026-03-09 06:15:45</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:45</t>
+          <t>2026-03-09 06:15:45</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:45</t>
+          <t>2026-03-09 06:15:45</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:45</t>
+          <t>2026-03-09 06:15:45</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:48</t>
+          <t>2026-03-09 06:15:48</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7539,7 +7539,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -7554,23 +7554,23 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>9.3</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>9.6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -7589,67 +7589,67 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:49</t>
+          <t>2026-03-09 06:15:49</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:49</t>
+          <t>2026-03-09 06:15:49</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:49</t>
+          <t>2026-03-09 06:15:49</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:49</t>
+          <t>2026-03-09 06:15:49</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:52</t>
+          <t>2026-03-09 06:15:52</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8637,7 +8637,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>332</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
@@ -8681,20 +8681,20 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
@@ -8724,17 +8724,17 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8785,7 +8785,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:53</t>
+          <t>2026-03-09 06:15:53</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:53</t>
+          <t>2026-03-09 06:15:53</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:53</t>
+          <t>2026-03-09 06:15:53</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:53</t>
+          <t>2026-03-09 06:15:53</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:55</t>
+          <t>2026-03-09 06:15:55</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9742,7 +9742,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -9780,88 +9780,88 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="AH42" t="inlineStr">
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
+      <c r="AQ42" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>4.6</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ42" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="AR42" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9869,17 +9869,17 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -9890,7 +9890,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:57</t>
+          <t>2026-03-09 06:15:57</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:57</t>
+          <t>2026-03-09 06:15:57</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:57</t>
+          <t>2026-03-09 06:15:57</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:57</t>
+          <t>2026-03-09 06:15:57</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10823,17 +10823,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-09 05:45:59</t>
+          <t>2026-03-09 06:15:59</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10861,23 +10861,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10888,22 +10888,22 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -10920,22 +10920,22 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:00</t>
+          <t>2026-03-09 06:16:00</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:00</t>
+          <t>2026-03-09 06:16:00</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:00</t>
+          <t>2026-03-09 06:16:00</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:00</t>
+          <t>2026-03-09 06:16:00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:02</t>
+          <t>2026-03-09 06:16:02</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11726,23 +11726,23 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -11753,22 +11753,22 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -11785,22 +11785,22 @@
       <c r="AL52" t="inlineStr"/>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:03</t>
+          <t>2026-03-09 06:16:04</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:03</t>
+          <t>2026-03-09 06:16:04</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:03</t>
+          <t>2026-03-09 06:16:04</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:03</t>
+          <t>2026-03-09 06:16:04</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12553,17 +12553,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:06</t>
+          <t>2026-03-09 06:16:06</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12576,14 +12576,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12623,26 +12623,26 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -12672,17 +12672,17 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
@@ -12712,22 +12712,22 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -12737,12 +12737,12 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>116</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:07</t>
+          <t>2026-03-09 06:16:07</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:07</t>
+          <t>2026-03-09 06:16:07</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:07</t>
+          <t>2026-03-09 06:16:07</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:07</t>
+          <t>2026-03-09 06:16:07</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:10</t>
+          <t>2026-03-09 06:16:10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13810,116 +13810,116 @@
       </c>
       <c r="V62" t="inlineStr">
         <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
           <t>8.6</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>9.4</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="AH62" t="inlineStr">
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
-      </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>306</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -13930,7 +13930,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:11</t>
+          <t>2026-03-09 06:16:11</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:11</t>
+          <t>2026-03-09 06:16:11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:11</t>
+          <t>2026-03-09 06:16:11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:11</t>
+          <t>2026-03-09 06:16:11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:13</t>
+          <t>2026-03-09 06:16:13</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14901,23 +14901,23 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
           <t>6.3</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>6.9</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr"/>
@@ -14928,22 +14928,22 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
@@ -14960,22 +14960,22 @@
       <c r="AL67" t="inlineStr"/>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:15</t>
+          <t>2026-03-09 06:16:15</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:15</t>
+          <t>2026-03-09 06:16:15</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:15</t>
+          <t>2026-03-09 06:16:15</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:15</t>
+          <t>2026-03-09 06:16:15</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15713,7 +15713,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:17</t>
+          <t>2026-03-09 06:16:17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15751,19 +15751,19 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>203</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15784,12 +15784,12 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -15799,26 +15799,26 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15843,22 +15843,22 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -15868,12 +15868,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>-6.1</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -15883,22 +15883,22 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:18</t>
+          <t>2026-03-09 06:16:18</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:18</t>
+          <t>2026-03-09 06:16:18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:18</t>
+          <t>2026-03-09 06:16:18</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:18</t>
+          <t>2026-03-09 06:16:18</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:21</t>
+          <t>2026-03-09 06:16:20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>208</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -16939,7 +16939,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -16954,31 +16954,31 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -16988,12 +16988,12 @@
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
@@ -17013,12 +17013,12 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
@@ -17028,12 +17028,12 @@
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -17053,17 +17053,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:22</t>
+          <t>2026-03-09 06:16:22</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:22</t>
+          <t>2026-03-09 06:16:22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:22</t>
+          <t>2026-03-09 06:16:22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:22</t>
+          <t>2026-03-09 06:16:22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18043,7 +18043,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18058,17 +18058,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:24</t>
+          <t>2026-03-09 06:16:24</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18081,7 +18081,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.2</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18114,98 +18114,98 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR82" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18213,22 +18213,22 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.2</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -18238,12 +18238,12 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.2</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:26</t>
+          <t>2026-03-09 06:16:26</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:26</t>
+          <t>2026-03-09 06:16:26</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:26</t>
+          <t>2026-03-09 06:16:26</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:26</t>
+          <t>2026-03-09 06:16:26</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:28</t>
+          <t>2026-03-09 06:16:28</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19265,7 +19265,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19290,21 +19290,21 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -19334,17 +19334,17 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
@@ -19374,17 +19374,17 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -19395,7 +19395,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:29</t>
+          <t>2026-03-09 06:16:30</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:29</t>
+          <t>2026-03-09 06:16:30</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:29</t>
+          <t>2026-03-09 06:16:30</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:29</t>
+          <t>2026-03-09 06:16:30</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20328,17 +20328,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:32</t>
+          <t>2026-03-09 06:16:32</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20384,17 +20384,17 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
+          <t>-5.6</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
           <t>-5.4</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>-4.8</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -20413,62 +20413,62 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
+          <t>-5.6</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
           <t>-5.4</t>
         </is>
       </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>-5.1</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>-4.8</t>
-        </is>
-      </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-5.6</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:34</t>
+          <t>2026-03-09 06:16:33</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:34</t>
+          <t>2026-03-09 06:16:33</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21027,7 +21027,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:34</t>
+          <t>2026-03-09 06:16:33</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21260,7 +21260,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:34</t>
+          <t>2026-03-09 06:16:33</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21478,7 +21478,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21493,17 +21493,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:36</t>
+          <t>2026-03-09 06:16:35</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -21529,7 +21529,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -21539,7 +21539,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21549,7 +21549,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -21559,7 +21559,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -21571,24 +21571,24 @@
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
@@ -21613,22 +21613,22 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
@@ -21653,17 +21653,17 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>126</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -21673,12 +21673,12 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:37</t>
+          <t>2026-03-09 06:16:36</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -21959,7 +21959,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:37</t>
+          <t>2026-03-09 06:16:36</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22192,7 +22192,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:37</t>
+          <t>2026-03-09 06:16:36</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:37</t>
+          <t>2026-03-09 06:16:36</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22643,7 +22643,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22658,17 +22658,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:40</t>
+          <t>2026-03-09 06:16:39</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22683,7 +22683,7 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>106</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -22704,7 +22704,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22719,31 +22719,31 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -22753,12 +22753,12 @@
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
@@ -22778,12 +22778,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
@@ -22793,12 +22793,12 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-6.6</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -22818,17 +22818,17 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22838,12 +22838,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:41</t>
+          <t>2026-03-09 06:16:40</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23124,7 +23124,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:41</t>
+          <t>2026-03-09 06:16:40</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:41</t>
+          <t>2026-03-09 06:16:40</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:41</t>
+          <t>2026-03-09 06:16:40</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23823,17 +23823,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:44</t>
+          <t>2026-03-09 06:16:42</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23848,17 +23848,17 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
@@ -23869,7 +23869,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23884,31 +23884,31 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -23918,17 +23918,17 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -23938,17 +23938,17 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
@@ -23958,17 +23958,17 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -23978,22 +23978,22 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -24003,12 +24003,12 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
@@ -24056,7 +24056,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:45</t>
+          <t>2026-03-09 06:16:44</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:45</t>
+          <t>2026-03-09 06:16:44</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:45</t>
+          <t>2026-03-09 06:16:44</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:45</t>
+          <t>2026-03-09 06:16:44</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -24988,17 +24988,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:48</t>
+          <t>2026-03-09 06:16:46</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -25024,7 +25024,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25044,17 +25044,17 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -25066,99 +25066,99 @@
       <c r="AA112" t="inlineStr"/>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
           <t>6.6</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>215</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25168,12 +25168,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:49</t>
+          <t>2026-03-09 06:16:47</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25454,7 +25454,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:49</t>
+          <t>2026-03-09 06:16:47</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:49</t>
+          <t>2026-03-09 06:16:47</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:49</t>
+          <t>2026-03-09 06:16:47</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26138,7 +26138,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -26153,17 +26153,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:51</t>
+          <t>2026-03-09 06:16:50</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26178,7 +26178,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>277</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -26199,7 +26199,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
@@ -26226,19 +26226,19 @@
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -26273,12 +26273,12 @@
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
@@ -26293,7 +26293,7 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
@@ -26313,17 +26313,17 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -26333,12 +26333,12 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>277</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:53</t>
+          <t>2026-03-09 06:16:51</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26619,7 +26619,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:53</t>
+          <t>2026-03-09 06:16:51</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26852,7 +26852,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:53</t>
+          <t>2026-03-09 06:16:51</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27085,7 +27085,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:53</t>
+          <t>2026-03-09 06:16:51</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27303,7 +27303,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -27318,17 +27318,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:55</t>
+          <t>2026-03-09 06:16:53</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -27353,12 +27353,12 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -27368,7 +27368,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -27378,56 +27378,56 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -27442,32 +27442,32 @@
       </c>
       <c r="AL122" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
@@ -27482,37 +27482,37 @@
       </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
@@ -27559,7 +27559,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:57</t>
+          <t>2026-03-09 06:16:55</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27800,7 +27800,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:57</t>
+          <t>2026-03-09 06:16:55</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28041,7 +28041,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:57</t>
+          <t>2026-03-09 06:16:55</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28282,7 +28282,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:57</t>
+          <t>2026-03-09 06:16:55</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28523,17 +28523,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-09 05:46:59</t>
+          <t>2026-03-09 06:16:57</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28558,7 +28558,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="R127" t="inlineStr"/>
@@ -28569,7 +28569,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28579,17 +28579,17 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -28608,27 +28608,27 @@
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -28648,27 +28648,27 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>-4.1</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>-4.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -28756,7 +28756,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:00</t>
+          <t>2026-03-09 06:16:58</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -28989,7 +28989,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:00</t>
+          <t>2026-03-09 06:16:58</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:00</t>
+          <t>2026-03-09 06:16:58</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29455,7 +29455,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:00</t>
+          <t>2026-03-09 06:16:58</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29673,7 +29673,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29688,17 +29688,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:03</t>
+          <t>2026-03-09 06:17:01</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29724,7 +29724,7 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29734,7 +29734,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -29749,12 +29749,12 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -29773,7 +29773,7 @@
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -29783,12 +29783,12 @@
       </c>
       <c r="AG132" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
@@ -29823,12 +29823,12 @@
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -29858,7 +29858,7 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
@@ -29873,7 +29873,7 @@
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
@@ -29921,7 +29921,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:04</t>
+          <t>2026-03-09 06:17:02</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30154,7 +30154,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:04</t>
+          <t>2026-03-09 06:17:02</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30387,7 +30387,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:04</t>
+          <t>2026-03-09 06:17:02</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:04</t>
+          <t>2026-03-09 06:17:02</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30853,17 +30853,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:06</t>
+          <t>2026-03-09 06:17:04</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -30895,7 +30895,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -30905,98 +30905,98 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
         <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN137" t="inlineStr">
+        <is>
           <t>8.6</t>
         </is>
       </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="AL137" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="AR137" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -31004,17 +31004,17 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
@@ -31025,7 +31025,7 @@
       <c r="AW137" t="inlineStr"/>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:08</t>
+          <t>2026-03-09 06:17:06</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31295,7 +31295,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:08</t>
+          <t>2026-03-09 06:17:06</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:08</t>
+          <t>2026-03-09 06:17:06</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:08</t>
+          <t>2026-03-09 06:17:06</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31943,7 +31943,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -31958,17 +31958,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:10</t>
+          <t>2026-03-09 06:17:08</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -31981,7 +31981,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>333</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32004,7 +32004,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32014,17 +32014,17 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -32036,29 +32036,29 @@
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
@@ -32078,27 +32078,27 @@
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
@@ -32118,12 +32118,12 @@
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -32191,7 +32191,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:12</t>
+          <t>2026-03-09 06:17:10</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:12</t>
+          <t>2026-03-09 06:17:10</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32657,7 +32657,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:12</t>
+          <t>2026-03-09 06:17:10</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32890,7 +32890,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:12</t>
+          <t>2026-03-09 06:17:10</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33108,7 +33108,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33123,17 +33123,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:14</t>
+          <t>2026-03-09 06:17:12</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33146,7 +33146,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
@@ -33154,7 +33154,7 @@
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>95</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
@@ -33169,7 +33169,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33179,14 +33179,14 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
       <c r="X147" t="inlineStr">
         <is>
           <t>10.3</t>
@@ -33194,116 +33194,116 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr"/>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN147" t="inlineStr">
         <is>
           <t>10.3</t>
         </is>
       </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AT147" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="AU147" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="AL147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AM147" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AP147" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>1020.3</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
         <is>
           <t>4.3</t>
-        </is>
-      </c>
-      <c r="AT147" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="AV147" t="inlineStr">
-        <is>
-          <t>1020.3</t>
-        </is>
-      </c>
-      <c r="AW147" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX147" t="inlineStr">
-        <is>
-          <t>11.2</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:15</t>
+          <t>2026-03-09 06:17:13</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:15</t>
+          <t>2026-03-09 06:17:13</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33822,7 +33822,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:15</t>
+          <t>2026-03-09 06:17:13</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34055,7 +34055,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:15</t>
+          <t>2026-03-09 06:17:13</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34273,7 +34273,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34288,17 +34288,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:18</t>
+          <t>2026-03-09 06:17:15</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34312,13 +34312,13 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
@@ -34334,7 +34334,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34344,98 +34344,98 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
           <t>-0.4</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>0.1</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR152" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -34443,22 +34443,22 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34468,12 +34468,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34521,7 +34521,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:19</t>
+          <t>2026-03-09 06:17:17</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34754,7 +34754,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:19</t>
+          <t>2026-03-09 06:17:17</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34987,7 +34987,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:19</t>
+          <t>2026-03-09 06:17:17</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35220,7 +35220,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:19</t>
+          <t>2026-03-09 06:17:17</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35438,7 +35438,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35453,17 +35453,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:22</t>
+          <t>2026-03-09 06:17:19</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35476,7 +35476,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35499,7 +35499,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -35514,31 +35514,31 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -35548,12 +35548,12 @@
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
@@ -35568,17 +35568,17 @@
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
@@ -35588,12 +35588,12 @@
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
@@ -35608,17 +35608,17 @@
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
@@ -35633,7 +35633,7 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -35686,7 +35686,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:23</t>
+          <t>2026-03-09 06:17:20</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35919,7 +35919,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:23</t>
+          <t>2026-03-09 06:17:20</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36152,7 +36152,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:23</t>
+          <t>2026-03-09 06:17:20</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:23</t>
+          <t>2026-03-09 06:17:20</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36603,7 +36603,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36618,17 +36618,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:25</t>
+          <t>2026-03-09 06:17:22</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36658,7 +36658,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>851.6</t>
+          <t>851.8</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36668,7 +36668,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -36678,17 +36678,17 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -36707,22 +36707,22 @@
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
@@ -36747,22 +36747,22 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-4.5</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
@@ -36797,7 +36797,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>851.6</t>
+          <t>851.8</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -36812,7 +36812,7 @@
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>851.6</t>
+          <t>851.8</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:27</t>
+          <t>2026-03-09 06:17:24</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37100,7 +37100,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:27</t>
+          <t>2026-03-09 06:17:24</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:27</t>
+          <t>2026-03-09 06:17:24</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37582,7 +37582,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:27</t>
+          <t>2026-03-09 06:17:24</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37772,7 +37772,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37787,17 +37787,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:29</t>
+          <t>2026-03-09 06:17:26</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37810,7 +37810,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>333</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -37832,12 +37832,12 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37847,101 +37847,101 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="W167" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="AG167" t="inlineStr">
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
       </c>
-      <c r="AH167" t="inlineStr">
+      <c r="AP167" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
+      <c r="AQ167" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL167" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
@@ -37951,17 +37951,17 @@
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
@@ -37971,12 +37971,12 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
@@ -38028,7 +38028,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:30</t>
+          <t>2026-03-09 06:17:27</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:30</t>
+          <t>2026-03-09 06:17:27</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:30</t>
+          <t>2026-03-09 06:17:27</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38715,7 +38715,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:30</t>
+          <t>2026-03-09 06:17:27</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38944,17 +38944,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:33</t>
+          <t>2026-03-09 06:17:30</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39177,7 +39177,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:34</t>
+          <t>2026-03-09 06:17:31</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:34</t>
+          <t>2026-03-09 06:17:31</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39643,7 +39643,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:34</t>
+          <t>2026-03-09 06:17:31</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39876,7 +39876,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:34</t>
+          <t>2026-03-09 06:17:31</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40109,17 +40109,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:37</t>
+          <t>2026-03-09 06:17:33</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40132,7 +40132,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>231</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40145,7 +40145,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1023.8</t>
+          <t>1023.9</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -40155,28 +40155,28 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
@@ -40190,69 +40190,69 @@
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="AI177" t="inlineStr">
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="AQ177" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="AR177" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -40260,12 +40260,12 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>231</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
@@ -40275,7 +40275,7 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>1023.8</t>
+          <t>1023.9</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr"/>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>1023.8</t>
+          <t>1023.9</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr"/>
@@ -40330,7 +40330,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:38</t>
+          <t>2026-03-09 06:17:35</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40551,7 +40551,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:38</t>
+          <t>2026-03-09 06:17:35</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40772,7 +40772,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:38</t>
+          <t>2026-03-09 06:17:35</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -40993,7 +40993,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:38</t>
+          <t>2026-03-09 06:17:35</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41199,7 +41199,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -41214,17 +41214,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:40</t>
+          <t>2026-03-09 06:17:37</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41237,7 +41237,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>271</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -41245,7 +41245,7 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R182" t="inlineStr"/>
@@ -41256,7 +41256,7 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -41266,56 +41266,56 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AG182" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -41325,37 +41325,37 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
@@ -41365,17 +41365,17 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -41386,7 +41386,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -41435,7 +41435,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:42</t>
+          <t>2026-03-09 06:17:38</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41656,7 +41656,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:42</t>
+          <t>2026-03-09 06:17:38</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41877,7 +41877,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:42</t>
+          <t>2026-03-09 06:17:38</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42098,7 +42098,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:42</t>
+          <t>2026-03-09 06:17:38</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42304,7 +42304,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42319,17 +42319,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:44</t>
+          <t>2026-03-09 06:17:41</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>252</t>
         </is>
       </c>
       <c r="N187" t="inlineStr"/>
@@ -42354,7 +42354,7 @@
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R187" t="inlineStr"/>
@@ -42365,7 +42365,7 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U187" t="inlineStr">
@@ -42375,56 +42375,56 @@
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z187" t="inlineStr"/>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -42439,32 +42439,32 @@
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.8</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -42479,17 +42479,17 @@
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
@@ -42499,12 +42499,12 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>252</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
@@ -42552,7 +42552,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:45</t>
+          <t>2026-03-09 06:17:42</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42785,7 +42785,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:45</t>
+          <t>2026-03-09 06:17:42</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:45</t>
+          <t>2026-03-09 06:17:42</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43251,7 +43251,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:45</t>
+          <t>2026-03-09 06:17:42</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43469,7 +43469,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43484,17 +43484,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:48</t>
+          <t>2026-03-09 06:17:44</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43510,7 +43510,7 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q192" t="inlineStr">
@@ -43530,23 +43530,23 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr"/>
@@ -43557,69 +43557,69 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>1023.6</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>05:30 - 06:00</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
           <t>1.8</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>1023.6</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>05:00 - 05:30</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR192" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -43627,7 +43627,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
@@ -43681,7 +43681,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:49</t>
+          <t>2026-03-09 06:17:46</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43878,7 +43878,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:49</t>
+          <t>2026-03-09 06:17:46</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44075,7 +44075,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:49</t>
+          <t>2026-03-09 06:17:46</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44272,7 +44272,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:49</t>
+          <t>2026-03-09 06:17:46</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44454,7 +44454,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44469,17 +44469,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:51</t>
+          <t>2026-03-09 06:17:48</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44492,7 +44492,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -44500,12 +44500,12 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
@@ -44515,7 +44515,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -44525,12 +44525,12 @@
       </c>
       <c r="V197" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr"/>
@@ -44554,12 +44554,12 @@
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -44569,12 +44569,12 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -44584,22 +44584,22 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -44609,12 +44609,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
@@ -44624,12 +44624,12 @@
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
@@ -44639,7 +44639,7 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
@@ -44654,7 +44654,7 @@
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
@@ -44702,7 +44702,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:53</t>
+          <t>2026-03-09 06:17:49</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44935,7 +44935,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:53</t>
+          <t>2026-03-09 06:17:49</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45168,7 +45168,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:53</t>
+          <t>2026-03-09 06:17:49</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45401,7 +45401,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:53</t>
+          <t>2026-03-09 06:17:49</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45619,7 +45619,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45634,17 +45634,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:55</t>
+          <t>2026-03-09 06:17:51</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45672,13 +45672,13 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr"/>
@@ -45699,17 +45699,17 @@
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
@@ -45731,17 +45731,17 @@
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
@@ -45807,7 +45807,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:56</t>
+          <t>2026-03-09 06:17:52</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45980,7 +45980,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:56</t>
+          <t>2026-03-09 06:17:52</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46153,7 +46153,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:56</t>
+          <t>2026-03-09 06:17:52</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46326,7 +46326,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:56</t>
+          <t>2026-03-09 06:17:52</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46484,7 +46484,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46499,17 +46499,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-09 05:47:58</t>
+          <t>2026-03-09 06:17:54</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46522,7 +46522,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>296</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46541,7 +46541,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46551,48 +46551,48 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="X207" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="W207" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="X207" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="AG207" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AG207" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
       <c r="AH207" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -46610,29 +46610,29 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>296</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="AO207" t="inlineStr">
+        <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
       <c r="AP207" t="inlineStr">
         <is>
           <t>4.9</t>
@@ -46650,17 +46650,17 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>296</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -46671,7 +46671,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -46720,7 +46720,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:00</t>
+          <t>2026-03-09 06:17:56</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46941,7 +46941,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:00</t>
+          <t>2026-03-09 06:17:56</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47162,7 +47162,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:00</t>
+          <t>2026-03-09 06:17:56</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47383,7 +47383,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:00</t>
+          <t>2026-03-09 06:17:56</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47589,7 +47589,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47604,17 +47604,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:02</t>
+          <t>2026-03-09 06:17:58</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47634,7 +47634,7 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>224</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -47644,7 +47644,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>852.0</t>
+          <t>852.3</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47654,7 +47654,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47664,17 +47664,17 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr">
@@ -47693,22 +47693,22 @@
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
@@ -47723,7 +47723,7 @@
       </c>
       <c r="AK212" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AL212" t="inlineStr">
@@ -47733,22 +47733,22 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>-6.2</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>-5.7</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>-6.9</t>
+          <t>-7.2</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>224</t>
         </is>
       </c>
       <c r="AT212" t="inlineStr">
@@ -47783,7 +47783,7 @@
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>852.0</t>
+          <t>852.3</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
@@ -47798,7 +47798,7 @@
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>852.0</t>
+          <t>852.3</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -47845,7 +47845,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:03</t>
+          <t>2026-03-09 06:18:00</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48086,7 +48086,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:03</t>
+          <t>2026-03-09 06:18:00</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48327,7 +48327,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:03</t>
+          <t>2026-03-09 06:18:00</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48568,7 +48568,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:03</t>
+          <t>2026-03-09 06:18:00</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48794,7 +48794,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48809,17 +48809,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:05</t>
+          <t>2026-03-09 06:18:02</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48834,22 +48834,22 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>179</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -48859,7 +48859,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -48869,12 +48869,12 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -48886,24 +48886,24 @@
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -48913,12 +48913,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -48928,22 +48928,22 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>05:00 - 05:30</t>
+          <t>05:30 - 06:00</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -48953,12 +48953,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -48968,42 +48968,42 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>179</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>1022.4</t>
+          <t>1022.5</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
@@ -49050,7 +49050,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:07</t>
+          <t>2026-03-09 06:18:04</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49291,7 +49291,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:07</t>
+          <t>2026-03-09 06:18:04</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49532,7 +49532,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:07</t>
+          <t>2026-03-09 06:18:04</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:07</t>
+          <t>2026-03-09 06:18:04</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50014,17 +50014,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:09</t>
+          <t>2026-03-09 06:18:06</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50247,7 +50247,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:11</t>
+          <t>2026-03-09 06:18:07</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50480,7 +50480,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:11</t>
+          <t>2026-03-09 06:18:07</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50713,7 +50713,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:11</t>
+          <t>2026-03-09 06:18:07</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -50946,7 +50946,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-09 05:48:11</t>
+          <t>2026-03-09 06:18:07</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51243,7 +51243,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51273,7 +51273,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51303,7 +51303,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51333,7 +51333,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51363,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51393,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51423,7 +51423,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51483,7 +51483,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51513,7 +51513,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51543,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51573,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51603,7 +51603,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51633,7 +51633,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51663,7 +51663,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51693,7 +51693,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51813,7 +51813,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51843,7 +51843,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51873,7 +51873,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51903,7 +51903,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51933,7 +51933,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52023,7 +52023,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52083,7 +52083,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52113,7 +52113,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52143,7 +52143,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52173,7 +52173,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52203,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52233,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52263,7 +52263,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52323,7 +52323,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52353,7 +52353,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52383,7 +52383,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52413,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52443,7 +52443,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52473,7 +52473,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52503,7 +52503,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>
@@ -52533,7 +52533,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T05:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T05:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:31</t>
+          <t>2026-03-09 08:45:29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:32</t>
+          <t>2026-03-09 08:45:31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:32</t>
+          <t>2026-03-09 08:45:31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:32</t>
+          <t>2026-03-09 08:45:31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:32</t>
+          <t>2026-03-09 08:45:31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1683,17 +1683,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:35</t>
+          <t>2026-03-09 08:45:33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:37</t>
+          <t>2026-03-09 08:45:35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:37</t>
+          <t>2026-03-09 08:45:35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:37</t>
+          <t>2026-03-09 08:45:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:37</t>
+          <t>2026-03-09 08:45:35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2848,17 +2848,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:39</t>
+          <t>2026-03-09 08:45:37</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:41</t>
+          <t>2026-03-09 08:45:38</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:41</t>
+          <t>2026-03-09 08:45:38</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:41</t>
+          <t>2026-03-09 08:45:38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:41</t>
+          <t>2026-03-09 08:45:38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:44</t>
+          <t>2026-03-09 08:45:41</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:45</t>
+          <t>2026-03-09 08:45:42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:45</t>
+          <t>2026-03-09 08:45:42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:45</t>
+          <t>2026-03-09 08:45:42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:45</t>
+          <t>2026-03-09 08:45:42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:48</t>
+          <t>2026-03-09 08:45:44</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:50</t>
+          <t>2026-03-09 08:45:46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:50</t>
+          <t>2026-03-09 08:45:46</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:50</t>
+          <t>2026-03-09 08:45:46</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:50</t>
+          <t>2026-03-09 08:45:46</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:52</t>
+          <t>2026-03-09 08:45:48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:54</t>
+          <t>2026-03-09 08:45:50</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:54</t>
+          <t>2026-03-09 08:45:50</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:54</t>
+          <t>2026-03-09 08:45:50</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:54</t>
+          <t>2026-03-09 08:45:50</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:57</t>
+          <t>2026-03-09 08:45:52</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:58</t>
+          <t>2026-03-09 08:45:53</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:58</t>
+          <t>2026-03-09 08:45:53</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:58</t>
+          <t>2026-03-09 08:45:53</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-09 08:15:58</t>
+          <t>2026-03-09 08:45:53</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:01</t>
+          <t>2026-03-09 08:45:56</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:03</t>
+          <t>2026-03-09 08:45:57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:03</t>
+          <t>2026-03-09 08:45:57</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:03</t>
+          <t>2026-03-09 08:45:57</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:03</t>
+          <t>2026-03-09 08:45:57</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:06</t>
+          <t>2026-03-09 08:46:00</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:07</t>
+          <t>2026-03-09 08:46:01</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:07</t>
+          <t>2026-03-09 08:46:01</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:07</t>
+          <t>2026-03-09 08:46:01</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:07</t>
+          <t>2026-03-09 08:46:01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10823,17 +10823,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:10</t>
+          <t>2026-03-09 08:46:03</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:11</t>
+          <t>2026-03-09 08:46:04</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:11</t>
+          <t>2026-03-09 08:46:04</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:11</t>
+          <t>2026-03-09 08:46:04</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:11</t>
+          <t>2026-03-09 08:46:04</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:14</t>
+          <t>2026-03-09 08:46:07</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:15</t>
+          <t>2026-03-09 08:46:08</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:15</t>
+          <t>2026-03-09 08:46:08</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:15</t>
+          <t>2026-03-09 08:46:08</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:15</t>
+          <t>2026-03-09 08:46:08</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12553,17 +12553,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:17</t>
+          <t>2026-03-09 08:46:10</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12794,7 +12794,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:19</t>
+          <t>2026-03-09 08:46:12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:19</t>
+          <t>2026-03-09 08:46:12</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:19</t>
+          <t>2026-03-09 08:46:12</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:19</t>
+          <t>2026-03-09 08:46:12</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:22</t>
+          <t>2026-03-09 08:46:14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:23</t>
+          <t>2026-03-09 08:46:15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:23</t>
+          <t>2026-03-09 08:46:15</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:23</t>
+          <t>2026-03-09 08:46:15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:23</t>
+          <t>2026-03-09 08:46:15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14863,17 +14863,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:26</t>
+          <t>2026-03-09 08:46:18</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:28</t>
+          <t>2026-03-09 08:46:19</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:28</t>
+          <t>2026-03-09 08:46:19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:28</t>
+          <t>2026-03-09 08:46:19</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:28</t>
+          <t>2026-03-09 08:46:19</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:30</t>
+          <t>2026-03-09 08:46:21</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:32</t>
+          <t>2026-03-09 08:46:22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:32</t>
+          <t>2026-03-09 08:46:22</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16427,7 +16427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:32</t>
+          <t>2026-03-09 08:46:22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:32</t>
+          <t>2026-03-09 08:46:22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:35</t>
+          <t>2026-03-09 08:46:25</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:37</t>
+          <t>2026-03-09 08:46:26</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:37</t>
+          <t>2026-03-09 08:46:26</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:37</t>
+          <t>2026-03-09 08:46:26</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:37</t>
+          <t>2026-03-09 08:46:26</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18058,17 +18058,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:40</t>
+          <t>2026-03-09 08:46:28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:41</t>
+          <t>2026-03-09 08:46:30</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:41</t>
+          <t>2026-03-09 08:46:30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18757,7 +18757,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:41</t>
+          <t>2026-03-09 08:46:30</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:41</t>
+          <t>2026-03-09 08:46:30</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:44</t>
+          <t>2026-03-09 08:46:32</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:46</t>
+          <t>2026-03-09 08:46:34</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:46</t>
+          <t>2026-03-09 08:46:34</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:46</t>
+          <t>2026-03-09 08:46:34</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:46</t>
+          <t>2026-03-09 08:46:34</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20328,17 +20328,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:48</t>
+          <t>2026-03-09 08:46:36</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20525,7 +20525,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:50</t>
+          <t>2026-03-09 08:46:37</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20758,7 +20758,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:50</t>
+          <t>2026-03-09 08:46:37</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:50</t>
+          <t>2026-03-09 08:46:37</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:50</t>
+          <t>2026-03-09 08:46:37</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21457,17 +21457,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:52</t>
+          <t>2026-03-09 08:46:39</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21690,7 +21690,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:54</t>
+          <t>2026-03-09 08:46:41</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:54</t>
+          <t>2026-03-09 08:46:41</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22156,7 +22156,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:54</t>
+          <t>2026-03-09 08:46:41</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:54</t>
+          <t>2026-03-09 08:46:41</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22622,17 +22622,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:57</t>
+          <t>2026-03-09 08:46:43</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22855,7 +22855,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:58</t>
+          <t>2026-03-09 08:46:45</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:58</t>
+          <t>2026-03-09 08:46:45</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23321,7 +23321,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:58</t>
+          <t>2026-03-09 08:46:45</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-09 08:16:58</t>
+          <t>2026-03-09 08:46:45</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23787,17 +23787,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:01</t>
+          <t>2026-03-09 08:46:47</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24020,7 +24020,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:03</t>
+          <t>2026-03-09 08:46:48</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:03</t>
+          <t>2026-03-09 08:46:48</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24486,7 +24486,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:03</t>
+          <t>2026-03-09 08:46:48</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24719,7 +24719,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:03</t>
+          <t>2026-03-09 08:46:48</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -24952,17 +24952,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:06</t>
+          <t>2026-03-09 08:46:51</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25185,7 +25185,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:07</t>
+          <t>2026-03-09 08:46:52</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25418,7 +25418,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:07</t>
+          <t>2026-03-09 08:46:52</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:07</t>
+          <t>2026-03-09 08:46:52</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25884,7 +25884,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:07</t>
+          <t>2026-03-09 08:46:52</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26117,17 +26117,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:10</t>
+          <t>2026-03-09 08:46:55</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26350,7 +26350,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:11</t>
+          <t>2026-03-09 08:46:56</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26583,7 +26583,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:11</t>
+          <t>2026-03-09 08:46:56</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:11</t>
+          <t>2026-03-09 08:46:56</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:11</t>
+          <t>2026-03-09 08:46:56</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27282,17 +27282,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:14</t>
+          <t>2026-03-09 08:46:59</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27523,7 +27523,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:16</t>
+          <t>2026-03-09 08:47:00</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27764,7 +27764,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:16</t>
+          <t>2026-03-09 08:47:00</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:16</t>
+          <t>2026-03-09 08:47:00</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28246,7 +28246,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:16</t>
+          <t>2026-03-09 08:47:00</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28487,17 +28487,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:19</t>
+          <t>2026-03-09 08:47:03</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:20</t>
+          <t>2026-03-09 08:47:04</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -28917,7 +28917,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:20</t>
+          <t>2026-03-09 08:47:04</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:20</t>
+          <t>2026-03-09 08:47:04</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29383,7 +29383,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:20</t>
+          <t>2026-03-09 08:47:04</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29616,17 +29616,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:23</t>
+          <t>2026-03-09 08:47:07</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29849,7 +29849,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:25</t>
+          <t>2026-03-09 08:47:08</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30082,7 +30082,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:25</t>
+          <t>2026-03-09 08:47:08</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:25</t>
+          <t>2026-03-09 08:47:08</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30548,7 +30548,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:25</t>
+          <t>2026-03-09 08:47:08</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30781,17 +30781,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:27</t>
+          <t>2026-03-09 08:47:10</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31002,7 +31002,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:29</t>
+          <t>2026-03-09 08:47:12</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31223,7 +31223,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:29</t>
+          <t>2026-03-09 08:47:12</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:29</t>
+          <t>2026-03-09 08:47:12</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:29</t>
+          <t>2026-03-09 08:47:12</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31886,17 +31886,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:31</t>
+          <t>2026-03-09 08:47:14</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:33</t>
+          <t>2026-03-09 08:47:15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32352,7 +32352,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:33</t>
+          <t>2026-03-09 08:47:15</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32585,7 +32585,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:33</t>
+          <t>2026-03-09 08:47:15</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:33</t>
+          <t>2026-03-09 08:47:15</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33051,17 +33051,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:36</t>
+          <t>2026-03-09 08:47:18</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:37</t>
+          <t>2026-03-09 08:47:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:37</t>
+          <t>2026-03-09 08:47:19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:37</t>
+          <t>2026-03-09 08:47:19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -33983,7 +33983,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:37</t>
+          <t>2026-03-09 08:47:19</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34216,17 +34216,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:40</t>
+          <t>2026-03-09 08:47:22</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34449,7 +34449,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:42</t>
+          <t>2026-03-09 08:47:23</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34682,7 +34682,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:42</t>
+          <t>2026-03-09 08:47:23</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -34915,7 +34915,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:42</t>
+          <t>2026-03-09 08:47:23</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35148,7 +35148,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:42</t>
+          <t>2026-03-09 08:47:23</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35381,17 +35381,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:45</t>
+          <t>2026-03-09 08:47:25</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35614,7 +35614,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:47</t>
+          <t>2026-03-09 08:47:27</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:47</t>
+          <t>2026-03-09 08:47:27</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36080,7 +36080,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:47</t>
+          <t>2026-03-09 08:47:27</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36313,7 +36313,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:47</t>
+          <t>2026-03-09 08:47:27</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36546,17 +36546,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:49</t>
+          <t>2026-03-09 08:47:29</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36755,7 +36755,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:50</t>
+          <t>2026-03-09 08:47:31</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -36996,7 +36996,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:50</t>
+          <t>2026-03-09 08:47:31</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37237,7 +37237,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:50</t>
+          <t>2026-03-09 08:47:31</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37478,7 +37478,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:50</t>
+          <t>2026-03-09 08:47:31</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37683,17 +37683,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:53</t>
+          <t>2026-03-09 08:47:33</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37924,7 +37924,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:55</t>
+          <t>2026-03-09 08:47:34</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38153,7 +38153,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:55</t>
+          <t>2026-03-09 08:47:34</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38382,7 +38382,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:55</t>
+          <t>2026-03-09 08:47:34</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38611,7 +38611,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:55</t>
+          <t>2026-03-09 08:47:34</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -38840,17 +38840,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:57</t>
+          <t>2026-03-09 08:47:37</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39073,7 +39073,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:59</t>
+          <t>2026-03-09 08:47:38</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39306,7 +39306,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:59</t>
+          <t>2026-03-09 08:47:38</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39539,7 +39539,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:59</t>
+          <t>2026-03-09 08:47:38</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-09 08:17:59</t>
+          <t>2026-03-09 08:47:38</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40005,17 +40005,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:02</t>
+          <t>2026-03-09 08:47:40</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40226,7 +40226,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:03</t>
+          <t>2026-03-09 08:47:42</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40447,7 +40447,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:03</t>
+          <t>2026-03-09 08:47:42</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40668,7 +40668,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:03</t>
+          <t>2026-03-09 08:47:42</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -40889,7 +40889,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:03</t>
+          <t>2026-03-09 08:47:42</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41110,17 +41110,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:06</t>
+          <t>2026-03-09 08:47:44</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41331,7 +41331,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:08</t>
+          <t>2026-03-09 08:47:45</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41552,7 +41552,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:08</t>
+          <t>2026-03-09 08:47:45</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41773,7 +41773,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:08</t>
+          <t>2026-03-09 08:47:45</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -41994,7 +41994,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:08</t>
+          <t>2026-03-09 08:47:45</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42215,17 +42215,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:11</t>
+          <t>2026-03-09 08:47:48</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42448,7 +42448,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:12</t>
+          <t>2026-03-09 08:47:49</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42681,7 +42681,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:12</t>
+          <t>2026-03-09 08:47:49</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -42914,7 +42914,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:12</t>
+          <t>2026-03-09 08:47:49</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43147,7 +43147,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:12</t>
+          <t>2026-03-09 08:47:49</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43380,17 +43380,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:15</t>
+          <t>2026-03-09 08:47:52</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43577,7 +43577,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:17</t>
+          <t>2026-03-09 08:47:53</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43774,7 +43774,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:17</t>
+          <t>2026-03-09 08:47:53</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -43971,7 +43971,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:17</t>
+          <t>2026-03-09 08:47:53</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:17</t>
+          <t>2026-03-09 08:47:53</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44365,17 +44365,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:19</t>
+          <t>2026-03-09 08:47:55</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:21</t>
+          <t>2026-03-09 08:47:57</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44831,7 +44831,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:21</t>
+          <t>2026-03-09 08:47:57</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45064,7 +45064,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:21</t>
+          <t>2026-03-09 08:47:57</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45297,7 +45297,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:21</t>
+          <t>2026-03-09 08:47:57</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45530,17 +45530,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:24</t>
+          <t>2026-03-09 08:47:59</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45703,7 +45703,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:25</t>
+          <t>2026-03-09 08:48:00</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:25</t>
+          <t>2026-03-09 08:48:00</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46049,7 +46049,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:25</t>
+          <t>2026-03-09 08:48:00</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46222,7 +46222,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:25</t>
+          <t>2026-03-09 08:48:00</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46395,17 +46395,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:28</t>
+          <t>2026-03-09 08:48:02</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46616,7 +46616,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:29</t>
+          <t>2026-03-09 08:48:04</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -46837,7 +46837,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:29</t>
+          <t>2026-03-09 08:48:04</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47058,7 +47058,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:29</t>
+          <t>2026-03-09 08:48:04</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47279,7 +47279,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:29</t>
+          <t>2026-03-09 08:48:04</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47500,17 +47500,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:32</t>
+          <t>2026-03-09 08:48:06</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47705,7 +47705,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:33</t>
+          <t>2026-03-09 08:48:08</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -47946,7 +47946,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:33</t>
+          <t>2026-03-09 08:48:08</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48187,7 +48187,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:33</t>
+          <t>2026-03-09 08:48:08</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48428,7 +48428,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:33</t>
+          <t>2026-03-09 08:48:08</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48669,17 +48669,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:36</t>
+          <t>2026-03-09 08:48:10</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48910,7 +48910,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:38</t>
+          <t>2026-03-09 08:48:12</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49151,7 +49151,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:38</t>
+          <t>2026-03-09 08:48:12</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49392,7 +49392,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:38</t>
+          <t>2026-03-09 08:48:12</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49633,7 +49633,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:38</t>
+          <t>2026-03-09 08:48:12</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -49874,17 +49874,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:41</t>
+          <t>2026-03-09 08:48:14</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50107,7 +50107,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:42</t>
+          <t>2026-03-09 08:48:16</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50340,7 +50340,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:42</t>
+          <t>2026-03-09 08:48:16</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50573,7 +50573,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:42</t>
+          <t>2026-03-09 08:48:16</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -50806,7 +50806,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-09 08:18:42</t>
+          <t>2026-03-09 08:48:16</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51073,7 +51073,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51103,7 +51103,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51133,7 +51133,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51163,7 +51163,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51193,7 +51193,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51223,7 +51223,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51253,7 +51253,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51283,7 +51283,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51313,7 +51313,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51343,7 +51343,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51373,7 +51373,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51403,7 +51403,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51433,7 +51433,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51463,7 +51463,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51493,7 +51493,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51523,7 +51523,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51553,7 +51553,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51583,7 +51583,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51613,7 +51613,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51643,7 +51643,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51673,7 +51673,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51703,7 +51703,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51733,7 +51733,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51763,7 +51763,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51823,7 +51823,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51853,7 +51853,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51883,7 +51883,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51913,7 +51913,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51943,7 +51943,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -51973,7 +51973,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52003,7 +52003,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52033,7 +52033,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52063,7 +52063,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52093,7 +52093,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52123,7 +52123,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52153,7 +52153,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52183,7 +52183,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZC&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52213,7 +52213,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52243,7 +52243,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52273,7 +52273,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52303,7 +52303,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52333,7 +52333,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>
@@ -52393,7 +52393,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T07:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-09T08:00Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:25</t>
+          <t>2026-03-11 02:15:28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -748,7 +748,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,22 +795,22 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -835,22 +835,22 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:26</t>
+          <t>2026-03-11 02:15:29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:26</t>
+          <t>2026-03-11 02:15:29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:26</t>
+          <t>2026-03-11 02:15:29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:26</t>
+          <t>2026-03-11 02:15:29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:29</t>
+          <t>2026-03-11 02:15:31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,17 +1732,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>108</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,96 +1763,96 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>-2.3</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1862,22 +1862,22 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:30</t>
+          <t>2026-03-11 02:15:33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:30</t>
+          <t>2026-03-11 02:15:33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:30</t>
+          <t>2026-03-11 02:15:33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:30</t>
+          <t>2026-03-11 02:15:33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:33</t>
+          <t>2026-03-11 02:15:35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>271</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1024.2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2928,51 +2928,51 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2987,32 +2987,32 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1024.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1024.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:34</t>
+          <t>2026-03-11 02:15:37</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:34</t>
+          <t>2026-03-11 02:15:37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:34</t>
+          <t>2026-03-11 02:15:37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:34</t>
+          <t>2026-03-11 02:15:37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:36</t>
+          <t>2026-03-11 02:15:39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4062,7 +4062,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>239</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4093,121 +4093,121 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
           <t>-2.4</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>-2.1</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
           <t>-2.4</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-2.6</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>-2.2</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-2.4</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>239</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:38</t>
+          <t>2026-03-11 02:15:41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:38</t>
+          <t>2026-03-11 02:15:41</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:38</t>
+          <t>2026-03-11 02:15:41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:38</t>
+          <t>2026-03-11 02:15:41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:40</t>
+          <t>2026-03-11 02:15:43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5258,98 +5258,98 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>8.3</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR22" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>205</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:42</t>
+          <t>2026-03-11 02:15:44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:42</t>
+          <t>2026-03-11 02:15:44</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:42</t>
+          <t>2026-03-11 02:15:44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:42</t>
+          <t>2026-03-11 02:15:44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:44</t>
+          <t>2026-03-11 02:15:47</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6403,7 +6403,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1023.9</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -6438,21 +6438,21 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -6467,54 +6467,54 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
           <t>11.7</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>4.7</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="AR27" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6522,22 +6522,22 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1023.9</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1023.9</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:46</t>
+          <t>2026-03-11 02:15:48</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:46</t>
+          <t>2026-03-11 02:15:48</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:46</t>
+          <t>2026-03-11 02:15:48</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:46</t>
+          <t>2026-03-11 02:15:48</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:48</t>
+          <t>2026-03-11 02:15:51</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -7563,12 +7563,12 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>1023.8</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7588,96 +7588,96 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -7687,22 +7687,22 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>1023.8</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>1023.8</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:49</t>
+          <t>2026-03-11 02:15:52</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:49</t>
+          <t>2026-03-11 02:15:52</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:49</t>
+          <t>2026-03-11 02:15:52</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:49</t>
+          <t>2026-03-11 02:15:52</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:52</t>
+          <t>2026-03-11 02:15:54</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8721,7 +8721,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>278</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8749,51 +8749,51 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
           <t>6.3</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>6.5</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
@@ -8808,32 +8808,32 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>278</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>278</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8869,7 +8869,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:53</t>
+          <t>2026-03-11 02:15:56</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:53</t>
+          <t>2026-03-11 02:15:56</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:53</t>
+          <t>2026-03-11 02:15:56</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:53</t>
+          <t>2026-03-11 02:15:56</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:56</t>
+          <t>2026-03-11 02:15:58</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -9859,31 +9859,31 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
@@ -9913,7 +9913,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
@@ -9974,7 +9974,7 @@
       <c r="AW42" t="inlineStr"/>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:57</t>
+          <t>2026-03-11 02:16:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:57</t>
+          <t>2026-03-11 02:16:00</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:57</t>
+          <t>2026-03-11 02:16:00</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:57</t>
+          <t>2026-03-11 02:16:00</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-11 01:45:59</t>
+          <t>2026-03-11 02:16:02</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10945,23 +10945,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10972,22 +10972,22 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -11004,22 +11004,22 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:01</t>
+          <t>2026-03-11 02:16:03</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:01</t>
+          <t>2026-03-11 02:16:03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:01</t>
+          <t>2026-03-11 02:16:03</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:01</t>
+          <t>2026-03-11 02:16:03</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:03</t>
+          <t>2026-03-11 02:16:06</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:04</t>
+          <t>2026-03-11 02:16:07</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:04</t>
+          <t>2026-03-11 02:16:07</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:04</t>
+          <t>2026-03-11 02:16:07</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:04</t>
+          <t>2026-03-11 02:16:07</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:07</t>
+          <t>2026-03-11 02:16:09</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>170</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12672,12 +12672,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1024.6</t>
+          <t>1024.7</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12697,141 +12697,141 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="AG57" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
       <c r="AH57" t="inlineStr">
         <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>1024.6</t>
+          <t>1024.7</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>1024.6</t>
+          <t>1024.7</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:08</t>
+          <t>2026-03-11 02:16:11</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:08</t>
+          <t>2026-03-11 02:16:11</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:08</t>
+          <t>2026-03-11 02:16:11</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:08</t>
+          <t>2026-03-11 02:16:11</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:11</t>
+          <t>2026-03-11 02:16:13</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>305</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -13899,7 +13899,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
@@ -13909,21 +13909,21 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
@@ -13953,17 +13953,17 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>305</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -13993,17 +13993,17 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>305</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -14014,7 +14014,7 @@
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:12</t>
+          <t>2026-03-11 02:16:15</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:12</t>
+          <t>2026-03-11 02:16:15</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:12</t>
+          <t>2026-03-11 02:16:15</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:12</t>
+          <t>2026-03-11 02:16:15</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:14</t>
+          <t>2026-03-11 02:16:17</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:15</t>
+          <t>2026-03-11 02:16:18</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:15</t>
+          <t>2026-03-11 02:16:18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:15</t>
+          <t>2026-03-11 02:16:18</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:15</t>
+          <t>2026-03-11 02:16:18</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:18</t>
+          <t>2026-03-11 02:16:21</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15835,14 +15835,14 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>203</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15868,98 +15868,98 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>-4.6</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
           <t>-3.9</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
+          <t>-4.6</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>-4.3</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
           <t>-3.9</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr">
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>-4.6</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>4.3</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>-3.6</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>-3.9</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="AR72" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15967,22 +15967,22 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15992,12 +15992,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>203</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:19</t>
+          <t>2026-03-11 02:16:22</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:19</t>
+          <t>2026-03-11 02:16:22</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:19</t>
+          <t>2026-03-11 02:16:22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:19</t>
+          <t>2026-03-11 02:16:22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:21</t>
+          <t>2026-03-11 02:16:24</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:23</t>
+          <t>2026-03-11 02:16:25</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:23</t>
+          <t>2026-03-11 02:16:25</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:23</t>
+          <t>2026-03-11 02:16:25</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:23</t>
+          <t>2026-03-11 02:16:25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:25</t>
+          <t>2026-03-11 02:16:28</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18165,7 +18165,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>316</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18178,7 +18178,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1024.5</t>
+          <t>1024.3</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -18188,7 +18188,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18198,22 +18198,22 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
@@ -18227,69 +18227,69 @@
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="AP82" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
-      <c r="AQ82" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="AR82" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18297,12 +18297,12 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>316</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>1024.5</t>
+          <t>1024.3</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>1024.5</t>
+          <t>1024.3</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:27</t>
+          <t>2026-03-11 02:16:29</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:27</t>
+          <t>2026-03-11 02:16:29</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:27</t>
+          <t>2026-03-11 02:16:29</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:27</t>
+          <t>2026-03-11 02:16:29</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:29</t>
+          <t>2026-03-11 02:16:31</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19359,17 +19359,17 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -19381,31 +19381,31 @@
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
       <c r="AI87" t="inlineStr">
         <is>
           <t>99</t>
@@ -19423,29 +19423,29 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
           <t>5.2</t>
         </is>
       </c>
-      <c r="AP87" t="inlineStr">
-        <is>
-          <t>4.9</t>
-        </is>
-      </c>
       <c r="AQ87" t="inlineStr">
         <is>
           <t>99</t>
@@ -19463,12 +19463,12 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -19479,7 +19479,7 @@
       <c r="AW87" t="inlineStr"/>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:31</t>
+          <t>2026-03-11 02:16:33</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:31</t>
+          <t>2026-03-11 02:16:33</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:31</t>
+          <t>2026-03-11 02:16:33</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:31</t>
+          <t>2026-03-11 02:16:33</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:33</t>
+          <t>2026-03-11 02:16:35</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20468,17 +20468,17 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
+          <t>-3.4</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>-3.6</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
           <t>-3.1</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>-3.3</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>-2.9</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -20497,22 +20497,22 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
+          <t>-3.4</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
@@ -20537,22 +20537,22 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
+          <t>-3.4</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
           <t>-3.1</t>
         </is>
       </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>-2.9</t>
-        </is>
-      </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:34</t>
+          <t>2026-03-11 02:16:37</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:34</t>
+          <t>2026-03-11 02:16:37</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:34</t>
+          <t>2026-03-11 02:16:37</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:34</t>
+          <t>2026-03-11 02:16:37</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:36</t>
+          <t>2026-03-11 02:16:39</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21600,7 +21600,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
@@ -21608,7 +21608,7 @@
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21633,56 +21633,56 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr"/>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -21692,37 +21692,37 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
           <t>7.7</t>
         </is>
       </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21732,17 +21732,17 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>190</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -21757,7 +21757,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:38</t>
+          <t>2026-03-11 02:16:41</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:38</t>
+          <t>2026-03-11 02:16:41</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:38</t>
+          <t>2026-03-11 02:16:41</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:38</t>
+          <t>2026-03-11 02:16:41</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22742,17 +22742,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:40</t>
+          <t>2026-03-11 02:16:43</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22777,18 +22777,18 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>94</t>
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22798,111 +22798,111 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
           <t>-3.4</t>
-        </is>
-      </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>-3.4</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>-3.2</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
           <t>-3.4</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr">
-        <is>
-          <t>-3.2</t>
-        </is>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
           <t>-3.4</t>
         </is>
       </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>14.8</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>-3.4</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>-3.2</t>
-        </is>
-      </c>
-      <c r="AP102" t="inlineStr">
-        <is>
-          <t>-3.4</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:42</t>
+          <t>2026-03-11 02:16:44</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:42</t>
+          <t>2026-03-11 02:16:44</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:42</t>
+          <t>2026-03-11 02:16:44</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:42</t>
+          <t>2026-03-11 02:16:44</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23907,17 +23907,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:44</t>
+          <t>2026-03-11 02:16:47</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23932,7 +23932,7 @@
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>34</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R107" t="inlineStr"/>
@@ -23953,7 +23953,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23968,31 +23968,31 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -24002,17 +24002,17 @@
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -24027,12 +24027,12 @@
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
@@ -24042,17 +24042,17 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.3</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -24067,17 +24067,17 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -24087,12 +24087,12 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:46</t>
+          <t>2026-03-11 02:16:48</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:46</t>
+          <t>2026-03-11 02:16:48</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:46</t>
+          <t>2026-03-11 02:16:48</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:46</t>
+          <t>2026-03-11 02:16:48</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25057,7 +25057,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25072,17 +25072,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:48</t>
+          <t>2026-03-11 02:16:50</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25095,7 +25095,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>121</t>
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
@@ -25108,7 +25108,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>1024.8</t>
+          <t>1024.9</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -25118,7 +25118,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25128,22 +25128,22 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr"/>
@@ -25157,22 +25157,22 @@
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
@@ -25187,32 +25187,32 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
@@ -25227,12 +25227,12 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>121</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
@@ -25242,7 +25242,7 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>1024.8</t>
+          <t>1024.9</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>1024.8</t>
+          <t>1024.9</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:49</t>
+          <t>2026-03-11 02:16:52</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:49</t>
+          <t>2026-03-11 02:16:52</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:49</t>
+          <t>2026-03-11 02:16:52</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:49</t>
+          <t>2026-03-11 02:16:52</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26222,7 +26222,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -26237,17 +26237,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:52</t>
+          <t>2026-03-11 02:16:54</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26262,7 +26262,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -26272,7 +26272,7 @@
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R117" t="inlineStr"/>
@@ -26283,7 +26283,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -26298,31 +26298,31 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -26332,17 +26332,17 @@
       </c>
       <c r="AG117" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -26357,12 +26357,12 @@
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
@@ -26372,17 +26372,17 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
@@ -26397,17 +26397,17 @@
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -26417,12 +26417,12 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:53</t>
+          <t>2026-03-11 02:16:56</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:53</t>
+          <t>2026-03-11 02:16:56</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:53</t>
+          <t>2026-03-11 02:16:56</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:53</t>
+          <t>2026-03-11 02:16:56</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,17 +27402,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:56</t>
+          <t>2026-03-11 02:16:58</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:57</t>
+          <t>2026-03-11 02:17:00</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:57</t>
+          <t>2026-03-11 02:17:00</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:57</t>
+          <t>2026-03-11 02:17:00</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:57</t>
+          <t>2026-03-11 02:17:00</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28607,17 +28607,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-11 01:46:59</t>
+          <t>2026-03-11 02:17:02</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28630,7 +28630,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28653,7 +28653,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28668,31 +28668,31 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -28702,82 +28702,82 @@
       </c>
       <c r="AG127" t="inlineStr">
         <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN127" t="inlineStr">
+        <is>
           <t>-2.3</t>
         </is>
       </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>-2.3</t>
-        </is>
-      </c>
-      <c r="AP127" t="inlineStr">
-        <is>
-          <t>-2.5</t>
-        </is>
-      </c>
-      <c r="AQ127" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -28787,12 +28787,12 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>227</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:01</t>
+          <t>2026-03-11 02:17:03</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:01</t>
+          <t>2026-03-11 02:17:03</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:01</t>
+          <t>2026-03-11 02:17:03</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:01</t>
+          <t>2026-03-11 02:17:03</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29757,7 +29757,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29772,17 +29772,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:03</t>
+          <t>2026-03-11 02:17:06</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>261</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -29803,12 +29803,12 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -29818,7 +29818,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -29828,12 +29828,12 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -29843,26 +29843,26 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AG132" t="inlineStr">
@@ -29872,12 +29872,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -29887,22 +29887,22 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -29912,12 +29912,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -29927,22 +29927,22 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>261</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
@@ -29952,12 +29952,12 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>1024.1</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:04</t>
+          <t>2026-03-11 02:17:07</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:04</t>
+          <t>2026-03-11 02:17:07</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:04</t>
+          <t>2026-03-11 02:17:07</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:04</t>
+          <t>2026-03-11 02:17:07</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30937,17 +30937,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:06</t>
+          <t>2026-03-11 02:17:09</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:08</t>
+          <t>2026-03-11 02:17:11</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:08</t>
+          <t>2026-03-11 02:17:11</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:08</t>
+          <t>2026-03-11 02:17:11</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:08</t>
+          <t>2026-03-11 02:17:11</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32027,7 +32027,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -32042,17 +32042,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:10</t>
+          <t>2026-03-11 02:17:13</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32065,7 +32065,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32078,7 +32078,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1024.2</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -32088,7 +32088,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32098,7 +32098,7 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
@@ -32108,7 +32108,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -32120,24 +32120,24 @@
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
@@ -32162,22 +32162,22 @@
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
@@ -32202,17 +32202,17 @@
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>1024.2</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
@@ -32222,12 +32222,12 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>1024.2</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:12</t>
+          <t>2026-03-11 02:17:15</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:12</t>
+          <t>2026-03-11 02:17:15</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:12</t>
+          <t>2026-03-11 02:17:15</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:12</t>
+          <t>2026-03-11 02:17:15</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33207,17 +33207,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:14</t>
+          <t>2026-03-11 02:17:17</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:15</t>
+          <t>2026-03-11 02:17:19</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33673,7 +33673,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:15</t>
+          <t>2026-03-11 02:17:19</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33906,7 +33906,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:15</t>
+          <t>2026-03-11 02:17:19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:15</t>
+          <t>2026-03-11 02:17:19</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34357,7 +34357,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34372,17 +34372,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:18</t>
+          <t>2026-03-11 02:17:21</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34396,7 +34396,7 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>99</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
@@ -34418,7 +34418,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34428,17 +34428,17 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
           <t>-0.3</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>0.8</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr"/>
@@ -34451,98 +34451,98 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN152" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL152" t="inlineStr">
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT152" t="inlineStr">
         <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT152" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34552,12 +34552,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34605,7 +34605,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:19</t>
+          <t>2026-03-11 02:17:22</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:19</t>
+          <t>2026-03-11 02:17:22</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35071,7 +35071,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:19</t>
+          <t>2026-03-11 02:17:22</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35304,7 +35304,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:19</t>
+          <t>2026-03-11 02:17:22</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35537,17 +35537,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:22</t>
+          <t>2026-03-11 02:17:24</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35770,7 +35770,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:23</t>
+          <t>2026-03-11 02:17:26</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -36003,7 +36003,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:23</t>
+          <t>2026-03-11 02:17:26</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:23</t>
+          <t>2026-03-11 02:17:26</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36469,7 +36469,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:23</t>
+          <t>2026-03-11 02:17:26</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36702,17 +36702,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:26</t>
+          <t>2026-03-11 02:17:28</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36943,7 +36943,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:27</t>
+          <t>2026-03-11 02:17:30</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37184,7 +37184,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:27</t>
+          <t>2026-03-11 02:17:30</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37425,7 +37425,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:27</t>
+          <t>2026-03-11 02:17:30</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37666,7 +37666,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:27</t>
+          <t>2026-03-11 02:17:30</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37892,7 +37892,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37907,17 +37907,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:30</t>
+          <t>2026-03-11 02:17:32</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37930,16 +37930,12 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>34</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
           <t>100</t>
@@ -37947,17 +37943,17 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1026.5</t>
+          <t>1026.6</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37967,7 +37963,7 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
@@ -37977,131 +37973,123 @@
       </c>
       <c r="X167" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
           <t>1.4</t>
-        </is>
-      </c>
-      <c r="Y167" t="inlineStr">
-        <is>
-          <t>0.7</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr"/>
+      <c r="AL167" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="AH167" t="inlineStr">
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
+      <c r="AQ167" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL167" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="AM167" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>1.2</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="AP167" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AT167" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>1026.5</t>
+          <t>1026.6</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>1026.5</t>
+          <t>1026.6</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
@@ -38148,7 +38136,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:31</t>
+          <t>2026-03-11 02:17:33</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38389,7 +38377,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:31</t>
+          <t>2026-03-11 02:17:33</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38618,7 +38606,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:31</t>
+          <t>2026-03-11 02:17:33</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38847,7 +38835,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:31</t>
+          <t>2026-03-11 02:17:33</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39061,7 +39049,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -39076,17 +39064,17 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:34</t>
+          <t>2026-03-11 02:17:36</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K172" t="n">
@@ -39099,7 +39087,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>324</t>
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
@@ -39112,7 +39100,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>1024.2</t>
+          <t>1023.9</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
@@ -39122,7 +39110,7 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U172" t="inlineStr">
@@ -39132,51 +39120,51 @@
       </c>
       <c r="V172" t="inlineStr">
         <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr"/>
       <c r="AA172" t="inlineStr"/>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="inlineStr"/>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
         <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
       <c r="AH172" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AI172" t="inlineStr">
@@ -39191,77 +39179,77 @@
       </c>
       <c r="AK172" t="inlineStr">
         <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN172" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AP172" t="inlineStr">
-        <is>
-          <t>7.9</t>
-        </is>
-      </c>
-      <c r="AQ172" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr">
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>1023.9</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="AT172" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AV172" t="inlineStr">
-        <is>
-          <t>1024.2</t>
-        </is>
-      </c>
-      <c r="AW172" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX172" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>1024.2</t>
+          <t>1023.9</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
@@ -39309,7 +39297,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:35</t>
+          <t>2026-03-11 02:17:37</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39542,7 +39530,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:35</t>
+          <t>2026-03-11 02:17:37</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39775,7 +39763,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:35</t>
+          <t>2026-03-11 02:17:37</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -40008,7 +39996,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:35</t>
+          <t>2026-03-11 02:17:37</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40226,7 +40214,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40241,17 +40229,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:37</t>
+          <t>2026-03-11 02:17:39</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40264,7 +40252,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40272,12 +40260,12 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>97</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>1026.9</t>
+          <t>1026.8</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
@@ -40287,102 +40275,102 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>97</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40392,33 +40380,33 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>1026.9</t>
+          <t>1026.8</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>1026.9</t>
+          <t>1026.8</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr"/>
@@ -40462,7 +40450,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:39</t>
+          <t>2026-03-11 02:17:41</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40683,7 +40671,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:39</t>
+          <t>2026-03-11 02:17:41</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40904,7 +40892,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:39</t>
+          <t>2026-03-11 02:17:41</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41125,7 +41113,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:39</t>
+          <t>2026-03-11 02:17:41</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41331,7 +41319,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -41346,17 +41334,17 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:41</t>
+          <t>2026-03-11 02:17:43</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -41369,7 +41357,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>290</t>
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
@@ -41377,7 +41365,7 @@
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="R182" t="inlineStr"/>
@@ -41388,7 +41376,7 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U182" t="inlineStr">
@@ -41398,56 +41386,56 @@
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>6.6</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr"/>
       <c r="AA182" t="inlineStr"/>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="inlineStr"/>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
         <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="AG182" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="AG182" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -41457,37 +41445,37 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>290</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
           <t>6.9</t>
         </is>
       </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>7.2</t>
-        </is>
-      </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>99</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
@@ -41497,17 +41485,17 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>290</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
@@ -41518,7 +41506,7 @@
       <c r="AW182" t="inlineStr"/>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -41567,7 +41555,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:42</t>
+          <t>2026-03-11 02:17:45</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41788,7 +41776,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:42</t>
+          <t>2026-03-11 02:17:45</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -42009,7 +41997,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:42</t>
+          <t>2026-03-11 02:17:45</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42218,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:42</t>
+          <t>2026-03-11 02:17:45</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42451,7 +42439,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:50</t>
+          <t>2026-03-11 02:17:53</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42684,7 +42672,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:51</t>
+          <t>2026-03-11 02:17:55</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42917,7 +42905,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:51</t>
+          <t>2026-03-11 02:17:55</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43150,7 +43138,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:51</t>
+          <t>2026-03-11 02:17:55</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43383,7 +43371,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:51</t>
+          <t>2026-03-11 02:17:55</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43601,7 +43589,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43616,17 +43604,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:53</t>
+          <t>2026-03-11 02:17:57</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43640,15 +43628,19 @@
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1024.2</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43658,23 +43650,23 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U192" t="inlineStr"/>
       <c r="V192" t="inlineStr">
         <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr"/>
@@ -43685,63 +43677,67 @@
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="AG192" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="AG192" t="inlineStr">
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>1024.2</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr"/>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>1024.4</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>7.8</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>7.7</t>
-        </is>
-      </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -43749,10 +43745,14 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="AS192" t="inlineStr"/>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>1024.4</t>
+          <t>1024.2</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr"/>
@@ -43801,7 +43801,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:54</t>
+          <t>2026-03-11 02:17:58</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43998,7 +43998,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:54</t>
+          <t>2026-03-11 02:17:58</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44195,7 +44195,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:54</t>
+          <t>2026-03-11 02:17:58</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44392,7 +44392,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:54</t>
+          <t>2026-03-11 02:17:58</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44574,7 +44574,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44589,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:56</t>
+          <t>2026-03-11 02:18:01</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N197" t="inlineStr"/>
@@ -44620,7 +44620,7 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>96</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
@@ -44635,7 +44635,7 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U197" t="inlineStr">
@@ -44650,7 +44650,7 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -44667,14 +44667,14 @@
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -44689,72 +44689,72 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AL197" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN197" t="inlineStr">
+        <is>
           <t>9.2</t>
         </is>
       </c>
-      <c r="AI197" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AJ197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
       </c>
-      <c r="AL197" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AM197" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="AQ197" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
@@ -44769,7 +44769,7 @@
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -44822,7 +44822,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:57</t>
+          <t>2026-03-11 02:18:02</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -45055,7 +45055,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:57</t>
+          <t>2026-03-11 02:18:02</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:57</t>
+          <t>2026-03-11 02:18:02</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45521,7 +45521,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-11 01:47:57</t>
+          <t>2026-03-11 02:18:02</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45739,7 +45739,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45754,17 +45754,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:00</t>
+          <t>2026-03-11 02:18:04</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45792,18 +45792,18 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U202" t="inlineStr"/>
       <c r="V202" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
@@ -45819,12 +45819,12 @@
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
@@ -45834,7 +45834,7 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
@@ -45851,12 +45851,12 @@
       <c r="AL202" t="inlineStr"/>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -45866,7 +45866,7 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
@@ -45927,7 +45927,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:01</t>
+          <t>2026-03-11 02:18:05</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -46100,7 +46100,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:01</t>
+          <t>2026-03-11 02:18:05</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46273,7 +46273,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:01</t>
+          <t>2026-03-11 02:18:05</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46446,7 +46446,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:01</t>
+          <t>2026-03-11 02:18:05</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46604,7 +46604,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46619,17 +46619,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:04</t>
+          <t>2026-03-11 02:18:08</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>208</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46661,7 +46661,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46671,51 +46671,51 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
@@ -46730,32 +46730,32 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
@@ -46770,17 +46770,17 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
@@ -46791,7 +46791,7 @@
       <c r="AW207" t="inlineStr"/>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -46840,7 +46840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:05</t>
+          <t>2026-03-11 02:18:09</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47061,7 +47061,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:05</t>
+          <t>2026-03-11 02:18:09</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:05</t>
+          <t>2026-03-11 02:18:09</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47503,7 +47503,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:05</t>
+          <t>2026-03-11 02:18:09</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47709,7 +47709,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47724,17 +47724,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:07</t>
+          <t>2026-03-11 02:18:12</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47747,7 +47747,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N212" t="inlineStr"/>
@@ -47764,7 +47764,7 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>854.4</t>
+          <t>854.5</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47774,7 +47774,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47784,141 +47784,141 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="W212" t="inlineStr">
         <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr"/>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr"/>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AG212" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AH212" t="inlineStr">
         <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="AL212" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>01:30 - 02:00</t>
+        </is>
+      </c>
+      <c r="AN212" t="inlineStr">
+        <is>
+          <t>-2.1</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
           <t>-1.9</t>
         </is>
       </c>
-      <c r="AI212" t="inlineStr">
+      <c r="AP212" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="AQ212" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
+      <c r="AR212" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS212" t="inlineStr">
         <is>
           <t>220</t>
         </is>
       </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>12.6</t>
-        </is>
-      </c>
-      <c r="AM212" t="inlineStr">
-        <is>
-          <t>01:00 - 01:30</t>
-        </is>
-      </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>-1.7</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="AP212" t="inlineStr">
-        <is>
-          <t>-1.9</t>
-        </is>
-      </c>
-      <c r="AQ212" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS212" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>854.4</t>
+          <t>854.5</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>854.4</t>
+          <t>854.5</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -47965,7 +47965,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:09</t>
+          <t>2026-03-11 02:18:13</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48206,7 +48206,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:09</t>
+          <t>2026-03-11 02:18:13</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48447,7 +48447,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:09</t>
+          <t>2026-03-11 02:18:13</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48688,7 +48688,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:09</t>
+          <t>2026-03-11 02:18:13</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48914,7 +48914,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48929,17 +48929,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:11</t>
+          <t>2026-03-11 02:18:15</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48954,22 +48954,22 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>194</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1026.0</t>
+          <t>1025.7</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -48979,7 +48979,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -48989,56 +48989,56 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="Y217" t="inlineStr"/>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr"/>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -49048,37 +49048,37 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -49088,42 +49088,42 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>1026.0</t>
+          <t>1025.7</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>1026.0</t>
+          <t>1025.7</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:13</t>
+          <t>2026-03-11 02:18:17</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49411,7 +49411,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:13</t>
+          <t>2026-03-11 02:18:17</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49652,7 +49652,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:13</t>
+          <t>2026-03-11 02:18:17</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49893,7 +49893,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:13</t>
+          <t>2026-03-11 02:18:17</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50119,7 +50119,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -50134,17 +50134,17 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:15</t>
+          <t>2026-03-11 02:18:19</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
       <c r="K222" t="n">
@@ -50157,7 +50157,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -50180,7 +50180,7 @@
       </c>
       <c r="T222" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="U222" t="inlineStr">
@@ -50195,31 +50195,31 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Z222" t="inlineStr"/>
       <c r="AA222" t="inlineStr"/>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AC222" t="inlineStr"/>
       <c r="AD222" t="inlineStr"/>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -50229,12 +50229,12 @@
       </c>
       <c r="AG222" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
@@ -50249,17 +50249,17 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>01:00 - 01:30</t>
+          <t>01:30 - 02:00</t>
         </is>
       </c>
       <c r="AN222" t="inlineStr">
@@ -50269,12 +50269,12 @@
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
@@ -50289,17 +50289,17 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
@@ -50314,7 +50314,7 @@
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
@@ -50367,7 +50367,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:16</t>
+          <t>2026-03-11 02:18:21</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -50600,7 +50600,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:16</t>
+          <t>2026-03-11 02:18:21</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -50833,7 +50833,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:16</t>
+          <t>2026-03-11 02:18:21</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -51066,7 +51066,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>2026-03-11 01:48:16</t>
+          <t>2026-03-11 02:18:21</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -51333,7 +51333,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51363,7 +51363,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51393,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51423,7 +51423,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51453,7 +51453,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51483,7 +51483,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51513,7 +51513,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51543,7 +51543,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51573,7 +51573,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51603,7 +51603,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51633,7 +51633,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51663,7 +51663,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51693,7 +51693,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51723,7 +51723,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51753,7 +51753,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51783,7 +51783,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51813,7 +51813,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51843,7 +51843,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51873,7 +51873,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51903,7 +51903,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51933,7 +51933,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51963,7 +51963,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -51993,7 +51993,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52023,7 +52023,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52053,7 +52053,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52083,7 +52083,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52113,7 +52113,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52143,7 +52143,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52173,7 +52173,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52203,7 +52203,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52233,7 +52233,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52263,7 +52263,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52293,7 +52293,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52323,7 +52323,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52353,7 +52353,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52383,7 +52383,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CI&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52413,7 +52413,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52473,7 +52473,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52503,7 +52503,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52533,7 +52533,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52563,7 +52563,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52593,7 +52593,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52623,7 +52623,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>
@@ -52653,7 +52653,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-11T01:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-11T01:30Z</t>
         </is>
       </c>
     </row>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:26</t>
+          <t>2026-03-16 01:45:29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -748,12 +748,12 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,27 +795,27 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.7</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:28</t>
+          <t>2026-03-16 01:45:31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:28</t>
+          <t>2026-03-16 01:45:31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:28</t>
+          <t>2026-03-16 01:45:31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:28</t>
+          <t>2026-03-16 01:45:31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:30</t>
+          <t>2026-03-16 01:45:33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,7 +1732,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>263</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1773,36 +1773,36 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1827,22 +1827,22 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:32</t>
+          <t>2026-03-16 01:45:35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:32</t>
+          <t>2026-03-16 01:45:35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:32</t>
+          <t>2026-03-16 01:45:35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:32</t>
+          <t>2026-03-16 01:45:35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:34</t>
+          <t>2026-03-16 01:45:38</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>294</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2928,98 +2928,98 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="AR12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3027,22 +3027,22 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:36</t>
+          <t>2026-03-16 01:45:40</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:36</t>
+          <t>2026-03-16 01:45:40</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:36</t>
+          <t>2026-03-16 01:45:40</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:36</t>
+          <t>2026-03-16 01:45:40</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:39</t>
+          <t>2026-03-16 01:45:42</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4038,7 +4038,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>313</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>84</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4069,121 +4069,121 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>-8.8</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
           <t>-9.2</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-9.3</t>
-        </is>
-      </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-8.7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>-8.8</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>-8.7</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
           <t>-9.2</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>11.9</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>-8.8</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>-8.7</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
         <is>
           <t>-9.2</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-9.3</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>-9.2</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>-9.2</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-9.3</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:41</t>
+          <t>2026-03-16 01:45:44</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:41</t>
+          <t>2026-03-16 01:45:44</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:41</t>
+          <t>2026-03-16 01:45:44</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:41</t>
+          <t>2026-03-16 01:45:44</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:43</t>
+          <t>2026-03-16 01:45:46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>222</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5209,12 +5209,12 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5234,56 +5234,56 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5293,37 +5293,37 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:45</t>
+          <t>2026-03-16 01:45:48</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:45</t>
+          <t>2026-03-16 01:45:48</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:45</t>
+          <t>2026-03-16 01:45:48</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-16 01:15:45</t>
+          <t>2026-03-16 01:45:48</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:03</t>
+          <t>2026-03-16 01:46:05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>335</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6374,12 +6374,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.3</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -6409,36 +6409,36 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6458,27 +6458,27 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.3</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1017.3</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:05</t>
+          <t>2026-03-16 01:46:07</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:05</t>
+          <t>2026-03-16 01:46:07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:05</t>
+          <t>2026-03-16 01:46:07</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:05</t>
+          <t>2026-03-16 01:46:07</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:07</t>
+          <t>2026-03-16 01:46:09</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7532,14 +7532,14 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -7576,25 +7576,25 @@
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -7619,22 +7619,22 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -7680,7 +7680,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:09</t>
+          <t>2026-03-16 01:46:11</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:09</t>
+          <t>2026-03-16 01:46:11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:09</t>
+          <t>2026-03-16 01:46:11</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:09</t>
+          <t>2026-03-16 01:46:11</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:11</t>
+          <t>2026-03-16 01:46:13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:13</t>
+          <t>2026-03-16 01:46:15</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:13</t>
+          <t>2026-03-16 01:46:15</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:13</t>
+          <t>2026-03-16 01:46:15</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:13</t>
+          <t>2026-03-16 01:46:15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:15</t>
+          <t>2026-03-16 01:46:18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9745,7 +9745,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -9756,23 +9756,23 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -9783,27 +9783,27 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -9815,27 +9815,27 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:17</t>
+          <t>2026-03-16 01:46:19</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:17</t>
+          <t>2026-03-16 01:46:19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:17</t>
+          <t>2026-03-16 01:46:19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:17</t>
+          <t>2026-03-16 01:46:19</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10583,17 +10583,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:20</t>
+          <t>2026-03-16 01:46:21</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10621,18 +10621,18 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -10648,12 +10648,12 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AG47" t="inlineStr">
@@ -10663,7 +10663,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -10680,12 +10680,12 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:21</t>
+          <t>2026-03-16 01:46:23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:21</t>
+          <t>2026-03-16 01:46:23</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:21</t>
+          <t>2026-03-16 01:46:23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:21</t>
+          <t>2026-03-16 01:46:23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11448,17 +11448,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:24</t>
+          <t>2026-03-16 01:46:25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -11508,56 +11508,56 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -11572,32 +11572,32 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -11632,12 +11632,12 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:25</t>
+          <t>2026-03-16 01:46:27</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:25</t>
+          <t>2026-03-16 01:46:27</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:25</t>
+          <t>2026-03-16 01:46:27</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:25</t>
+          <t>2026-03-16 01:46:27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:28</t>
+          <t>2026-03-16 01:46:29</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>326</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12684,7 +12684,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12705,56 +12705,56 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -12764,37 +12764,37 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -12804,17 +12804,17 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -12825,7 +12825,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:29</t>
+          <t>2026-03-16 01:46:31</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:29</t>
+          <t>2026-03-16 01:46:31</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:29</t>
+          <t>2026-03-16 01:46:31</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:29</t>
+          <t>2026-03-16 01:46:31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:32</t>
+          <t>2026-03-16 01:46:33</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13785,7 +13785,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13796,23 +13796,23 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -13823,27 +13823,27 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -13855,27 +13855,27 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:33</t>
+          <t>2026-03-16 01:46:35</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:33</t>
+          <t>2026-03-16 01:46:35</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:33</t>
+          <t>2026-03-16 01:46:35</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:33</t>
+          <t>2026-03-16 01:46:35</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:35</t>
+          <t>2026-03-16 01:46:37</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>181</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -14679,56 +14679,56 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -14743,32 +14743,32 @@
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-2.6</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.2</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>181</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>181</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:37</t>
+          <t>2026-03-16 01:46:38</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:37</t>
+          <t>2026-03-16 01:46:38</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:37</t>
+          <t>2026-03-16 01:46:38</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:37</t>
+          <t>2026-03-16 01:46:38</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15788,17 +15788,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:40</t>
+          <t>2026-03-16 01:46:41</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15844,51 +15844,51 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -15908,27 +15908,27 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -15948,17 +15948,17 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15968,12 +15968,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:41</t>
+          <t>2026-03-16 01:46:42</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:41</t>
+          <t>2026-03-16 01:46:42</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:41</t>
+          <t>2026-03-16 01:46:42</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:41</t>
+          <t>2026-03-16 01:46:42</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16953,17 +16953,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:44</t>
+          <t>2026-03-16 01:46:45</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>351</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -16984,12 +16984,12 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -17009,56 +17009,56 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -17068,37 +17068,37 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -17108,22 +17108,22 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>351</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:45</t>
+          <t>2026-03-16 01:46:46</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:45</t>
+          <t>2026-03-16 01:46:46</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:45</t>
+          <t>2026-03-16 01:46:46</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:45</t>
+          <t>2026-03-16 01:46:46</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18118,17 +18118,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:47</t>
+          <t>2026-03-16 01:46:49</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18149,7 +18149,7 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18170,12 +18170,12 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -18185,26 +18185,26 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
@@ -18214,12 +18214,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -18229,22 +18229,22 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -18254,12 +18254,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
@@ -18269,17 +18269,17 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -18290,7 +18290,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:49</t>
+          <t>2026-03-16 01:46:50</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:49</t>
+          <t>2026-03-16 01:46:50</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:49</t>
+          <t>2026-03-16 01:46:50</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:49</t>
+          <t>2026-03-16 01:46:50</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:52</t>
+          <t>2026-03-16 01:46:53</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19246,7 +19246,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>286</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19258,7 +19258,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19279,56 +19279,56 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19343,32 +19343,32 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-4.3</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.6</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19383,17 +19383,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>286</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>286</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:54</t>
+          <t>2026-03-16 01:46:54</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:54</t>
+          <t>2026-03-16 01:46:54</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:54</t>
+          <t>2026-03-16 01:46:54</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:54</t>
+          <t>2026-03-16 01:46:54</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20388,17 +20388,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:56</t>
+          <t>2026-03-16 01:46:57</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20419,12 +20419,12 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1022.5</t>
+          <t>1022.6</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20444,56 +20444,56 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -20503,37 +20503,37 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -20543,22 +20543,22 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>1022.5</t>
+          <t>1022.6</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -20568,12 +20568,12 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>1022.5</t>
+          <t>1022.6</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:57</t>
+          <t>2026-03-16 01:46:59</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:57</t>
+          <t>2026-03-16 01:46:59</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:57</t>
+          <t>2026-03-16 01:46:59</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-16 01:16:57</t>
+          <t>2026-03-16 01:46:59</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21553,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:00</t>
+          <t>2026-03-16 01:47:01</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21578,7 +21578,7 @@
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>342</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R97" t="inlineStr"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21609,56 +21609,56 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -21673,32 +21673,32 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21713,17 +21713,17 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -21733,12 +21733,12 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>63.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:02</t>
+          <t>2026-03-16 01:47:03</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:02</t>
+          <t>2026-03-16 01:47:03</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:02</t>
+          <t>2026-03-16 01:47:03</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:02</t>
+          <t>2026-03-16 01:47:03</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22703,7 +22703,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22718,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:04</t>
+          <t>2026-03-16 01:47:05</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22743,7 +22743,7 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22774,12 +22774,12 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -22791,24 +22791,24 @@
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
@@ -22818,12 +22818,12 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -22838,17 +22838,17 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.8</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -22858,12 +22858,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-7.1</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -22878,17 +22878,17 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:06</t>
+          <t>2026-03-16 01:47:07</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:06</t>
+          <t>2026-03-16 01:47:07</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:06</t>
+          <t>2026-03-16 01:47:07</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:06</t>
+          <t>2026-03-16 01:47:07</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:09</t>
+          <t>2026-03-16 01:47:09</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>278</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -23914,12 +23914,12 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1020.2</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -23929,7 +23929,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23939,96 +23939,96 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -24038,22 +24038,22 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>278</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1020.2</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -24063,12 +24063,12 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>1020.0</t>
+          <t>1020.2</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:10</t>
+          <t>2026-03-16 01:47:10</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:10</t>
+          <t>2026-03-16 01:47:10</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:10</t>
+          <t>2026-03-16 01:47:10</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:10</t>
+          <t>2026-03-16 01:47:10</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25048,17 +25048,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:13</t>
+          <t>2026-03-16 01:47:13</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25073,7 +25073,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R112" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25104,17 +25104,17 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr"/>
@@ -25128,32 +25128,32 @@
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -25173,27 +25173,27 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -25213,12 +25213,12 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25228,12 +25228,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:14</t>
+          <t>2026-03-16 01:47:15</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:14</t>
+          <t>2026-03-16 01:47:15</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:14</t>
+          <t>2026-03-16 01:47:15</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:14</t>
+          <t>2026-03-16 01:47:15</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:20</t>
+          <t>2026-03-16 01:47:22</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:22</t>
+          <t>2026-03-16 01:47:23</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:22</t>
+          <t>2026-03-16 01:47:23</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:22</t>
+          <t>2026-03-16 01:47:23</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27177,7 +27177,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:22</t>
+          <t>2026-03-16 01:47:23</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27403,7 +27403,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -27418,17 +27418,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:24</t>
+          <t>2026-03-16 01:47:26</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27441,7 +27441,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>78</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -27453,7 +27453,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R122" t="inlineStr"/>
@@ -27464,7 +27464,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -27474,121 +27474,121 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AG122" t="inlineStr">
         <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN122" t="inlineStr">
+        <is>
           <t>-3.5</t>
         </is>
       </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>-5.4</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="AL122" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>-4.7</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>-3.5</t>
-        </is>
-      </c>
-      <c r="AP122" t="inlineStr">
-        <is>
-          <t>-5.4</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
       <c r="AT122" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
@@ -27598,12 +27598,12 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
@@ -27651,7 +27651,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:26</t>
+          <t>2026-03-16 01:47:27</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:26</t>
+          <t>2026-03-16 01:47:27</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:26</t>
+          <t>2026-03-16 01:47:27</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:26</t>
+          <t>2026-03-16 01:47:27</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28568,7 +28568,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28583,17 +28583,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:28</t>
+          <t>2026-03-16 01:47:29</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28606,7 +28606,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>229</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28614,12 +28614,12 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.4</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -28629,7 +28629,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28639,17 +28639,17 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -28668,27 +28668,27 @@
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -28703,32 +28703,32 @@
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -28743,7 +28743,7 @@
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>229</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
@@ -28753,7 +28753,7 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.4</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -28768,7 +28768,7 @@
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>1018.3</t>
+          <t>1018.4</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
@@ -28816,7 +28816,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:30</t>
+          <t>2026-03-16 01:47:31</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29049,7 +29049,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:30</t>
+          <t>2026-03-16 01:47:31</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:30</t>
+          <t>2026-03-16 01:47:31</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:30</t>
+          <t>2026-03-16 01:47:31</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -29748,17 +29748,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:33</t>
+          <t>2026-03-16 01:47:33</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29771,7 +29771,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>353</t>
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
@@ -29779,7 +29779,7 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R132" t="inlineStr"/>
@@ -29790,7 +29790,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -29800,14 +29800,14 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
       <c r="X132" t="inlineStr">
         <is>
           <t>11.7</t>
@@ -29815,81 +29815,81 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
         <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AG132" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr">
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>25.6</t>
+        </is>
+      </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
       </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>25.9</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="AM132" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN132" t="inlineStr">
+      <c r="AP132" t="inlineStr">
         <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
-      <c r="AP132" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
-      </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
@@ -29899,17 +29899,17 @@
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
@@ -29920,7 +29920,7 @@
       <c r="AW132" t="inlineStr"/>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -29969,7 +29969,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:35</t>
+          <t>2026-03-16 01:47:34</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30190,7 +30190,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:35</t>
+          <t>2026-03-16 01:47:34</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30411,7 +30411,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:35</t>
+          <t>2026-03-16 01:47:34</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30632,7 +30632,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:35</t>
+          <t>2026-03-16 01:47:34</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30853,17 +30853,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:37</t>
+          <t>2026-03-16 01:47:36</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30876,7 +30876,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -30884,12 +30884,12 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -30899,7 +30899,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -30909,12 +30909,12 @@
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
@@ -30924,26 +30924,26 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AG137" t="inlineStr">
@@ -30953,12 +30953,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -30968,22 +30968,22 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -30993,12 +30993,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -31008,22 +31008,22 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
@@ -31033,12 +31033,12 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
@@ -31086,7 +31086,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:38</t>
+          <t>2026-03-16 01:47:38</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31319,7 +31319,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:38</t>
+          <t>2026-03-16 01:47:38</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31552,7 +31552,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:38</t>
+          <t>2026-03-16 01:47:38</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:38</t>
+          <t>2026-03-16 01:47:38</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32003,7 +32003,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -32018,17 +32018,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:41</t>
+          <t>2026-03-16 01:47:41</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32041,7 +32041,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
@@ -32049,12 +32049,12 @@
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1016.4</t>
+          <t>1016.6</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -32064,7 +32064,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32074,96 +32074,96 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>114.8</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>62.6</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>69.5</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
@@ -32173,22 +32173,22 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>114.8</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>1016.4</t>
+          <t>1016.6</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
@@ -32198,12 +32198,12 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>114.8</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>1016.4</t>
+          <t>1016.6</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
@@ -32251,7 +32251,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:43</t>
+          <t>2026-03-16 01:47:42</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32484,7 +32484,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:43</t>
+          <t>2026-03-16 01:47:42</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32717,7 +32717,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:43</t>
+          <t>2026-03-16 01:47:42</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:43</t>
+          <t>2026-03-16 01:47:42</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33168,7 +33168,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33183,17 +33183,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:46</t>
+          <t>2026-03-16 01:47:44</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33207,7 +33207,7 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O147" t="inlineStr"/>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="R147" t="inlineStr"/>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33239,56 +33239,56 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
           <t>0.7</t>
-        </is>
-      </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="X147" t="inlineStr">
-        <is>
-          <t>0.8</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -33303,32 +33303,32 @@
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -33343,17 +33343,17 @@
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
@@ -33363,12 +33363,12 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>314</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:47</t>
+          <t>2026-03-16 01:47:46</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33649,7 +33649,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:47</t>
+          <t>2026-03-16 01:47:46</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33882,7 +33882,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:47</t>
+          <t>2026-03-16 01:47:46</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:47</t>
+          <t>2026-03-16 01:47:46</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34348,17 +34348,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:49</t>
+          <t>2026-03-16 01:47:49</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34371,7 +34371,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -34384,7 +34384,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -34394,7 +34394,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34404,17 +34404,17 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -34426,31 +34426,31 @@
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
       <c r="AI152" t="inlineStr">
         <is>
           <t>40</t>
@@ -34468,29 +34468,29 @@
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
           <t>1.1</t>
         </is>
       </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
       <c r="AQ152" t="inlineStr">
         <is>
           <t>40</t>
@@ -34508,17 +34508,17 @@
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34528,12 +34528,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>1021.2</t>
+          <t>1021.4</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34581,7 +34581,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:51</t>
+          <t>2026-03-16 01:47:51</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34814,7 +34814,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:51</t>
+          <t>2026-03-16 01:47:51</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35047,7 +35047,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:51</t>
+          <t>2026-03-16 01:47:51</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:51</t>
+          <t>2026-03-16 01:47:51</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35498,7 +35498,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35513,17 +35513,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:54</t>
+          <t>2026-03-16 01:47:53</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35536,7 +35536,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35548,12 +35548,12 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>849.3</t>
+          <t>849.6</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -35573,56 +35573,56 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -35637,32 +35637,32 @@
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-2.5</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -35677,37 +35677,37 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>849.3</t>
+          <t>849.6</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>849.3</t>
+          <t>849.6</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:55</t>
+          <t>2026-03-16 01:47:55</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35995,7 +35995,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:55</t>
+          <t>2026-03-16 01:47:55</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:55</t>
+          <t>2026-03-16 01:47:55</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:55</t>
+          <t>2026-03-16 01:47:55</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36703,7 +36703,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36718,17 +36718,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:58</t>
+          <t>2026-03-16 01:47:57</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36741,7 +36741,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>289</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -36753,12 +36753,12 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36768,7 +36768,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -36783,31 +36783,31 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -36817,17 +36817,17 @@
       </c>
       <c r="AG162" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -36842,12 +36842,12 @@
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
@@ -36857,17 +36857,17 @@
       </c>
       <c r="AO162" t="inlineStr">
         <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -36882,37 +36882,37 @@
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>24.1</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>289</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
@@ -36959,7 +36959,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:59</t>
+          <t>2026-03-16 01:47:59</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:59</t>
+          <t>2026-03-16 01:47:59</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37441,7 +37441,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:59</t>
+          <t>2026-03-16 01:47:59</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37682,7 +37682,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-16 01:17:59</t>
+          <t>2026-03-16 01:47:59</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37908,7 +37908,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37923,17 +37923,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:02</t>
+          <t>2026-03-16 01:48:02</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>340</t>
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
@@ -37959,7 +37959,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37994,21 +37994,21 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -38038,17 +38038,17 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
@@ -38078,22 +38078,22 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
@@ -38103,12 +38103,12 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1017.1</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:04</t>
+          <t>2026-03-16 01:48:03</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38389,7 +38389,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:04</t>
+          <t>2026-03-16 01:48:03</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38622,7 +38622,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:04</t>
+          <t>2026-03-16 01:48:03</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38855,7 +38855,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:04</t>
+          <t>2026-03-16 01:48:03</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39088,7 +39088,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:10</t>
+          <t>2026-03-16 01:48:09</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:12</t>
+          <t>2026-03-16 01:48:11</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39530,7 +39530,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:12</t>
+          <t>2026-03-16 01:48:11</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39751,7 +39751,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:12</t>
+          <t>2026-03-16 01:48:11</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39972,7 +39972,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:12</t>
+          <t>2026-03-16 01:48:11</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40178,7 +40178,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40193,17 +40193,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:15</t>
+          <t>2026-03-16 01:48:13</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40216,7 +40216,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>295</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40224,7 +40224,7 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R177" t="inlineStr"/>
@@ -40235,7 +40235,7 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
@@ -40245,56 +40245,56 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -40304,37 +40304,37 @@
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AL177" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40344,17 +40344,17 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -40365,7 +40365,7 @@
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -40414,7 +40414,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:17</t>
+          <t>2026-03-16 01:48:14</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40635,7 +40635,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:17</t>
+          <t>2026-03-16 01:48:14</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40856,7 +40856,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:17</t>
+          <t>2026-03-16 01:48:14</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41077,7 +41077,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:17</t>
+          <t>2026-03-16 01:48:14</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41298,7 +41298,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:23</t>
+          <t>2026-03-16 01:48:22</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41531,7 +41531,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:25</t>
+          <t>2026-03-16 01:48:23</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41764,7 +41764,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:25</t>
+          <t>2026-03-16 01:48:23</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:25</t>
+          <t>2026-03-16 01:48:23</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42230,7 +42230,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:25</t>
+          <t>2026-03-16 01:48:23</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42448,7 +42448,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42463,17 +42463,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:27</t>
+          <t>2026-03-16 01:48:26</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42490,12 +42490,12 @@
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -42505,23 +42505,23 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr"/>
@@ -42532,27 +42532,27 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -42562,33 +42562,33 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr"/>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -42598,7 +42598,7 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>1019.9</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -42648,7 +42648,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:29</t>
+          <t>2026-03-16 01:48:27</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42833,7 +42833,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:29</t>
+          <t>2026-03-16 01:48:27</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43030,7 +43030,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:29</t>
+          <t>2026-03-16 01:48:27</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43227,7 +43227,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:29</t>
+          <t>2026-03-16 01:48:27</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43424,17 +43424,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:31</t>
+          <t>2026-03-16 01:48:30</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -43455,12 +43455,12 @@
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43470,7 +43470,7 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -43480,17 +43480,17 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
           <t>10.2</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>10.4</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -43502,99 +43502,99 @@
       <c r="AA192" t="inlineStr"/>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr"/>
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
           <t>10.2</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
         <is>
           <t>19.4</t>
         </is>
       </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>10.4</t>
-        </is>
-      </c>
-      <c r="AP192" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="AQ192" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS192" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
@@ -43604,12 +43604,12 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>1017.5</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:32</t>
+          <t>2026-03-16 01:48:31</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43890,7 +43890,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:32</t>
+          <t>2026-03-16 01:48:31</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:32</t>
+          <t>2026-03-16 01:48:31</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44356,7 +44356,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:32</t>
+          <t>2026-03-16 01:48:31</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44574,7 +44574,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44589,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:35</t>
+          <t>2026-03-16 01:48:33</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44616,7 +44616,7 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R197" t="inlineStr"/>
@@ -44627,18 +44627,18 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
@@ -44654,12 +44654,12 @@
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -44669,12 +44669,12 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -44686,12 +44686,12 @@
       <c r="AL197" t="inlineStr"/>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -44701,12 +44701,12 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
@@ -44762,7 +44762,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:36</t>
+          <t>2026-03-16 01:48:35</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44935,7 +44935,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:36</t>
+          <t>2026-03-16 01:48:35</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45108,7 +45108,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:36</t>
+          <t>2026-03-16 01:48:35</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45281,7 +45281,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:36</t>
+          <t>2026-03-16 01:48:35</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45454,17 +45454,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:39</t>
+          <t>2026-03-16 01:48:38</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45477,7 +45477,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -45485,7 +45485,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -45496,7 +45496,7 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
@@ -45506,56 +45506,56 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr"/>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -45565,37 +45565,37 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -45605,17 +45605,17 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -45626,7 +45626,7 @@
       <c r="AW202" t="inlineStr"/>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -45675,7 +45675,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:41</t>
+          <t>2026-03-16 01:48:39</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45896,7 +45896,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:41</t>
+          <t>2026-03-16 01:48:39</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46117,7 +46117,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:41</t>
+          <t>2026-03-16 01:48:39</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46338,7 +46338,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:41</t>
+          <t>2026-03-16 01:48:39</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46559,17 +46559,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:43</t>
+          <t>2026-03-16 01:48:42</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46582,24 +46582,24 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>236</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>852.6</t>
+          <t>853.0</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -46609,7 +46609,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46619,7 +46619,7 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
@@ -46634,26 +46634,26 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -46678,22 +46678,22 @@
       </c>
       <c r="AK207" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -46708,7 +46708,7 @@
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -46718,42 +46718,42 @@
       </c>
       <c r="AS207" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>852.6</t>
+          <t>853.0</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>852.6</t>
+          <t>853.0</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
@@ -46800,7 +46800,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:45</t>
+          <t>2026-03-16 01:48:44</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:45</t>
+          <t>2026-03-16 01:48:44</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:45</t>
+          <t>2026-03-16 01:48:44</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47523,7 +47523,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:45</t>
+          <t>2026-03-16 01:48:44</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47749,7 +47749,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47764,17 +47764,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:47</t>
+          <t>2026-03-16 01:48:46</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47789,7 +47789,7 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>210</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -47799,12 +47799,12 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>1028.3</t>
+          <t>1028.9</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47814,7 +47814,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47824,56 +47824,56 @@
       </c>
       <c r="V212" t="inlineStr">
         <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
           <t>-2.3</t>
-        </is>
-      </c>
-      <c r="W212" t="inlineStr">
-        <is>
-          <t>-3.1</t>
-        </is>
-      </c>
-      <c r="X212" t="inlineStr">
-        <is>
-          <t>-1.6</t>
         </is>
       </c>
       <c r="Y212" t="inlineStr"/>
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
         <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
           <t>-2.3</t>
         </is>
       </c>
-      <c r="AG212" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
       <c r="AH212" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -47888,32 +47888,32 @@
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="AO212" t="inlineStr">
+        <is>
           <t>-2.3</t>
         </is>
       </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>-1.6</t>
-        </is>
-      </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
@@ -47928,37 +47928,37 @@
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>1028.3</t>
+          <t>1028.9</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>210</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>1028.3</t>
+          <t>1028.9</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -48005,7 +48005,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:49</t>
+          <t>2026-03-16 01:48:48</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48246,7 +48246,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:49</t>
+          <t>2026-03-16 01:48:48</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48487,7 +48487,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:49</t>
+          <t>2026-03-16 01:48:48</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48728,7 +48728,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:49</t>
+          <t>2026-03-16 01:48:48</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48954,7 +48954,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48969,17 +48969,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:51</t>
+          <t>2026-03-16 01:48:50</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48992,7 +48992,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>334</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
@@ -49000,12 +49000,12 @@
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1020.6</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -49015,7 +49015,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -49025,96 +49025,96 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="X217" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr"/>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>00:30 - 01:00</t>
+          <t>01:00 - 01:30</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AH217" t="inlineStr">
         <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="AI217" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AL217" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="AM217" t="inlineStr">
+        <is>
+          <t>01:00 - 01:30</t>
+        </is>
+      </c>
+      <c r="AN217" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AL217" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>00:30 - 01:00</t>
-        </is>
-      </c>
-      <c r="AN217" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -49124,22 +49124,22 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>1020.6</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
@@ -49149,12 +49149,12 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>1020.6</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
@@ -49202,7 +49202,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:53</t>
+          <t>2026-03-16 01:48:52</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49435,7 +49435,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:53</t>
+          <t>2026-03-16 01:48:52</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49668,7 +49668,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:53</t>
+          <t>2026-03-16 01:48:52</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49901,7 +49901,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-16 01:18:53</t>
+          <t>2026-03-16 01:48:52</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50173,7 +50173,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -50204,7 +50204,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -50235,7 +50235,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -50297,7 +50297,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -50359,7 +50359,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -50390,7 +50390,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -50421,7 +50421,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -50452,7 +50452,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -50514,7 +50514,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -50545,7 +50545,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -50576,7 +50576,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -50607,7 +50607,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -50638,7 +50638,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -50669,7 +50669,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -50700,7 +50700,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -50731,7 +50731,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -50762,7 +50762,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -50793,7 +50793,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -50824,7 +50824,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -50855,7 +50855,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -50886,7 +50886,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -50948,7 +50948,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -51010,7 +51010,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -51041,7 +51041,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -51072,7 +51072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -51103,7 +51103,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -51134,7 +51134,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -51165,7 +51165,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -51196,7 +51196,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -51227,7 +51227,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -51413,7 +51413,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -51475,7 +51475,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -51506,7 +51506,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -51537,7 +51537,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T00:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T01:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:27</t>
+          <t>2026-03-16 02:45:28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,27 +795,27 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -835,27 +835,27 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-3.5</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:29</t>
+          <t>2026-03-16 02:45:29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:29</t>
+          <t>2026-03-16 02:45:29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:29</t>
+          <t>2026-03-16 02:45:29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:29</t>
+          <t>2026-03-16 02:45:29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:32</t>
+          <t>2026-03-16 02:45:32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,7 +1732,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>137</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,56 +1763,56 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>-7.0</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-7.7</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-6.6</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
           <t>-7.0</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>-6.6</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-7.7</t>
-        </is>
-      </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1827,32 +1827,32 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
+          <t>-6.2</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>-5.5</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
           <t>-7.0</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>-6.6</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-7.7</t>
-        </is>
-      </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>137</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:34</t>
+          <t>2026-03-16 02:45:33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:34</t>
+          <t>2026-03-16 02:45:33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:34</t>
+          <t>2026-03-16 02:45:33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:34</t>
+          <t>2026-03-16 02:45:33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:36</t>
+          <t>2026-03-16 02:45:36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2903,12 +2903,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1017.5</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,62 +2918,62 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2983,37 +2983,37 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3023,33 +3023,33 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1017.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr"/>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1017.8</t>
+          <t>1017.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:38</t>
+          <t>2026-03-16 02:45:37</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:38</t>
+          <t>2026-03-16 02:45:37</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:38</t>
+          <t>2026-03-16 02:45:37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:38</t>
+          <t>2026-03-16 02:45:37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:41</t>
+          <t>2026-03-16 02:45:40</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4026,17 +4026,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>268</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4057,56 +4057,56 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.7</t>
+          <t>-7.5</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-5.7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>-5.7</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
           <t>-7.5</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-8.7</t>
-        </is>
-      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4116,37 +4116,37 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-8.2</t>
+          <t>-6.9</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
+          <t>-5.7</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
           <t>-7.5</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-8.7</t>
-        </is>
-      </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>63</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -4156,22 +4156,22 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:42</t>
+          <t>2026-03-16 02:45:41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:42</t>
+          <t>2026-03-16 02:45:41</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:42</t>
+          <t>2026-03-16 02:45:41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:42</t>
+          <t>2026-03-16 02:45:41</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5166,17 +5166,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:45</t>
+          <t>2026-03-16 02:45:43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>335</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5222,51 +5222,51 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
@@ -5281,32 +5281,32 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -5321,22 +5321,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>335</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1016.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:47</t>
+          <t>2026-03-16 02:45:45</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:47</t>
+          <t>2026-03-16 02:45:45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:47</t>
+          <t>2026-03-16 02:45:45</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-16 02:15:47</t>
+          <t>2026-03-16 02:45:45</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:04</t>
+          <t>2026-03-16 02:46:00</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6362,12 +6362,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6387,22 +6387,22 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
@@ -6416,27 +6416,27 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6446,37 +6446,37 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>25.9</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1017.2</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:06</t>
+          <t>2026-03-16 02:46:01</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:06</t>
+          <t>2026-03-16 02:46:01</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:06</t>
+          <t>2026-03-16 02:46:01</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:06</t>
+          <t>2026-03-16 02:46:01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:08</t>
+          <t>2026-03-16 02:46:04</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7520,7 +7520,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>353</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7548,51 +7548,51 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>11.6</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>11.8</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -7607,32 +7607,32 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -7647,17 +7647,17 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -7668,7 +7668,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:10</t>
+          <t>2026-03-16 02:46:05</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:10</t>
+          <t>2026-03-16 02:46:05</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:10</t>
+          <t>2026-03-16 02:46:05</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:10</t>
+          <t>2026-03-16 02:46:05</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8601,17 +8601,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:13</t>
+          <t>2026-03-16 02:46:08</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8625,14 +8625,14 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8653,56 +8653,56 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
           <t>9.5</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>9.7</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -8712,37 +8712,37 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
@@ -8752,17 +8752,17 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8773,7 +8773,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:14</t>
+          <t>2026-03-16 02:46:09</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:14</t>
+          <t>2026-03-16 02:46:09</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:14</t>
+          <t>2026-03-16 02:46:09</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:14</t>
+          <t>2026-03-16 02:46:09</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9706,17 +9706,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:17</t>
+          <t>2026-03-16 02:46:11</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9733,7 +9733,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -9744,23 +9744,23 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -9771,27 +9771,27 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -9803,27 +9803,27 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:18</t>
+          <t>2026-03-16 02:46:13</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:18</t>
+          <t>2026-03-16 02:46:13</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:18</t>
+          <t>2026-03-16 02:46:13</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:18</t>
+          <t>2026-03-16 02:46:13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10571,17 +10571,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:21</t>
+          <t>2026-03-16 02:46:15</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10598,7 +10598,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -10609,23 +10609,23 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
           <t>11.4</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>11.6</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10636,27 +10636,27 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -10668,27 +10668,27 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
           <t>11.4</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:23</t>
+          <t>2026-03-16 02:46:16</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:23</t>
+          <t>2026-03-16 02:46:16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:23</t>
+          <t>2026-03-16 02:46:16</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:23</t>
+          <t>2026-03-16 02:46:16</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11436,17 +11436,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:25</t>
+          <t>2026-03-16 02:46:18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>84</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -11471,12 +11471,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1021.4</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -11496,56 +11496,56 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -11560,32 +11560,32 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -11600,37 +11600,37 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>1021.4</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>1021.4</t>
+          <t>1021.7</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:27</t>
+          <t>2026-03-16 02:46:19</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:27</t>
+          <t>2026-03-16 02:46:19</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:27</t>
+          <t>2026-03-16 02:46:19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:27</t>
+          <t>2026-03-16 02:46:19</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12641,17 +12641,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:30</t>
+          <t>2026-03-16 02:46:22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12672,7 +12672,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
@@ -12683,7 +12683,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12693,56 +12693,56 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -12752,37 +12752,37 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -12792,17 +12792,17 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>333</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -12813,7 +12813,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:31</t>
+          <t>2026-03-16 02:46:23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:31</t>
+          <t>2026-03-16 02:46:23</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:31</t>
+          <t>2026-03-16 02:46:23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:31</t>
+          <t>2026-03-16 02:46:23</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13746,17 +13746,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:34</t>
+          <t>2026-03-16 02:46:25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13773,7 +13773,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13784,23 +13784,23 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
           <t>11.1</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>11.4</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -13811,27 +13811,27 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -13843,27 +13843,27 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
+          <t>10.9</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:35</t>
+          <t>2026-03-16 02:46:26</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:35</t>
+          <t>2026-03-16 02:46:26</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:35</t>
+          <t>2026-03-16 02:46:26</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14438,7 +14438,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:35</t>
+          <t>2026-03-16 02:46:26</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14596,7 +14596,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14611,17 +14611,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:38</t>
+          <t>2026-03-16 02:46:29</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>162</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -14667,56 +14667,56 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -14731,32 +14731,32 @@
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>-3.0</t>
-        </is>
-      </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -14771,17 +14771,17 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -14791,12 +14791,12 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>63.4</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -14844,7 +14844,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:40</t>
+          <t>2026-03-16 02:46:30</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15077,7 +15077,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:40</t>
+          <t>2026-03-16 02:46:30</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:40</t>
+          <t>2026-03-16 02:46:30</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:40</t>
+          <t>2026-03-16 02:46:30</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15776,17 +15776,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:42</t>
+          <t>2026-03-16 02:46:33</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R72" t="inlineStr"/>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15837,31 +15837,31 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -15871,17 +15871,17 @@
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -15896,12 +15896,12 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
@@ -15911,17 +15911,17 @@
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
@@ -15936,17 +15936,17 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>37.4</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16009,7 +16009,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:44</t>
+          <t>2026-03-16 02:46:34</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:44</t>
+          <t>2026-03-16 02:46:34</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16475,7 +16475,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:44</t>
+          <t>2026-03-16 02:46:34</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16708,7 +16708,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:44</t>
+          <t>2026-03-16 02:46:34</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16941,17 +16941,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:47</t>
+          <t>2026-03-16 02:46:36</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16964,7 +16964,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>208</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -16972,12 +16972,12 @@
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -16997,96 +16997,96 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AG77" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
           <t>-0.1</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
@@ -17096,22 +17096,22 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>208</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17121,12 +17121,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:49</t>
+          <t>2026-03-16 02:46:38</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:49</t>
+          <t>2026-03-16 02:46:38</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:49</t>
+          <t>2026-03-16 02:46:38</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:49</t>
+          <t>2026-03-16 02:46:38</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18106,17 +18106,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:51</t>
+          <t>2026-03-16 02:46:40</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18129,7 +18129,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18137,7 +18137,7 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18158,17 +18158,17 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -18180,34 +18180,34 @@
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -18222,32 +18222,32 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
@@ -18262,12 +18262,12 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>172</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -18278,7 +18278,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:53</t>
+          <t>2026-03-16 02:46:41</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:53</t>
+          <t>2026-03-16 02:46:41</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:53</t>
+          <t>2026-03-16 02:46:41</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -18990,7 +18990,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:53</t>
+          <t>2026-03-16 02:46:41</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19211,17 +19211,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:56</t>
+          <t>2026-03-16 02:46:44</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19257,7 +19257,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19267,56 +19267,56 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
           <t>-2.4</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
           <t>-2.4</t>
         </is>
       </c>
-      <c r="AG87" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19331,32 +19331,32 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
           <t>-2.4</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>-1.5</t>
-        </is>
-      </c>
-      <c r="AP87" t="inlineStr">
-        <is>
-          <t>-4.5</t>
-        </is>
-      </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19371,17 +19371,17 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -19391,12 +19391,12 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>23.4</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:57</t>
+          <t>2026-03-16 02:46:45</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:57</t>
+          <t>2026-03-16 02:46:45</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19910,7 +19910,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:57</t>
+          <t>2026-03-16 02:46:45</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20143,7 +20143,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-16 02:16:57</t>
+          <t>2026-03-16 02:46:45</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20361,7 +20361,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20376,17 +20376,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:00</t>
+          <t>2026-03-16 02:46:48</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20407,12 +20407,12 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1022.9</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20432,56 +20432,56 @@
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr"/>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -20491,37 +20491,37 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.6</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -20531,22 +20531,22 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>1022.9</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -20556,12 +20556,12 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>1022.9</t>
+          <t>1023.0</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:01</t>
+          <t>2026-03-16 02:46:49</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:01</t>
+          <t>2026-03-16 02:46:49</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21075,7 +21075,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:01</t>
+          <t>2026-03-16 02:46:49</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:01</t>
+          <t>2026-03-16 02:46:49</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21541,17 +21541,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:04</t>
+          <t>2026-03-16 02:46:51</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21566,7 +21566,7 @@
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>353</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R97" t="inlineStr"/>
@@ -21587,7 +21587,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21597,56 +21597,56 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -21661,32 +21661,32 @@
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
@@ -21701,17 +21701,17 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -21721,12 +21721,12 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>353</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:05</t>
+          <t>2026-03-16 02:46:53</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22007,7 +22007,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:05</t>
+          <t>2026-03-16 02:46:53</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:05</t>
+          <t>2026-03-16 02:46:53</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:05</t>
+          <t>2026-03-16 02:46:53</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22706,17 +22706,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:08</t>
+          <t>2026-03-16 02:46:55</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22731,7 +22731,7 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>345</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22762,56 +22762,56 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -22826,32 +22826,32 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-2.8</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -22866,17 +22866,17 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22939,7 +22939,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:10</t>
+          <t>2026-03-16 02:46:57</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23172,7 +23172,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:10</t>
+          <t>2026-03-16 02:46:57</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:10</t>
+          <t>2026-03-16 02:46:57</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:10</t>
+          <t>2026-03-16 02:46:57</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23856,7 +23856,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23871,17 +23871,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:13</t>
+          <t>2026-03-16 02:46:59</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23894,7 +23894,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>260</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -23902,12 +23902,12 @@
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23927,56 +23927,56 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr"/>
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -23986,37 +23986,37 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
@@ -24026,22 +24026,22 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>260</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -24051,12 +24051,12 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>1020.3</t>
+          <t>1020.5</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:15</t>
+          <t>2026-03-16 02:47:01</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24337,7 +24337,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:15</t>
+          <t>2026-03-16 02:47:01</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:15</t>
+          <t>2026-03-16 02:47:01</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24803,7 +24803,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:15</t>
+          <t>2026-03-16 02:47:01</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25021,7 +25021,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25036,17 +25036,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:17</t>
+          <t>2026-03-16 02:47:03</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25061,7 +25061,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R112" t="inlineStr"/>
@@ -25082,7 +25082,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25092,56 +25092,56 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -25156,32 +25156,32 @@
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
@@ -25196,17 +25196,17 @@
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25216,12 +25216,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:19</t>
+          <t>2026-03-16 02:47:05</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:19</t>
+          <t>2026-03-16 02:47:05</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25735,7 +25735,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:19</t>
+          <t>2026-03-16 02:47:05</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:19</t>
+          <t>2026-03-16 02:47:05</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26201,7 +26201,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:30</t>
+          <t>2026-03-16 02:47:15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26442,7 +26442,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:31</t>
+          <t>2026-03-16 02:47:17</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26683,7 +26683,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:31</t>
+          <t>2026-03-16 02:47:17</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:31</t>
+          <t>2026-03-16 02:47:17</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:31</t>
+          <t>2026-03-16 02:47:17</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27406,17 +27406,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:34</t>
+          <t>2026-03-16 02:47:19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:35</t>
+          <t>2026-03-16 02:47:20</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:35</t>
+          <t>2026-03-16 02:47:20</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:35</t>
+          <t>2026-03-16 02:47:20</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:35</t>
+          <t>2026-03-16 02:47:20</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28556,7 +28556,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -28571,17 +28571,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:38</t>
+          <t>2026-03-16 02:47:23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>267</t>
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
@@ -28602,12 +28602,12 @@
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -28617,7 +28617,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -28627,56 +28627,56 @@
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -28686,37 +28686,37 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
@@ -28726,22 +28726,22 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>267</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -28751,12 +28751,12 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.0</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
@@ -28804,7 +28804,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:40</t>
+          <t>2026-03-16 02:47:24</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29037,7 +29037,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:40</t>
+          <t>2026-03-16 02:47:24</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:40</t>
+          <t>2026-03-16 02:47:24</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29503,7 +29503,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:40</t>
+          <t>2026-03-16 02:47:24</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29736,17 +29736,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:42</t>
+          <t>2026-03-16 02:47:26</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -29957,7 +29957,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:44</t>
+          <t>2026-03-16 02:47:28</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30178,7 +30178,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:44</t>
+          <t>2026-03-16 02:47:28</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30399,7 +30399,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:44</t>
+          <t>2026-03-16 02:47:28</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:44</t>
+          <t>2026-03-16 02:47:28</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30826,7 +30826,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -30841,17 +30841,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:47</t>
+          <t>2026-03-16 02:47:30</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -30864,7 +30864,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39</t>
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
@@ -30872,12 +30872,12 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>1016.7</t>
+          <t>1016.1</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
@@ -30887,7 +30887,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -30907,26 +30907,26 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -30936,7 +30936,7 @@
       </c>
       <c r="AG137" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AH137" t="inlineStr">
@@ -30946,7 +30946,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -30956,17 +30956,17 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
@@ -30976,7 +30976,7 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
@@ -30986,7 +30986,7 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
@@ -30996,22 +30996,22 @@
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>1016.7</t>
+          <t>1016.1</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
@@ -31021,12 +31021,12 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>1016.7</t>
+          <t>1016.1</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:49</t>
+          <t>2026-03-16 02:47:32</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:49</t>
+          <t>2026-03-16 02:47:32</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:49</t>
+          <t>2026-03-16 02:47:32</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31773,7 +31773,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:49</t>
+          <t>2026-03-16 02:47:32</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -31991,7 +31991,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -32006,17 +32006,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:51</t>
+          <t>2026-03-16 02:47:34</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32042,7 +32042,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>1015.8</t>
+          <t>1015.4</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
@@ -32052,7 +32052,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -32062,121 +32062,121 @@
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>107.3</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AG142" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AH142" t="inlineStr">
         <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="AI142" t="inlineStr">
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>68.8</t>
-        </is>
-      </c>
-      <c r="AL142" t="inlineStr">
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>67.3</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="AQ142" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>68.8</t>
-        </is>
-      </c>
-      <c r="AT142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>107.3</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>1015.8</t>
+          <t>1015.4</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
@@ -32186,12 +32186,12 @@
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>107.3</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>1015.8</t>
+          <t>1015.4</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
@@ -32239,7 +32239,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:53</t>
+          <t>2026-03-16 02:47:35</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32472,7 +32472,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:53</t>
+          <t>2026-03-16 02:47:35</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:53</t>
+          <t>2026-03-16 02:47:35</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32938,7 +32938,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:53</t>
+          <t>2026-03-16 02:47:35</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -33171,17 +33171,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:56</t>
+          <t>2026-03-16 02:47:38</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33206,7 +33206,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R147" t="inlineStr"/>
@@ -33217,7 +33217,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
@@ -33237,36 +33237,36 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AG147" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AH147" t="inlineStr">
@@ -33276,7 +33276,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -33291,22 +33291,22 @@
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
@@ -33316,7 +33316,7 @@
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
@@ -33331,7 +33331,7 @@
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
@@ -33341,7 +33341,7 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
@@ -33356,7 +33356,7 @@
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:57</t>
+          <t>2026-03-16 02:47:39</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33637,7 +33637,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:57</t>
+          <t>2026-03-16 02:47:39</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33870,7 +33870,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:57</t>
+          <t>2026-03-16 02:47:39</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34103,7 +34103,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-16 02:17:57</t>
+          <t>2026-03-16 02:47:39</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -34336,17 +34336,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:00</t>
+          <t>2026-03-16 02:47:42</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -34359,7 +34359,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
@@ -34367,12 +34367,12 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="S152" t="inlineStr">
@@ -34382,7 +34382,7 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U152" t="inlineStr">
@@ -34392,56 +34392,56 @@
       </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AG152" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -34451,37 +34451,37 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
@@ -34491,22 +34491,22 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
@@ -34516,12 +34516,12 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>1021.9</t>
+          <t>1022.3</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
@@ -34569,7 +34569,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:02</t>
+          <t>2026-03-16 02:47:43</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34802,7 +34802,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:02</t>
+          <t>2026-03-16 02:47:43</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35035,7 +35035,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:02</t>
+          <t>2026-03-16 02:47:43</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35268,7 +35268,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:02</t>
+          <t>2026-03-16 02:47:43</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -35486,7 +35486,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -35501,17 +35501,17 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:04</t>
+          <t>2026-03-16 02:47:45</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -35524,7 +35524,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
@@ -35536,12 +35536,12 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>849.4</t>
+          <t>849.3</t>
         </is>
       </c>
       <c r="S157" t="inlineStr">
@@ -35551,7 +35551,7 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U157" t="inlineStr">
@@ -35561,56 +35561,56 @@
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AG157" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AH157" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -35625,32 +35625,32 @@
       </c>
       <c r="AL157" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
@@ -35665,37 +35665,37 @@
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>849.4</t>
+          <t>849.3</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>849.4</t>
+          <t>849.3</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
@@ -35742,7 +35742,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:06</t>
+          <t>2026-03-16 02:47:47</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35983,7 +35983,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:06</t>
+          <t>2026-03-16 02:47:47</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36224,7 +36224,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:06</t>
+          <t>2026-03-16 02:47:47</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36465,7 +36465,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:06</t>
+          <t>2026-03-16 02:47:47</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -36691,7 +36691,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -36706,17 +36706,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:09</t>
+          <t>2026-03-16 02:47:49</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K162" t="n">
@@ -36729,7 +36729,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>288</t>
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
@@ -36741,12 +36741,12 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
@@ -36756,7 +36756,7 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U162" t="inlineStr">
@@ -36766,141 +36766,141 @@
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr"/>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
       <c r="AD162" t="inlineStr"/>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AG162" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AH162" t="inlineStr">
         <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>20.9</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN162" t="inlineStr">
+        <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AL162" t="inlineStr">
-        <is>
-          <t>26.6</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>288</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>1022.2</t>
+          <t>1022.4</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
@@ -36947,7 +36947,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:10</t>
+          <t>2026-03-16 02:47:51</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37188,7 +37188,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:10</t>
+          <t>2026-03-16 02:47:51</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37429,7 +37429,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:10</t>
+          <t>2026-03-16 02:47:51</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37670,7 +37670,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:10</t>
+          <t>2026-03-16 02:47:51</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -37896,7 +37896,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -37911,17 +37911,17 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:13</t>
+          <t>2026-03-16 02:47:53</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -37947,7 +37947,7 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1016.7</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
@@ -37957,7 +37957,7 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U167" t="inlineStr">
@@ -37967,51 +37967,51 @@
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr"/>
       <c r="AA167" t="inlineStr"/>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="AC167" t="inlineStr"/>
       <c r="AD167" t="inlineStr"/>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AG167" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AI167" t="inlineStr">
@@ -38026,7 +38026,7 @@
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AL167" t="inlineStr">
@@ -38036,22 +38036,22 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AQ167" t="inlineStr">
@@ -38066,7 +38066,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AT167" t="inlineStr">
@@ -38076,12 +38076,12 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1016.7</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
@@ -38091,12 +38091,12 @@
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>1017.1</t>
+          <t>1016.7</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
@@ -38144,7 +38144,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:14</t>
+          <t>2026-03-16 02:47:55</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:14</t>
+          <t>2026-03-16 02:47:55</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38610,7 +38610,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:14</t>
+          <t>2026-03-16 02:47:55</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38843,7 +38843,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:14</t>
+          <t>2026-03-16 02:47:55</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:25</t>
+          <t>2026-03-16 02:48:05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39297,7 +39297,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:27</t>
+          <t>2026-03-16 02:48:06</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39518,7 +39518,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:27</t>
+          <t>2026-03-16 02:48:06</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39739,7 +39739,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:27</t>
+          <t>2026-03-16 02:48:06</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:27</t>
+          <t>2026-03-16 02:48:06</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40166,7 +40166,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -40181,17 +40181,17 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:29</t>
+          <t>2026-03-16 02:48:09</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -40204,7 +40204,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>295</t>
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
@@ -40212,7 +40212,7 @@
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R177" t="inlineStr"/>
@@ -40223,7 +40223,7 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U177" t="inlineStr">
@@ -40233,96 +40233,96 @@
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="Z177" t="inlineStr"/>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="inlineStr"/>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AG177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AH177" t="inlineStr">
         <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AI177" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="AM177" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN177" t="inlineStr">
+        <is>
           <t>3.4</t>
         </is>
       </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AL177" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>3.9</t>
-        </is>
-      </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AR177" t="inlineStr">
@@ -40332,17 +40332,17 @@
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AT177" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>295</t>
         </is>
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
@@ -40353,7 +40353,7 @@
       <c r="AW177" t="inlineStr"/>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -40402,7 +40402,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:31</t>
+          <t>2026-03-16 02:48:10</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:31</t>
+          <t>2026-03-16 02:48:10</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:31</t>
+          <t>2026-03-16 02:48:10</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41065,7 +41065,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:31</t>
+          <t>2026-03-16 02:48:10</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41286,7 +41286,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:41</t>
+          <t>2026-03-16 02:48:21</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41519,7 +41519,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:43</t>
+          <t>2026-03-16 02:48:22</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41752,7 +41752,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:43</t>
+          <t>2026-03-16 02:48:22</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -41985,7 +41985,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:43</t>
+          <t>2026-03-16 02:48:22</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42218,7 +42218,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:43</t>
+          <t>2026-03-16 02:48:22</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42436,7 +42436,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -42451,17 +42451,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:45</t>
+          <t>2026-03-16 02:48:25</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -42477,17 +42477,17 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
@@ -42497,23 +42497,23 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U187" t="inlineStr"/>
       <c r="V187" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr"/>
@@ -42524,27 +42524,27 @@
       <c r="AD187" t="inlineStr"/>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AG187" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -42554,37 +42554,37 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
@@ -42594,12 +42594,12 @@
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>1019.3</t>
+          <t>1019.4</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr"/>
@@ -42648,7 +42648,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:47</t>
+          <t>2026-03-16 02:48:26</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42833,7 +42833,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:47</t>
+          <t>2026-03-16 02:48:26</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -43030,7 +43030,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:47</t>
+          <t>2026-03-16 02:48:26</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43227,7 +43227,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:47</t>
+          <t>2026-03-16 02:48:26</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43409,7 +43409,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -43424,17 +43424,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:50</t>
+          <t>2026-03-16 02:48:28</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -43447,7 +43447,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N192" t="inlineStr"/>
@@ -43455,12 +43455,12 @@
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="S192" t="inlineStr">
@@ -43470,7 +43470,7 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U192" t="inlineStr">
@@ -43480,96 +43480,96 @@
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="X192" t="inlineStr">
+        <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="Z192" t="inlineStr"/>
       <c r="AA192" t="inlineStr"/>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr"/>
       <c r="AD192" t="inlineStr"/>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AG192" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AH192" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="AL192" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="AM192" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN192" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
-      <c r="AL192" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
@@ -43579,22 +43579,22 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
@@ -43604,12 +43604,12 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1017.9</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
@@ -43657,7 +43657,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:51</t>
+          <t>2026-03-16 02:48:30</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43890,7 +43890,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:51</t>
+          <t>2026-03-16 02:48:30</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:51</t>
+          <t>2026-03-16 02:48:30</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44356,7 +44356,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:51</t>
+          <t>2026-03-16 02:48:30</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44574,7 +44574,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44589,17 +44589,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:54</t>
+          <t>2026-03-16 02:48:32</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -44616,7 +44616,7 @@
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R197" t="inlineStr"/>
@@ -44627,23 +44627,23 @@
       </c>
       <c r="T197" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U197" t="inlineStr"/>
       <c r="V197" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
           <t>11.6</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>11.7</t>
         </is>
       </c>
       <c r="Y197" t="inlineStr"/>
@@ -44654,27 +44654,27 @@
       <c r="AD197" t="inlineStr"/>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -44686,27 +44686,27 @@
       <c r="AL197" t="inlineStr"/>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
           <t>11.6</t>
         </is>
       </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>11.7</t>
-        </is>
-      </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
@@ -44762,7 +44762,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:55</t>
+          <t>2026-03-16 02:48:33</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44935,7 +44935,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:55</t>
+          <t>2026-03-16 02:48:33</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -45108,7 +45108,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:55</t>
+          <t>2026-03-16 02:48:33</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45281,7 +45281,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:55</t>
+          <t>2026-03-16 02:48:33</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45439,7 +45439,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -45454,17 +45454,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:58</t>
+          <t>2026-03-16 02:48:36</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -45477,7 +45477,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N202" t="inlineStr"/>
@@ -45485,7 +45485,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -45496,7 +45496,7 @@
       </c>
       <c r="T202" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U202" t="inlineStr">
@@ -45506,96 +45506,96 @@
       </c>
       <c r="V202" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z202" t="inlineStr"/>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="inlineStr"/>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AG202" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AH202" t="inlineStr">
         <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="AL202" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>02:00 - 02:30</t>
+        </is>
+      </c>
+      <c r="AN202" t="inlineStr">
+        <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="AL202" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="AM202" t="inlineStr">
-        <is>
-          <t>01:30 - 02:00</t>
-        </is>
-      </c>
-      <c r="AN202" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
@@ -45605,17 +45605,17 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
@@ -45626,7 +45626,7 @@
       <c r="AW202" t="inlineStr"/>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -45675,7 +45675,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:59</t>
+          <t>2026-03-16 02:48:37</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45896,7 +45896,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:59</t>
+          <t>2026-03-16 02:48:37</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -46117,7 +46117,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:59</t>
+          <t>2026-03-16 02:48:37</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46338,7 +46338,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-16 02:18:59</t>
+          <t>2026-03-16 02:48:37</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46544,7 +46544,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -46559,17 +46559,17 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:02</t>
+          <t>2026-03-16 02:48:39</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K207" t="n">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="N207" t="inlineStr"/>
@@ -46594,12 +46594,12 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
@@ -46609,7 +46609,7 @@
       </c>
       <c r="T207" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U207" t="inlineStr">
@@ -46619,56 +46619,56 @@
       </c>
       <c r="V207" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr"/>
       <c r="AA207" t="inlineStr"/>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AC207" t="inlineStr"/>
       <c r="AD207" t="inlineStr"/>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AG207" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AH207" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -46683,32 +46683,32 @@
       </c>
       <c r="AL207" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="AQ207" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AR207" t="inlineStr">
@@ -46723,37 +46723,37 @@
       </c>
       <c r="AT207" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>852.0</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
@@ -46800,7 +46800,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:03</t>
+          <t>2026-03-16 02:48:41</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47041,7 +47041,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:03</t>
+          <t>2026-03-16 02:48:41</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -47282,7 +47282,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:03</t>
+          <t>2026-03-16 02:48:41</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47523,7 +47523,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:03</t>
+          <t>2026-03-16 02:48:41</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47749,7 +47749,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -47764,17 +47764,17 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:06</t>
+          <t>2026-03-16 02:48:43</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K212" t="n">
@@ -47789,7 +47789,7 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>178</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -47799,12 +47799,12 @@
       </c>
       <c r="Q212" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
@@ -47814,7 +47814,7 @@
       </c>
       <c r="T212" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U212" t="inlineStr">
@@ -47841,19 +47841,19 @@
       <c r="Z212" t="inlineStr"/>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr"/>
       <c r="AC212" t="inlineStr"/>
       <c r="AD212" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -47873,7 +47873,7 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -47888,12 +47888,12 @@
       </c>
       <c r="AL212" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
@@ -47913,7 +47913,7 @@
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AR212" t="inlineStr">
@@ -47928,37 +47928,37 @@
       </c>
       <c r="AT212" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>178</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.0</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
@@ -48005,7 +48005,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:08</t>
+          <t>2026-03-16 02:48:44</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48246,7 +48246,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:08</t>
+          <t>2026-03-16 02:48:44</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -48487,7 +48487,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:08</t>
+          <t>2026-03-16 02:48:44</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48728,7 +48728,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:08</t>
+          <t>2026-03-16 02:48:44</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48954,7 +48954,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -48969,17 +48969,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:10</t>
+          <t>2026-03-16 02:48:47</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -48992,7 +48992,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N217" t="inlineStr"/>
@@ -49000,12 +49000,12 @@
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
@@ -49015,7 +49015,7 @@
       </c>
       <c r="T217" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="U217" t="inlineStr">
@@ -49025,12 +49025,12 @@
       </c>
       <c r="V217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
@@ -49040,26 +49040,26 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr"/>
       <c r="AA217" t="inlineStr"/>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AC217" t="inlineStr"/>
       <c r="AD217" t="inlineStr"/>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -49069,12 +49069,12 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -49084,22 +49084,22 @@
       </c>
       <c r="AK217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AL217" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>01:30 - 02:00</t>
+          <t>02:00 - 02:30</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -49109,12 +49109,12 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AQ217" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AR217" t="inlineStr">
@@ -49124,22 +49124,22 @@
       </c>
       <c r="AS217" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AT217" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
@@ -49149,12 +49149,12 @@
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>1020.8</t>
+          <t>1021.0</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
@@ -49202,7 +49202,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:12</t>
+          <t>2026-03-16 02:48:48</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49435,7 +49435,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:12</t>
+          <t>2026-03-16 02:48:48</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -49668,7 +49668,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:12</t>
+          <t>2026-03-16 02:48:48</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -49901,7 +49901,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>2026-03-16 02:19:12</t>
+          <t>2026-03-16 02:48:48</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -50173,7 +50173,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -50204,7 +50204,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -50235,7 +50235,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -50266,7 +50266,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -50297,7 +50297,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -50359,7 +50359,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -50390,7 +50390,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -50421,7 +50421,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -50452,7 +50452,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -50514,7 +50514,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -50545,7 +50545,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -50576,7 +50576,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -50607,7 +50607,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -50638,7 +50638,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -50669,7 +50669,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -50700,7 +50700,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -50731,7 +50731,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -50762,7 +50762,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -50793,7 +50793,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -50824,7 +50824,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -50855,7 +50855,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -50886,7 +50886,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -50948,7 +50948,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -50979,7 +50979,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -51010,7 +51010,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -51041,7 +51041,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -51072,7 +51072,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -51103,7 +51103,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -51134,7 +51134,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -51165,7 +51165,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -51196,7 +51196,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -51227,7 +51227,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -51289,7 +51289,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -51382,7 +51382,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -51413,7 +51413,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -51444,7 +51444,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -51475,7 +51475,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -51506,7 +51506,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -51537,7 +51537,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T01:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T02:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:28</t>
+          <t>2026-03-16 04:45:28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -748,12 +748,12 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -764,7 +764,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -795,17 +795,17 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -835,17 +835,17 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:29</t>
+          <t>2026-03-16 04:45:29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:29</t>
+          <t>2026-03-16 04:45:29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:29</t>
+          <t>2026-03-16 04:45:29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:29</t>
+          <t>2026-03-16 04:45:29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:31</t>
+          <t>2026-03-16 04:45:31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1732,7 +1732,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>243</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1763,56 +1763,56 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1827,32 +1827,32 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-4.2</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>243</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:33</t>
+          <t>2026-03-16 04:45:33</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:33</t>
+          <t>2026-03-16 04:45:33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:33</t>
+          <t>2026-03-16 04:45:33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:33</t>
+          <t>2026-03-16 04:45:33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:35</t>
+          <t>2026-03-16 04:45:35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>259</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2903,12 +2903,12 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>77</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2928,17 +2928,17 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2957,27 +2957,27 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2992,32 +2992,32 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:37</t>
+          <t>2026-03-16 04:45:36</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:37</t>
+          <t>2026-03-16 04:45:36</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:37</t>
+          <t>2026-03-16 04:45:36</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:37</t>
+          <t>2026-03-16 04:45:36</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:39</t>
+          <t>2026-03-16 04:45:39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4038,17 +4038,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>326</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -4069,56 +4069,56 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>-3.8</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
           <t>-4.4</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-4.9</t>
-        </is>
-      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4128,37 +4128,37 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-4.7</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
+          <t>-3.8</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
           <t>-4.4</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-4.9</t>
-        </is>
-      </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -4168,22 +4168,22 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>131</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>326</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:41</t>
+          <t>2026-03-16 04:45:40</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:41</t>
+          <t>2026-03-16 04:45:40</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:41</t>
+          <t>2026-03-16 04:45:40</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:41</t>
+          <t>2026-03-16 04:45:40</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:43</t>
+          <t>2026-03-16 04:45:43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>281</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -5209,12 +5209,12 @@
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -5234,56 +5234,56 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -5293,37 +5293,37 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>281</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -5333,22 +5333,22 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>281</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>1017.3</t>
+          <t>1017.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:45</t>
+          <t>2026-03-16 04:45:44</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:45</t>
+          <t>2026-03-16 04:45:44</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:45</t>
+          <t>2026-03-16 04:45:44</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-16 04:15:45</t>
+          <t>2026-03-16 04:45:44</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:00</t>
+          <t>2026-03-16 04:45:58</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>310</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -6374,12 +6374,12 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -6404,31 +6404,31 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -6438,17 +6438,17 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -6458,17 +6458,17 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
@@ -6478,17 +6478,17 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>310</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>1017.7</t>
+          <t>1017.6</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:02</t>
+          <t>2026-03-16 04:46:00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:02</t>
+          <t>2026-03-16 04:46:00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:02</t>
+          <t>2026-03-16 04:46:00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:02</t>
+          <t>2026-03-16 04:46:00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:04</t>
+          <t>2026-03-16 04:46:02</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7532,14 +7532,14 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>342</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R32" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -7560,56 +7560,56 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -7619,37 +7619,37 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
@@ -7659,17 +7659,17 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>342</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -7680,7 +7680,7 @@
       <c r="AW32" t="inlineStr"/>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:05</t>
+          <t>2026-03-16 04:46:04</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:05</t>
+          <t>2026-03-16 04:46:04</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:05</t>
+          <t>2026-03-16 04:46:04</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:05</t>
+          <t>2026-03-16 04:46:04</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8613,17 +8613,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:08</t>
+          <t>2026-03-16 04:46:06</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8637,14 +8637,14 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R37" t="inlineStr"/>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -8665,17 +8665,17 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
           <t>2.4</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>4.0</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -8688,93 +8688,93 @@
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
           <t>2.4</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>114</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -8785,7 +8785,7 @@
       <c r="AW37" t="inlineStr"/>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:09</t>
+          <t>2026-03-16 04:46:07</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:09</t>
+          <t>2026-03-16 04:46:07</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:09</t>
+          <t>2026-03-16 04:46:07</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:09</t>
+          <t>2026-03-16 04:46:07</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:12</t>
+          <t>2026-03-16 04:46:10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -9745,7 +9745,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R42" t="inlineStr"/>
@@ -9756,23 +9756,23 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -9783,27 +9783,27 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -9815,27 +9815,27 @@
       <c r="AL42" t="inlineStr"/>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:13</t>
+          <t>2026-03-16 04:46:11</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:13</t>
+          <t>2026-03-16 04:46:11</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:13</t>
+          <t>2026-03-16 04:46:11</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:13</t>
+          <t>2026-03-16 04:46:11</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10568,7 +10568,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10583,17 +10583,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:15</t>
+          <t>2026-03-16 04:46:13</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -10610,7 +10610,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -10632,12 +10632,12 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -10648,7 +10648,7 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -10658,17 +10658,17 @@
       </c>
       <c r="AG47" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -10680,7 +10680,7 @@
       <c r="AL47" t="inlineStr"/>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
@@ -10690,17 +10690,17 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:17</t>
+          <t>2026-03-16 04:46:14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:17</t>
+          <t>2026-03-16 04:46:14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:17</t>
+          <t>2026-03-16 04:46:14</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:17</t>
+          <t>2026-03-16 04:46:14</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -11448,17 +11448,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:19</t>
+          <t>2026-03-16 04:46:17</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>276</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -11483,12 +11483,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1023.3</t>
+          <t>1023.5</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -11508,56 +11508,56 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AG52" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -11572,32 +11572,32 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>51</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
@@ -11612,37 +11612,37 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>1023.3</t>
+          <t>1023.5</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>276</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>1023.3</t>
+          <t>1023.5</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:21</t>
+          <t>2026-03-16 04:46:18</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:21</t>
+          <t>2026-03-16 04:46:18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:21</t>
+          <t>2026-03-16 04:46:18</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12412,7 +12412,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:21</t>
+          <t>2026-03-16 04:46:18</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -12653,17 +12653,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:23</t>
+          <t>2026-03-16 04:46:20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>322</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -12684,7 +12684,7 @@
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="R57" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -12705,56 +12705,56 @@
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -12764,37 +12764,37 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.8</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
@@ -12804,17 +12804,17 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
@@ -12825,7 +12825,7 @@
       <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:25</t>
+          <t>2026-03-16 04:46:22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:25</t>
+          <t>2026-03-16 04:46:22</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:25</t>
+          <t>2026-03-16 04:46:22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:25</t>
+          <t>2026-03-16 04:46:22</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13743,7 +13743,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -13758,17 +13758,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:27</t>
+          <t>2026-03-16 04:46:24</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -13785,7 +13785,7 @@
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R62" t="inlineStr"/>
@@ -13796,23 +13796,23 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -13823,27 +13823,27 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AG62" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -13855,27 +13855,27 @@
       <c r="AL62" t="inlineStr"/>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="AP62" t="inlineStr">
-        <is>
-          <t>10.3</t>
-        </is>
-      </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:28</t>
+          <t>2026-03-16 04:46:25</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:28</t>
+          <t>2026-03-16 04:46:25</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:28</t>
+          <t>2026-03-16 04:46:25</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:28</t>
+          <t>2026-03-16 04:46:25</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -14623,17 +14623,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:31</t>
+          <t>2026-03-16 04:46:28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -14658,7 +14658,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R67" t="inlineStr"/>
@@ -14669,7 +14669,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -14679,17 +14679,17 @@
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -14701,34 +14701,34 @@
       <c r="AA67" t="inlineStr"/>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -14748,27 +14748,27 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -14788,12 +14788,12 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:32</t>
+          <t>2026-03-16 04:46:29</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15089,7 +15089,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:32</t>
+          <t>2026-03-16 04:46:29</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:32</t>
+          <t>2026-03-16 04:46:29</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:32</t>
+          <t>2026-03-16 04:46:29</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15773,7 +15773,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -15788,17 +15788,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:35</t>
+          <t>2026-03-16 04:46:32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -15811,14 +15811,14 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -15844,51 +15844,51 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AG72" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
@@ -15903,32 +15903,32 @@
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
@@ -15943,22 +15943,22 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -15968,12 +15968,12 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>24.8</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
@@ -16021,7 +16021,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:36</t>
+          <t>2026-03-16 04:46:33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:36</t>
+          <t>2026-03-16 04:46:33</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16487,7 +16487,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:36</t>
+          <t>2026-03-16 04:46:33</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:36</t>
+          <t>2026-03-16 04:46:33</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -16953,17 +16953,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:39</t>
+          <t>2026-03-16 04:46:35</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16976,7 +16976,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
@@ -16989,7 +16989,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.3</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -16999,7 +16999,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -17009,17 +17009,17 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
           <t>-0.4</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>-0.1</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -17031,29 +17031,29 @@
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
         <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
@@ -17073,27 +17073,27 @@
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -17113,17 +17113,17 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>325</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.3</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -17133,12 +17133,12 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>1018.0</t>
+          <t>1018.3</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:40</t>
+          <t>2026-03-16 04:46:37</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:40</t>
+          <t>2026-03-16 04:46:37</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17652,7 +17652,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:40</t>
+          <t>2026-03-16 04:46:37</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17885,7 +17885,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:40</t>
+          <t>2026-03-16 04:46:37</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -18118,17 +18118,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:42</t>
+          <t>2026-03-16 04:46:39</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18141,7 +18141,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -18149,7 +18149,7 @@
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R82" t="inlineStr"/>
@@ -18160,7 +18160,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -18170,56 +18170,56 @@
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AG82" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -18229,37 +18229,37 @@
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
@@ -18269,17 +18269,17 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -18290,7 +18290,7 @@
       <c r="AW82" t="inlineStr"/>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:44</t>
+          <t>2026-03-16 04:46:40</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:44</t>
+          <t>2026-03-16 04:46:40</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:44</t>
+          <t>2026-03-16 04:46:40</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19002,7 +19002,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:44</t>
+          <t>2026-03-16 04:46:40</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -19223,17 +19223,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:46</t>
+          <t>2026-03-16 04:46:43</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="R87" t="inlineStr"/>
@@ -19269,7 +19269,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -19279,56 +19279,56 @@
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -19343,32 +19343,32 @@
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:47</t>
+          <t>2026-03-16 04:46:44</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19689,7 +19689,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:47</t>
+          <t>2026-03-16 04:46:44</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:47</t>
+          <t>2026-03-16 04:46:44</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:47</t>
+          <t>2026-03-16 04:46:44</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -20388,17 +20388,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:50</t>
+          <t>2026-03-16 04:46:46</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -20419,12 +20419,12 @@
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1023.2</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -20449,17 +20449,17 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr"/>
@@ -20473,7 +20473,7 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -20483,17 +20483,17 @@
       </c>
       <c r="AG92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -20503,17 +20503,17 @@
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
@@ -20523,17 +20523,17 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AR92" t="inlineStr">
@@ -20543,12 +20543,12 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AU92" t="inlineStr">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>1023.2</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>1023.2</t>
+          <t>1023.6</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:51</t>
+          <t>2026-03-16 04:46:48</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:51</t>
+          <t>2026-03-16 04:46:48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:51</t>
+          <t>2026-03-16 04:46:48</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21320,7 +21320,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:51</t>
+          <t>2026-03-16 04:46:48</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -21553,17 +21553,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:54</t>
+          <t>2026-03-16 04:46:50</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21578,7 +21578,7 @@
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -21588,7 +21588,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R97" t="inlineStr"/>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
@@ -21609,136 +21609,136 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr">
+        <is>
+          <t>32.8</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AP97" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AT97" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="AV97" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
-      </c>
-      <c r="AW97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:55</t>
+          <t>2026-03-16 04:46:51</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22019,7 +22019,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:55</t>
+          <t>2026-03-16 04:46:51</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:55</t>
+          <t>2026-03-16 04:46:51</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22485,7 +22485,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:55</t>
+          <t>2026-03-16 04:46:51</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22703,7 +22703,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -22718,17 +22718,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:58</t>
+          <t>2026-03-16 04:46:54</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22743,7 +22743,7 @@
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R102" t="inlineStr"/>
@@ -22764,7 +22764,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -22774,56 +22774,56 @@
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AG102" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -22838,32 +22838,32 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>-4.3</t>
+          <t>-4.1</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>-4.4</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
@@ -22878,17 +22878,17 @@
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -22898,12 +22898,12 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>360</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
@@ -22951,7 +22951,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:59</t>
+          <t>2026-03-16 04:46:55</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:59</t>
+          <t>2026-03-16 04:46:55</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23417,7 +23417,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:59</t>
+          <t>2026-03-16 04:46:55</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-16 04:16:59</t>
+          <t>2026-03-16 04:46:55</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23868,7 +23868,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -23883,17 +23883,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:02</t>
+          <t>2026-03-16 04:46:57</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>268</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -23929,7 +23929,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -23939,17 +23939,17 @@
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -23961,29 +23961,29 @@
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
@@ -24003,27 +24003,27 @@
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -24043,12 +24043,12 @@
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -24063,7 +24063,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -24116,7 +24116,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:03</t>
+          <t>2026-03-16 04:46:59</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:03</t>
+          <t>2026-03-16 04:46:59</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24582,7 +24582,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:03</t>
+          <t>2026-03-16 04:46:59</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24815,7 +24815,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:03</t>
+          <t>2026-03-16 04:46:59</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -25048,17 +25048,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:06</t>
+          <t>2026-03-16 04:47:01</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25073,7 +25073,7 @@
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R112" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -25104,121 +25104,121 @@
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="AG112" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>18.7</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>-1.9</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>-1.3</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="AP112" t="inlineStr">
-        <is>
-          <t>-1.8</t>
-        </is>
-      </c>
-      <c r="AQ112" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -25228,12 +25228,12 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:07</t>
+          <t>2026-03-16 04:47:03</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:07</t>
+          <t>2026-03-16 04:47:03</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25747,7 +25747,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:07</t>
+          <t>2026-03-16 04:47:03</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -25980,7 +25980,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:07</t>
+          <t>2026-03-16 04:47:03</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:20</t>
+          <t>2026-03-16 04:47:15</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -26454,7 +26454,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:20</t>
+          <t>2026-03-16 04:47:15</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26695,7 +26695,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:20</t>
+          <t>2026-03-16 04:47:15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:20</t>
+          <t>2026-03-16 04:47:15</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27162,7 +27162,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -27177,17 +27177,17 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:23</t>
+          <t>2026-03-16 04:47:17</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -27200,7 +27200,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
@@ -27212,7 +27212,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="R121" t="inlineStr"/>
@@ -27223,7 +27223,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -27233,56 +27233,56 @@
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
       <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -27297,32 +27297,32 @@
       </c>
       <c r="AL121" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
@@ -27337,17 +27337,17 @@
       </c>
       <c r="AT121" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
@@ -27357,12 +27357,12 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>25.9</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
@@ -27410,7 +27410,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:24</t>
+          <t>2026-03-16 04:47:19</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:24</t>
+          <t>2026-03-16 04:47:19</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:24</t>
+          <t>2026-03-16 04:47:19</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28109,7 +28109,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:24</t>
+          <t>2026-03-16 04:47:19</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28327,7 +28327,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -28342,17 +28342,17 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:27</t>
+          <t>2026-03-16 04:47:21</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>233</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -28373,12 +28373,12 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -28388,7 +28388,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -28398,96 +28398,96 @@
       </c>
       <c r="V126" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr"/>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="AG126" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
+          <t>-1.2</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN126" t="inlineStr">
+        <is>
           <t>-0.7</t>
         </is>
       </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="AL126" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
@@ -28497,22 +28497,22 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
@@ -28522,12 +28522,12 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>1018.8</t>
+          <t>1019.3</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:28</t>
+          <t>2026-03-16 04:47:23</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:28</t>
+          <t>2026-03-16 04:47:23</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29041,7 +29041,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:28</t>
+          <t>2026-03-16 04:47:23</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:28</t>
+          <t>2026-03-16 04:47:23</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -29507,17 +29507,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:30</t>
+          <t>2026-03-16 04:47:25</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -29530,7 +29530,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
@@ -29538,7 +29538,7 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R131" t="inlineStr"/>
@@ -29549,7 +29549,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -29559,56 +29559,56 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -29618,37 +29618,37 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
@@ -29658,17 +29658,17 @@
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
@@ -29679,7 +29679,7 @@
       <c r="AW131" t="inlineStr"/>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -29728,7 +29728,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:32</t>
+          <t>2026-03-16 04:47:26</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:32</t>
+          <t>2026-03-16 04:47:26</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30170,7 +30170,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:32</t>
+          <t>2026-03-16 04:47:26</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30391,7 +30391,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:32</t>
+          <t>2026-03-16 04:47:26</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -30612,17 +30612,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:34</t>
+          <t>2026-03-16 04:47:29</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -30635,7 +30635,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
@@ -30648,7 +30648,7 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -30658,7 +30658,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -30668,48 +30668,48 @@
       </c>
       <c r="V136" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>9.3</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr"/>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr"/>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AH136" t="inlineStr">
         <is>
           <t>9.3</t>
@@ -30727,29 +30727,29 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
       <c r="AP136" t="inlineStr">
         <is>
           <t>9.3</t>
@@ -30767,22 +30767,22 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
@@ -30792,12 +30792,12 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>1016.8</t>
+          <t>1016.9</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:36</t>
+          <t>2026-03-16 04:47:30</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -31078,7 +31078,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:36</t>
+          <t>2026-03-16 04:47:30</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31311,7 +31311,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:36</t>
+          <t>2026-03-16 04:47:30</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31544,7 +31544,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:36</t>
+          <t>2026-03-16 04:47:30</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31762,7 +31762,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -31777,17 +31777,17 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:38</t>
+          <t>2026-03-16 04:47:33</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -31800,7 +31800,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>358</t>
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
@@ -31808,12 +31808,12 @@
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>1015.3</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="S141" t="inlineStr">
@@ -31823,7 +31823,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -31838,7 +31838,7 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
@@ -31848,21 +31848,21 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr"/>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -31877,12 +31877,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -31892,17 +31892,17 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
@@ -31917,12 +31917,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
@@ -31932,22 +31932,22 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>358</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>1015.3</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
@@ -31957,12 +31957,12 @@
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>111.6</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>1015.3</t>
+          <t>1015.5</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
@@ -32010,7 +32010,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:40</t>
+          <t>2026-03-16 04:47:34</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -32243,7 +32243,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:40</t>
+          <t>2026-03-16 04:47:34</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32476,7 +32476,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:40</t>
+          <t>2026-03-16 04:47:34</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32709,7 +32709,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:40</t>
+          <t>2026-03-16 04:47:34</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32927,7 +32927,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -32942,17 +32942,17 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:42</t>
+          <t>2026-03-16 04:47:37</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -32966,7 +32966,7 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>306</t>
         </is>
       </c>
       <c r="O146" t="inlineStr"/>
@@ -32977,7 +32977,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>98</t>
         </is>
       </c>
       <c r="R146" t="inlineStr"/>
@@ -32988,7 +32988,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -32998,121 +32998,121 @@
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
           <t>-1.2</t>
-        </is>
-      </c>
-      <c r="X146" t="inlineStr">
-        <is>
-          <t>0.5</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr"/>
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="AG146" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="AH146" t="inlineStr">
         <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>-1.4</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
           <t>-1.2</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AL146" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="AM146" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>-0.1</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="AP146" t="inlineStr">
-        <is>
-          <t>-1.2</t>
-        </is>
-      </c>
-      <c r="AQ146" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>306</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
@@ -33122,12 +33122,12 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>306</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
@@ -33175,7 +33175,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:44</t>
+          <t>2026-03-16 04:47:38</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -33408,7 +33408,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:44</t>
+          <t>2026-03-16 04:47:38</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33641,7 +33641,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:44</t>
+          <t>2026-03-16 04:47:38</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:44</t>
+          <t>2026-03-16 04:47:38</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34092,7 +34092,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -34107,17 +34107,17 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:46</t>
+          <t>2026-03-16 04:47:40</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -34130,7 +34130,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
@@ -34138,12 +34138,12 @@
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
@@ -34153,7 +34153,7 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U151" t="inlineStr">
@@ -34163,56 +34163,56 @@
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="inlineStr"/>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG151" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -34222,37 +34222,37 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
@@ -34262,22 +34262,22 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
@@ -34287,12 +34287,12 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>1022.3</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
@@ -34340,7 +34340,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:48</t>
+          <t>2026-03-16 04:47:42</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -34573,7 +34573,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:48</t>
+          <t>2026-03-16 04:47:42</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:48</t>
+          <t>2026-03-16 04:47:42</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -35039,7 +35039,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:48</t>
+          <t>2026-03-16 04:47:42</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -35257,7 +35257,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -35272,17 +35272,17 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:50</t>
+          <t>2026-03-16 04:47:44</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -35295,7 +35295,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
@@ -35307,12 +35307,12 @@
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.3</t>
         </is>
       </c>
       <c r="S156" t="inlineStr">
@@ -35322,7 +35322,7 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U156" t="inlineStr">
@@ -35332,56 +35332,56 @@
       </c>
       <c r="V156" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>-0.8</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="Z156" t="inlineStr"/>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="inlineStr"/>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -35396,32 +35396,32 @@
       </c>
       <c r="AL156" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
           <t>-0.3</t>
         </is>
       </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
@@ -35436,37 +35436,37 @@
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.3</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>849.8</t>
+          <t>850.3</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:52</t>
+          <t>2026-03-16 04:47:46</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -35754,7 +35754,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:52</t>
+          <t>2026-03-16 04:47:46</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -35995,7 +35995,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:52</t>
+          <t>2026-03-16 04:47:46</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -36236,7 +36236,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:52</t>
+          <t>2026-03-16 04:47:46</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -36462,7 +36462,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -36477,17 +36477,17 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:54</t>
+          <t>2026-03-16 04:47:48</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K161" t="n">
@@ -36500,7 +36500,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
@@ -36517,7 +36517,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>1022.1</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="S161" t="inlineStr">
@@ -36527,7 +36527,7 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U161" t="inlineStr">
@@ -36552,21 +36552,21 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr"/>
       <c r="AA161" t="inlineStr"/>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr"/>
       <c r="AD161" t="inlineStr"/>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -36601,12 +36601,12 @@
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
@@ -36641,37 +36641,37 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>1022.1</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>1022.1</t>
+          <t>1022.2</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
@@ -36718,7 +36718,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:55</t>
+          <t>2026-03-16 04:47:49</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -36959,7 +36959,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:55</t>
+          <t>2026-03-16 04:47:49</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -37200,7 +37200,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:55</t>
+          <t>2026-03-16 04:47:49</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -37441,7 +37441,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:55</t>
+          <t>2026-03-16 04:47:49</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -37667,7 +37667,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -37682,17 +37682,17 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>2026-03-16 04:17:58</t>
+          <t>2026-03-16 04:47:52</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K166" t="n">
@@ -37705,7 +37705,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
@@ -37728,7 +37728,7 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U166" t="inlineStr">
@@ -37738,51 +37738,51 @@
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr"/>
       <c r="AA166" t="inlineStr"/>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr"/>
       <c r="AD166" t="inlineStr"/>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AG166" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AI166" t="inlineStr">
@@ -37797,32 +37797,32 @@
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AL166" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AQ166" t="inlineStr">
@@ -37837,17 +37837,17 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>22.7</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
@@ -37862,7 +37862,7 @@
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -37915,7 +37915,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:00</t>
+          <t>2026-03-16 04:47:53</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:00</t>
+          <t>2026-03-16 04:47:53</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -38381,7 +38381,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:00</t>
+          <t>2026-03-16 04:47:53</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -38614,7 +38614,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:00</t>
+          <t>2026-03-16 04:47:53</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -38847,7 +38847,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:12</t>
+          <t>2026-03-16 04:48:05</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -39068,7 +39068,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:12</t>
+          <t>2026-03-16 04:48:05</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -39289,7 +39289,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:12</t>
+          <t>2026-03-16 04:48:05</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -39510,7 +39510,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:12</t>
+          <t>2026-03-16 04:48:05</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -39716,7 +39716,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -39731,17 +39731,17 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:14</t>
+          <t>2026-03-16 04:48:07</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -39754,7 +39754,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>298</t>
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
@@ -39762,7 +39762,7 @@
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R175" t="inlineStr"/>
@@ -39773,7 +39773,7 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U175" t="inlineStr">
@@ -39783,96 +39783,96 @@
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr"/>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr"/>
       <c r="AD175" t="inlineStr"/>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="AG175" t="inlineStr">
         <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN175" t="inlineStr">
+        <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>1.7</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AJ175" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
-      </c>
-      <c r="AL175" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="AM175" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
@@ -39882,17 +39882,17 @@
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>298</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
@@ -39903,7 +39903,7 @@
       <c r="AW175" t="inlineStr"/>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -39952,7 +39952,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:15</t>
+          <t>2026-03-16 04:48:09</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -40173,7 +40173,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:15</t>
+          <t>2026-03-16 04:48:09</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -40394,7 +40394,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:15</t>
+          <t>2026-03-16 04:48:09</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -40615,7 +40615,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:15</t>
+          <t>2026-03-16 04:48:09</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -40836,7 +40836,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:28</t>
+          <t>2026-03-16 04:48:20</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -41069,7 +41069,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:28</t>
+          <t>2026-03-16 04:48:20</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -41302,7 +41302,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:28</t>
+          <t>2026-03-16 04:48:20</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -41535,7 +41535,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:28</t>
+          <t>2026-03-16 04:48:20</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -41753,7 +41753,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -41768,17 +41768,17 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:30</t>
+          <t>2026-03-16 04:48:23</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K184" t="n">
@@ -41794,7 +41794,7 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q184" t="inlineStr">
@@ -41814,7 +41814,7 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U184" t="inlineStr"/>
@@ -41825,12 +41825,12 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr"/>
@@ -41841,7 +41841,7 @@
       <c r="AD184" t="inlineStr"/>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -41851,12 +41851,12 @@
       </c>
       <c r="AG184" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
@@ -41871,7 +41871,7 @@
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
@@ -41881,7 +41881,7 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
@@ -41891,12 +41891,12 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
@@ -41965,7 +41965,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:32</t>
+          <t>2026-03-16 04:48:24</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -42150,7 +42150,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:32</t>
+          <t>2026-03-16 04:48:24</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -42347,7 +42347,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:32</t>
+          <t>2026-03-16 04:48:24</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -42544,7 +42544,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:32</t>
+          <t>2026-03-16 04:48:24</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -42726,7 +42726,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -42741,17 +42741,17 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:34</t>
+          <t>2026-03-16 04:48:26</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -42764,7 +42764,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>293</t>
         </is>
       </c>
       <c r="N189" t="inlineStr"/>
@@ -42777,7 +42777,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
@@ -42787,7 +42787,7 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U189" t="inlineStr">
@@ -42797,51 +42797,51 @@
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="Z189" t="inlineStr"/>
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="inlineStr"/>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
@@ -42856,32 +42856,32 @@
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
@@ -42896,22 +42896,22 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>293</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
@@ -42921,12 +42921,12 @@
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>1018.1</t>
+          <t>1018.2</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
@@ -42974,7 +42974,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:36</t>
+          <t>2026-03-16 04:48:28</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -43207,7 +43207,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:36</t>
+          <t>2026-03-16 04:48:28</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -43440,7 +43440,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:36</t>
+          <t>2026-03-16 04:48:28</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:36</t>
+          <t>2026-03-16 04:48:28</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -43891,7 +43891,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -43906,17 +43906,17 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:38</t>
+          <t>2026-03-16 04:48:30</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -43933,7 +43933,7 @@
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="R194" t="inlineStr"/>
@@ -43944,23 +43944,23 @@
       </c>
       <c r="T194" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U194" t="inlineStr"/>
       <c r="V194" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr"/>
@@ -43971,27 +43971,27 @@
       <c r="AD194" t="inlineStr"/>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AG194" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -44003,27 +44003,27 @@
       <c r="AL194" t="inlineStr"/>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>10.7</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
@@ -44079,7 +44079,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:39</t>
+          <t>2026-03-16 04:48:31</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -44252,7 +44252,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:39</t>
+          <t>2026-03-16 04:48:31</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -44425,7 +44425,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:39</t>
+          <t>2026-03-16 04:48:31</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -44598,7 +44598,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:39</t>
+          <t>2026-03-16 04:48:31</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -44756,7 +44756,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -44771,17 +44771,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:41</t>
+          <t>2026-03-16 04:48:34</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -44794,7 +44794,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>305</t>
         </is>
       </c>
       <c r="N199" t="inlineStr"/>
@@ -44802,7 +44802,7 @@
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R199" t="inlineStr"/>
@@ -44813,7 +44813,7 @@
       </c>
       <c r="T199" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U199" t="inlineStr">
@@ -44823,17 +44823,17 @@
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -44845,94 +44845,94 @@
       <c r="AA199" t="inlineStr"/>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="inlineStr"/>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AH199" t="inlineStr">
         <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="AL199" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>04:00 - 04:30</t>
+        </is>
+      </c>
+      <c r="AN199" t="inlineStr">
+        <is>
           <t>-1.1</t>
         </is>
       </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AJ199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR199" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
-      <c r="AL199" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="AM199" t="inlineStr">
-        <is>
-          <t>03:30 - 04:00</t>
-        </is>
-      </c>
-      <c r="AN199" t="inlineStr">
-        <is>
-          <t>-0.7</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="AP199" t="inlineStr">
-        <is>
-          <t>-1.1</t>
-        </is>
-      </c>
-      <c r="AQ199" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AS199" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>305</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
@@ -44943,7 +44943,7 @@
       <c r="AW199" t="inlineStr"/>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -44992,7 +44992,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:43</t>
+          <t>2026-03-16 04:48:35</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -45213,7 +45213,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:43</t>
+          <t>2026-03-16 04:48:35</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -45434,7 +45434,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:43</t>
+          <t>2026-03-16 04:48:35</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -45655,7 +45655,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:43</t>
+          <t>2026-03-16 04:48:35</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -45861,7 +45861,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -45876,17 +45876,17 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:45</t>
+          <t>2026-03-16 04:48:38</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K204" t="n">
@@ -45899,7 +45899,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>61</t>
         </is>
       </c>
       <c r="N204" t="inlineStr"/>
@@ -45916,7 +45916,7 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>853.1</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
@@ -45926,7 +45926,7 @@
       </c>
       <c r="T204" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U204" t="inlineStr">
@@ -45936,12 +45936,12 @@
       </c>
       <c r="V204" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
@@ -45951,26 +45951,26 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="Z204" t="inlineStr"/>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="inlineStr"/>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AG204" t="inlineStr">
@@ -45980,7 +45980,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
@@ -46000,17 +46000,17 @@
       </c>
       <c r="AL204" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>-3.6</t>
+          <t>-3.5</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -46020,7 +46020,7 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>-3.8</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
@@ -46040,37 +46040,37 @@
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>853.1</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>852.7</t>
+          <t>853.1</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
@@ -46117,7 +46117,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:47</t>
+          <t>2026-03-16 04:48:39</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -46358,7 +46358,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:47</t>
+          <t>2026-03-16 04:48:39</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:47</t>
+          <t>2026-03-16 04:48:39</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -46840,7 +46840,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:47</t>
+          <t>2026-03-16 04:48:39</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -47066,7 +47066,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -47081,17 +47081,17 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:49</t>
+          <t>2026-03-16 04:48:42</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -47106,12 +47106,12 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>180</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -47121,7 +47121,7 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.8</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
@@ -47131,7 +47131,7 @@
       </c>
       <c r="T209" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U209" t="inlineStr">
@@ -47146,31 +47146,31 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="Y209" t="inlineStr"/>
       <c r="Z209" t="inlineStr"/>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AB209" t="inlineStr"/>
       <c r="AC209" t="inlineStr"/>
       <c r="AD209" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -47180,12 +47180,12 @@
       </c>
       <c r="AG209" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AI209" t="inlineStr">
@@ -47200,17 +47200,17 @@
       </c>
       <c r="AK209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AL209" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
@@ -47220,12 +47220,12 @@
       </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-3.8</t>
         </is>
       </c>
       <c r="AQ209" t="inlineStr">
@@ -47240,42 +47240,42 @@
       </c>
       <c r="AS209" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AT209" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.8</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>180</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>1028.4</t>
+          <t>1028.8</t>
         </is>
       </c>
       <c r="BA209" t="inlineStr">
@@ -47322,7 +47322,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:51</t>
+          <t>2026-03-16 04:48:43</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -47563,7 +47563,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:51</t>
+          <t>2026-03-16 04:48:43</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -47804,7 +47804,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:51</t>
+          <t>2026-03-16 04:48:43</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:51</t>
+          <t>2026-03-16 04:48:43</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -48271,7 +48271,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -48286,17 +48286,17 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:54</t>
+          <t>2026-03-16 04:48:45</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>03:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -48309,7 +48309,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="N214" t="inlineStr"/>
@@ -48322,7 +48322,7 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
@@ -48332,7 +48332,7 @@
       </c>
       <c r="T214" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="U214" t="inlineStr">
@@ -48342,7 +48342,7 @@
       </c>
       <c r="V214" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="W214" t="inlineStr">
@@ -48357,26 +48357,26 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr"/>
       <c r="AA214" t="inlineStr"/>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AC214" t="inlineStr"/>
       <c r="AD214" t="inlineStr"/>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AG214" t="inlineStr">
@@ -48401,22 +48401,22 @@
       </c>
       <c r="AK214" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AL214" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>03:30 - 04:00</t>
+          <t>04:00 - 04:30</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -48441,22 +48441,22 @@
       </c>
       <c r="AS214" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AT214" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
@@ -48466,12 +48466,12 @@
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>12.6</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>1021.1</t>
+          <t>1021.3</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
@@ -48519,7 +48519,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:55</t>
+          <t>2026-03-16 04:48:47</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -48752,7 +48752,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:55</t>
+          <t>2026-03-16 04:48:47</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -48985,7 +48985,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:55</t>
+          <t>2026-03-16 04:48:47</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -49218,7 +49218,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>2026-03-16 04:18:55</t>
+          <t>2026-03-16 04:48:47</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -49490,7 +49490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -49521,7 +49521,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -49552,7 +49552,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -49583,7 +49583,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -49614,7 +49614,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -49676,7 +49676,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -49707,7 +49707,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -49738,7 +49738,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -49769,7 +49769,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -49800,7 +49800,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -49831,7 +49831,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -49862,7 +49862,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -49893,7 +49893,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -49924,7 +49924,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -49955,7 +49955,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -49986,7 +49986,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -50017,7 +50017,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -50048,7 +50048,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -50079,7 +50079,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -50110,7 +50110,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -50141,7 +50141,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -50172,7 +50172,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -50203,7 +50203,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -50265,7 +50265,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -50296,7 +50296,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -50327,7 +50327,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -50358,7 +50358,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -50389,7 +50389,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -50420,7 +50420,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XR&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -50451,7 +50451,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YA&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -50482,7 +50482,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DG&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -50513,7 +50513,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X5&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -50544,7 +50544,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D4&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -50606,7 +50606,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -50668,7 +50668,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XH&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -50699,7 +50699,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -50730,7 +50730,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UE&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -50761,7 +50761,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XO&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -50792,7 +50792,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VS&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -50823,7 +50823,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YN&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -50854,7 +50854,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T03:30Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D7&amp;dia=2026-03-16T04:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>

--- a/src/data/resum_periode_meteocat.xlsx
+++ b/src/data/resum_periode_meteocat.xlsx
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:31</t>
+          <t>2026-03-17 15:15:33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YT&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:32</t>
+          <t>2026-03-17 15:15:35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:32</t>
+          <t>2026-03-17 15:15:35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:32</t>
+          <t>2026-03-17 15:15:35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:32</t>
+          <t>2026-03-17 15:15:35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:35</t>
+          <t>2026-03-17 15:15:38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z1&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:37</t>
+          <t>2026-03-17 15:15:40</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:37</t>
+          <t>2026-03-17 15:15:40</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:37</t>
+          <t>2026-03-17 15:15:40</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:37</t>
+          <t>2026-03-17 15:15:40</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:39</t>
+          <t>2026-03-17 15:15:42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DN&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:41</t>
+          <t>2026-03-17 15:15:44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:41</t>
+          <t>2026-03-17 15:15:44</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:41</t>
+          <t>2026-03-17 15:15:44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:41</t>
+          <t>2026-03-17 15:15:44</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4037,17 +4037,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:44</t>
+          <t>2026-03-17 15:15:47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z6&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:45</t>
+          <t>2026-03-17 15:15:48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:45</t>
+          <t>2026-03-17 15:15:48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:45</t>
+          <t>2026-03-17 15:15:48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:45</t>
+          <t>2026-03-17 15:15:48</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -5202,17 +5202,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:48</t>
+          <t>2026-03-17 15:15:51</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DJ&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:50</t>
+          <t>2026-03-17 15:15:52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:50</t>
+          <t>2026-03-17 15:15:52</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:50</t>
+          <t>2026-03-17 15:15:52</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:50</t>
+          <t>2026-03-17 15:15:52</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:52</t>
+          <t>2026-03-17 15:15:55</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=X4&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:54</t>
+          <t>2026-03-17 15:15:57</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:54</t>
+          <t>2026-03-17 15:15:57</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:54</t>
+          <t>2026-03-17 15:15:57</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:54</t>
+          <t>2026-03-17 15:15:57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:57</t>
+          <t>2026-03-17 15:15:59</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D5&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:58</t>
+          <t>2026-03-17 15:16:01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:58</t>
+          <t>2026-03-17 15:16:01</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:58</t>
+          <t>2026-03-17 15:16:01</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-03-17 14:45:58</t>
+          <t>2026-03-17 15:16:01</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -8697,17 +8697,17 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:01</t>
+          <t>2026-03-17 15:16:04</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YS&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -8918,7 +8918,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:03</t>
+          <t>2026-03-17 15:16:06</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:03</t>
+          <t>2026-03-17 15:16:06</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:03</t>
+          <t>2026-03-17 15:16:06</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:03</t>
+          <t>2026-03-17 15:16:06</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -9802,17 +9802,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:05</t>
+          <t>2026-03-17 15:16:08</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=UN&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:07</t>
+          <t>2026-03-17 15:16:10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:07</t>
+          <t>2026-03-17 15:16:10</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:07</t>
+          <t>2026-03-17 15:16:10</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:07</t>
+          <t>2026-03-17 15:16:10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:10</t>
+          <t>2026-03-17 15:16:12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=MS&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -11080,7 +11080,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:11</t>
+          <t>2026-03-17 15:16:13</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:11</t>
+          <t>2026-03-17 15:16:13</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:11</t>
+          <t>2026-03-17 15:16:13</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:11</t>
+          <t>2026-03-17 15:16:13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -11772,17 +11772,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:14</t>
+          <t>2026-03-17 15:16:15</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=W1&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:15</t>
+          <t>2026-03-17 15:16:16</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:15</t>
+          <t>2026-03-17 15:16:16</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:15</t>
+          <t>2026-03-17 15:16:16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:15</t>
+          <t>2026-03-17 15:16:16</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:18</t>
+          <t>2026-03-17 15:16:19</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=DP&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:19</t>
+          <t>2026-03-17 15:16:21</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:19</t>
+          <t>2026-03-17 15:16:21</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:19</t>
+          <t>2026-03-17 15:16:21</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -13601,7 +13601,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:19</t>
+          <t>2026-03-17 15:16:21</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:22</t>
+          <t>2026-03-17 15:16:23</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XL&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:24</t>
+          <t>2026-03-17 15:16:24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:24</t>
+          <t>2026-03-17 15:16:24</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:24</t>
+          <t>2026-03-17 15:16:24</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:24</t>
+          <t>2026-03-17 15:16:24</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -14947,17 +14947,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:26</t>
+          <t>2026-03-17 15:16:27</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VZ&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -15120,7 +15120,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:28</t>
+          <t>2026-03-17 15:16:28</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -15293,7 +15293,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:28</t>
+          <t>2026-03-17 15:16:28</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:28</t>
+          <t>2026-03-17 15:16:28</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:28</t>
+          <t>2026-03-17 15:16:28</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -15812,17 +15812,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:30</t>
+          <t>2026-03-17 15:16:31</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z7&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16045,7 +16045,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:32</t>
+          <t>2026-03-17 15:16:33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:32</t>
+          <t>2026-03-17 15:16:33</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:32</t>
+          <t>2026-03-17 15:16:33</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:32</t>
+          <t>2026-03-17 15:16:33</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -16977,17 +16977,17 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:34</t>
+          <t>2026-03-17 15:16:35</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XK&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:36</t>
+          <t>2026-03-17 15:16:36</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17443,7 +17443,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:36</t>
+          <t>2026-03-17 15:16:36</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:36</t>
+          <t>2026-03-17 15:16:36</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -17909,7 +17909,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:36</t>
+          <t>2026-03-17 15:16:36</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18142,17 +18142,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:38</t>
+          <t>2026-03-17 15:16:39</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=XJ&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -18375,7 +18375,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:40</t>
+          <t>2026-03-17 15:16:40</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -18608,7 +18608,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:40</t>
+          <t>2026-03-17 15:16:40</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:40</t>
+          <t>2026-03-17 15:16:40</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:40</t>
+          <t>2026-03-17 15:16:40</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -19307,17 +19307,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:43</t>
+          <t>2026-03-17 15:16:42</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YU&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -19528,7 +19528,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:44</t>
+          <t>2026-03-17 15:16:43</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:44</t>
+          <t>2026-03-17 15:16:43</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:44</t>
+          <t>2026-03-17 15:16:43</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:44</t>
+          <t>2026-03-17 15:16:43</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -20412,17 +20412,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:47</t>
+          <t>2026-03-17 15:16:46</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=ZE&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:49</t>
+          <t>2026-03-17 15:16:48</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:49</t>
+          <t>2026-03-17 15:16:48</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -21111,7 +21111,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:49</t>
+          <t>2026-03-17 15:16:48</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -21344,7 +21344,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:49</t>
+          <t>2026-03-17 15:16:48</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -21577,17 +21577,17 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:51</t>
+          <t>2026-03-17 15:16:50</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CD&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -21810,7 +21810,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:53</t>
+          <t>2026-03-17 15:16:52</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:53</t>
+          <t>2026-03-17 15:16:52</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:53</t>
+          <t>2026-03-17 15:16:52</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:53</t>
+          <t>2026-03-17 15:16:52</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -22742,17 +22742,17 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:56</t>
+          <t>2026-03-17 15:16:54</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z2&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -22975,7 +22975,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:58</t>
+          <t>2026-03-17 15:16:55</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:58</t>
+          <t>2026-03-17 15:16:55</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:58</t>
+          <t>2026-03-17 15:16:55</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2026-03-17 14:46:58</t>
+          <t>2026-03-17 15:16:55</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -23907,17 +23907,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:00</t>
+          <t>2026-03-17 15:16:58</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z5&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:02</t>
+          <t>2026-03-17 15:16:59</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:02</t>
+          <t>2026-03-17 15:16:59</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:02</t>
+          <t>2026-03-17 15:16:59</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:02</t>
+          <t>2026-03-17 15:16:59</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -25072,17 +25072,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:04</t>
+          <t>2026-03-17 15:17:01</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=VK&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:06</t>
+          <t>2026-03-17 15:17:03</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -25538,7 +25538,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:06</t>
+          <t>2026-03-17 15:17:03</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -25771,7 +25771,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:06</t>
+          <t>2026-03-17 15:17:03</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:06</t>
+          <t>2026-03-17 15:17:03</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -26237,17 +26237,17 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:09</t>
+          <t>2026-03-17 15:17:06</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z3&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -26470,7 +26470,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:10</t>
+          <t>2026-03-17 15:17:07</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -26703,7 +26703,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:10</t>
+          <t>2026-03-17 15:17:07</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:10</t>
+          <t>2026-03-17 15:17:07</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:10</t>
+          <t>2026-03-17 15:17:07</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -27402,17 +27402,17 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:13</t>
+          <t>2026-03-17 15:17:10</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=CG&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K122" t="n">
@@ -27643,7 +27643,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:15</t>
+          <t>2026-03-17 15:17:12</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:15</t>
+          <t>2026-03-17 15:17:12</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:15</t>
+          <t>2026-03-17 15:17:12</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -28366,7 +28366,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:15</t>
+          <t>2026-03-17 15:17:12</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -28607,17 +28607,17 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:17</t>
+          <t>2026-03-17 15:17:14</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=Z9&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -28840,7 +28840,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:19</t>
+          <t>2026-03-17 15:17:15</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -29073,7 +29073,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:19</t>
+          <t>2026-03-17 15:17:15</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:19</t>
+          <t>2026-03-17 15:17:15</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:19</t>
+          <t>2026-03-17 15:17:15</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -29772,17 +29772,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:22</t>
+          <t>2026-03-17 15:17:17</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YB&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -30005,7 +30005,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:23</t>
+          <t>2026-03-17 15:17:18</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -30238,7 +30238,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:23</t>
+          <t>2026-03-17 15:17:18</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:23</t>
+          <t>2026-03-17 15:17:18</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -30704,7 +30704,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:23</t>
+          <t>2026-03-17 15:17:18</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -30937,17 +30937,17 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:26</t>
+          <t>2026-03-17 15:17:21</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=YP&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:28</t>
+          <t>2026-03-17 15:17:22</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:28</t>
+          <t>2026-03-17 15:17:22</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -31600,7 +31600,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:28</t>
+          <t>2026-03-17 15:17:22</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -31821,7 +31821,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:28</t>
+          <t>2026-03-17 15:17:22</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -32042,17 +32042,17 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:30</t>
+          <t>2026-03-17 15:17:25</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=J5&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K142" t="n">
@@ -32275,7 +32275,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:31</t>
+          <t>2026-03-17 15:17:27</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -32508,7 +32508,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:31</t>
+          <t>2026-03-17 15:17:27</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -32741,7 +32741,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:31</t>
+          <t>2026-03-17 15:17:27</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:31</t>
+          <t>2026-03-17 15:17:27</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -33207,17 +33207,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:34</t>
+          <t>2026-03-17 15:17:29</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-17T14:00Z</t>
+          <t>https://www.meteo.cat/observacions/xema/dades?codi=D6&amp;dia=2026-03-17T14:30Z</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -33440,7 +33440,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:36</t>
+          <t>2026-03-17 15:17:30</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -33673,7 +33673,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:36</t>
+          <t>2026-03-17 15:17:30</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -33906,7 +33906,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:36</t>
+          <t>2026-03-17 15:17:30</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -34139,7 +34139,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:36</t>
+          <t>2026-03-17 15:17:30</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -34372,17 +34372,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>2026-03-17 14:47:38</t>
+          <t>2026-03-17 15:17:33</t>
         </is>
       